--- a/data/ASC.MI.xlsx
+++ b/data/ASC.MI.xlsx
@@ -62871,7 +62871,7 @@
         <v>43962</v>
       </c>
       <c r="C2718" t="n">
-        <v>2.72499990463257</v>
+        <v>2.74499988555908</v>
       </c>
       <c r="D2718" t="n">
         <v>2.70499992370605</v>
@@ -62883,6 +62883,29 @@
         <v>2.74499988555908</v>
       </c>
       <c r="G2718" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>166168</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>2.73000001907349</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>2.68499994277954</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>2.70000004768372</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>2.68499994277954</v>
+      </c>
+      <c r="G2719" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ASC.MI.xlsx
+++ b/data/ASC.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>151366</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>2.71000003814697</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>2.66499996185303</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>2.69000005722046</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>2.66499996185303</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ASC.MI.xlsx
+++ b/data/ASC.MI.xlsx
@@ -62932,6 +62932,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>111387</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>2.69000005722046</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>2.69000005722046</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ASC.MI.xlsx
+++ b/data/ASC.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>69930</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>2.74499988555908</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>2.74499988555908</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ASC.MI.xlsx
+++ b/data/ASC.MI.xlsx
@@ -62796,22 +62796,22 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>40917</v>
+        <v>50137</v>
       </c>
       <c r="C2715" t="n">
-        <v>2.77500009536743</v>
+        <v>2.79999995231628</v>
       </c>
       <c r="D2715" t="n">
-        <v>2.75</v>
+        <v>2.75500011444092</v>
       </c>
       <c r="E2715" t="n">
-        <v>2.75</v>
+        <v>2.79999995231628</v>
       </c>
       <c r="F2715" t="n">
-        <v>2.76500010490417</v>
+        <v>2.75500011444092</v>
       </c>
       <c r="G2715" t="s">
         <v>7</v>
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>57603</v>
+        <v>40917</v>
       </c>
       <c r="C2716" t="n">
-        <v>2.76999998092651</v>
+        <v>2.77500009536743</v>
       </c>
       <c r="D2716" t="n">
-        <v>2.73000001907349</v>
+        <v>2.75</v>
       </c>
       <c r="E2716" t="n">
-        <v>2.74000000953674</v>
+        <v>2.75</v>
       </c>
       <c r="F2716" t="n">
-        <v>2.73000001907349</v>
+        <v>2.76500010490417</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,22 +62842,22 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>89013</v>
+        <v>57603</v>
       </c>
       <c r="C2717" t="n">
-        <v>2.75</v>
+        <v>2.76999998092651</v>
       </c>
       <c r="D2717" t="n">
-        <v>2.70000004768372</v>
+        <v>2.73000001907349</v>
       </c>
       <c r="E2717" t="n">
-        <v>2.72499990463257</v>
+        <v>2.74000000953674</v>
       </c>
       <c r="F2717" t="n">
-        <v>2.70000004768372</v>
+        <v>2.73000001907349</v>
       </c>
       <c r="G2717" t="s">
         <v>7</v>
@@ -62865,22 +62865,22 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>43962</v>
+        <v>89013</v>
       </c>
       <c r="C2718" t="n">
-        <v>2.74499988555908</v>
+        <v>2.75</v>
       </c>
       <c r="D2718" t="n">
-        <v>2.70499992370605</v>
+        <v>2.70000004768372</v>
       </c>
       <c r="E2718" t="n">
-        <v>2.71000003814697</v>
+        <v>2.72499990463257</v>
       </c>
       <c r="F2718" t="n">
-        <v>2.74499988555908</v>
+        <v>2.70000004768372</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,22 +62888,22 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>166168</v>
+        <v>43962</v>
       </c>
       <c r="C2719" t="n">
-        <v>2.73000001907349</v>
+        <v>2.74499988555908</v>
       </c>
       <c r="D2719" t="n">
-        <v>2.68499994277954</v>
+        <v>2.70499992370605</v>
       </c>
       <c r="E2719" t="n">
-        <v>2.70000004768372</v>
+        <v>2.71000003814697</v>
       </c>
       <c r="F2719" t="n">
-        <v>2.68499994277954</v>
+        <v>2.74499988555908</v>
       </c>
       <c r="G2719" t="s">
         <v>7</v>
@@ -62911,22 +62911,22 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>151366</v>
+        <v>166168</v>
       </c>
       <c r="C2720" t="n">
-        <v>2.71000003814697</v>
+        <v>2.73000001907349</v>
       </c>
       <c r="D2720" t="n">
-        <v>2.66499996185303</v>
+        <v>2.68499994277954</v>
       </c>
       <c r="E2720" t="n">
-        <v>2.69000005722046</v>
+        <v>2.70000004768372</v>
       </c>
       <c r="F2720" t="n">
-        <v>2.66499996185303</v>
+        <v>2.68499994277954</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>111387</v>
+        <v>151366</v>
       </c>
       <c r="C2721" t="n">
-        <v>2.69000005722046</v>
+        <v>2.71000003814697</v>
       </c>
       <c r="D2721" t="n">
-        <v>2.66000008583069</v>
+        <v>2.66499996185303</v>
       </c>
       <c r="E2721" t="n">
         <v>2.69000005722046</v>
       </c>
       <c r="F2721" t="n">
-        <v>2.66000008583069</v>
+        <v>2.66499996185303</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>69930</v>
+        <v>111387</v>
       </c>
       <c r="C2722" t="n">
-        <v>2.74499988555908</v>
+        <v>2.69000005722046</v>
       </c>
       <c r="D2722" t="n">
         <v>2.66000008583069</v>
       </c>
       <c r="E2722" t="n">
+        <v>2.69000005722046</v>
+      </c>
+      <c r="F2722" t="n">
         <v>2.66000008583069</v>
       </c>
-      <c r="F2722" t="n">
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>93636</v>
+      </c>
+      <c r="C2723" t="n">
         <v>2.74499988555908</v>
       </c>
-      <c r="G2722" t="s">
+      <c r="D2723" t="n">
+        <v>2.68499994277954</v>
+      </c>
+      <c r="E2723" t="n">
+        <v>2.74499988555908</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>2.72499990463257</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ASC.MI.xlsx
+++ b/data/ASC.MI.xlsx
@@ -421,7 +421,7 @@
         <v>2.21600008010864</v>
       </c>
       <c r="G2" t="n">
-        <v>1.21448862552643</v>
+        <v>1.21448886394501</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G5" t="n">
-        <v>1.20571982860565</v>
+        <v>1.20571959018707</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>2.17600011825562</v>
       </c>
       <c r="G6" t="n">
-        <v>1.19256639480591</v>
+        <v>1.1925665140152</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>2.16400003433228</v>
       </c>
       <c r="G7" t="n">
-        <v>1.18598973751068</v>
+        <v>1.18598985671997</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G9" t="n">
-        <v>1.21120035648346</v>
+        <v>1.21120047569275</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>2.16599988937378</v>
       </c>
       <c r="G10" t="n">
-        <v>1.1870858669281</v>
+        <v>1.18708598613739</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G12" t="n">
-        <v>1.13447260856628</v>
+        <v>1.13447272777557</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>2.07599997520447</v>
       </c>
       <c r="G13" t="n">
-        <v>1.13776099681854</v>
+        <v>1.13776111602783</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G14" t="n">
-        <v>1.10158956050873</v>
+        <v>1.10158944129944</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G15" t="n">
-        <v>1.12351155281067</v>
+        <v>1.12351143360138</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>2.16400003433228</v>
       </c>
       <c r="G16" t="n">
-        <v>1.18598973751068</v>
+        <v>1.18598985671997</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G17" t="n">
-        <v>1.19475865364075</v>
+        <v>1.19475877285004</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>2.17400002479553</v>
       </c>
       <c r="G18" t="n">
-        <v>1.19147038459778</v>
+        <v>1.19147062301636</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>2.16199994087219</v>
       </c>
       <c r="G19" t="n">
-        <v>1.18489384651184</v>
+        <v>1.18489372730255</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G20" t="n">
-        <v>1.19475865364075</v>
+        <v>1.19475877285004</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>2.20600008964539</v>
       </c>
       <c r="G21" t="n">
-        <v>1.20900821685791</v>
+        <v>1.20900809764862</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>2.21399998664856</v>
       </c>
       <c r="G22" t="n">
-        <v>1.21339237689972</v>
+        <v>1.21339273452759</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G24" t="n">
-        <v>1.21120035648346</v>
+        <v>1.21120047569275</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G25" t="n">
-        <v>1.20023930072784</v>
+        <v>1.20023918151855</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>2.16400003433228</v>
       </c>
       <c r="G26" t="n">
-        <v>1.18598973751068</v>
+        <v>1.18598985671997</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G28" t="n">
-        <v>1.150914311409</v>
+        <v>1.15091407299042</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>2.09800004959106</v>
       </c>
       <c r="G29" t="n">
-        <v>1.14981830120087</v>
+        <v>1.14981806278229</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>2.06599998474121</v>
       </c>
       <c r="G30" t="n">
-        <v>1.13228046894073</v>
+        <v>1.13228034973145</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>2.09400010108948</v>
       </c>
       <c r="G31" t="n">
-        <v>1.14762604236603</v>
+        <v>1.14762592315674</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>2.1340000629425</v>
       </c>
       <c r="G32" t="n">
-        <v>1.16954815387726</v>
+        <v>1.16954827308655</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G33" t="n">
-        <v>1.16735589504242</v>
+        <v>1.16735601425171</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G34" t="n">
-        <v>1.16735589504242</v>
+        <v>1.16735601425171</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G35" t="n">
-        <v>1.17283642292023</v>
+        <v>1.17283654212952</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G38" t="n">
-        <v>1.16735589504242</v>
+        <v>1.16735601425171</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G39" t="n">
-        <v>1.16735589504242</v>
+        <v>1.16735601425171</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>2.17400002479553</v>
       </c>
       <c r="G40" t="n">
-        <v>1.19147038459778</v>
+        <v>1.19147062301636</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G41" t="n">
-        <v>1.19475865364075</v>
+        <v>1.19475877285004</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G42" t="n">
-        <v>1.20023930072784</v>
+        <v>1.20023918151855</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G45" t="n">
-        <v>1.2243537902832</v>
+        <v>1.22435355186462</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G48" t="n">
-        <v>1.20023930072784</v>
+        <v>1.20023918151855</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G49" t="n">
-        <v>1.21120035648346</v>
+        <v>1.21120047569275</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G50" t="n">
-        <v>1.20023930072784</v>
+        <v>1.20023918151855</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>2.22399997711182</v>
       </c>
       <c r="G52" t="n">
-        <v>1.21887302398682</v>
+        <v>1.21887314319611</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>2.29200005531311</v>
       </c>
       <c r="G57" t="n">
-        <v>1.25614070892334</v>
+        <v>1.25614082813263</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>2.2739999294281</v>
       </c>
       <c r="G58" t="n">
-        <v>1.24627566337585</v>
+        <v>1.24627578258514</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>2.26600003242493</v>
       </c>
       <c r="G59" t="n">
-        <v>1.24189114570618</v>
+        <v>1.24189126491547</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G61" t="n">
-        <v>1.23969924449921</v>
+        <v>1.23969912528992</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>2.28800010681152</v>
       </c>
       <c r="G62" t="n">
-        <v>1.25394880771637</v>
+        <v>1.25394856929779</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>2.29200005531311</v>
       </c>
       <c r="G63" t="n">
-        <v>1.25614070892334</v>
+        <v>1.25614082813263</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G64" t="n">
-        <v>1.25723671913147</v>
+        <v>1.25723683834076</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G65" t="n">
-        <v>1.26052510738373</v>
+        <v>1.26052522659302</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>2.27600002288818</v>
       </c>
       <c r="G66" t="n">
-        <v>1.24737191200256</v>
+        <v>1.24737179279327</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>2.30200004577637</v>
       </c>
       <c r="G68" t="n">
-        <v>1.26162135601044</v>
+        <v>1.26162147521973</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G69" t="n">
-        <v>1.26052510738373</v>
+        <v>1.26052522659302</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G71" t="n">
-        <v>1.27696681022644</v>
+        <v>1.27696692943573</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>2.33400011062622</v>
       </c>
       <c r="G72" t="n">
-        <v>1.27915894985199</v>
+        <v>1.27915906906128</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>2.34800004959106</v>
       </c>
       <c r="G74" t="n">
-        <v>1.28683185577393</v>
+        <v>1.28683173656464</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>2.34800004959106</v>
       </c>
       <c r="G75" t="n">
-        <v>1.28683185577393</v>
+        <v>1.28683173656464</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>2.33400011062622</v>
       </c>
       <c r="G76" t="n">
-        <v>1.27915894985199</v>
+        <v>1.27915906906128</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G78" t="n">
-        <v>1.2747745513916</v>
+        <v>1.27477467060089</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>2.33200001716614</v>
       </c>
       <c r="G80" t="n">
-        <v>1.27806293964386</v>
+        <v>1.27806282043457</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>2.3659999370575</v>
       </c>
       <c r="G81" t="n">
-        <v>1.29669654369354</v>
+        <v>1.29669678211212</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>2.36199998855591</v>
       </c>
       <c r="G88" t="n">
-        <v>1.29450464248657</v>
+        <v>1.29450452327728</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>2.26399993896484</v>
       </c>
       <c r="G90" t="n">
-        <v>1.32501232624054</v>
+        <v>1.32501208782196</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G91" t="n">
-        <v>1.32267129421234</v>
+        <v>1.32267117500305</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>2.26600003242493</v>
       </c>
       <c r="G92" t="n">
-        <v>1.32618248462677</v>
+        <v>1.32618260383606</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G95" t="n">
-        <v>1.35193359851837</v>
+        <v>1.35193383693695</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>2.33200001716614</v>
       </c>
       <c r="G96" t="n">
-        <v>1.36480939388275</v>
+        <v>1.36480927467346</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>2.33200001716614</v>
       </c>
       <c r="G97" t="n">
-        <v>1.36480939388275</v>
+        <v>1.36480927467346</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>2.34400010108948</v>
       </c>
       <c r="G98" t="n">
-        <v>1.37183260917664</v>
+        <v>1.37183237075806</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>2.35400009155273</v>
       </c>
       <c r="G100" t="n">
-        <v>1.37768507003784</v>
+        <v>1.37768483161926</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>2.36199998855591</v>
       </c>
       <c r="G101" t="n">
-        <v>1.38236701488495</v>
+        <v>1.38236677646637</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G103" t="n">
-        <v>1.41631150245667</v>
+        <v>1.41631162166595</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G105" t="n">
-        <v>1.42801678180695</v>
+        <v>1.42801654338837</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>2.46399998664856</v>
       </c>
       <c r="G106" t="n">
-        <v>1.44206285476685</v>
+        <v>1.44206273555756</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>2.50200009346008</v>
       </c>
       <c r="G107" t="n">
-        <v>1.46430253982544</v>
+        <v>1.46430242061615</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>2.44199991226196</v>
       </c>
       <c r="G108" t="n">
-        <v>1.42918705940247</v>
+        <v>1.42918717861176</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G109" t="n">
-        <v>1.43972170352936</v>
+        <v>1.43972194194794</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>2.43199992179871</v>
       </c>
       <c r="G110" t="n">
-        <v>1.42333471775055</v>
+        <v>1.42333483695984</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>2.59200000762939</v>
       </c>
       <c r="G114" t="n">
-        <v>1.51697492599487</v>
+        <v>1.51697480678558</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>2.47399997711182</v>
       </c>
       <c r="G117" t="n">
-        <v>1.44791543483734</v>
+        <v>1.44791531562805</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>2.52600002288818</v>
       </c>
       <c r="G119" t="n">
-        <v>1.47834849357605</v>
+        <v>1.47834837436676</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>2.59800004959106</v>
       </c>
       <c r="G120" t="n">
-        <v>1.52048671245575</v>
+        <v>1.52048659324646</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G124" t="n">
-        <v>1.46898448467255</v>
+        <v>1.46898436546326</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>2.53600001335144</v>
       </c>
       <c r="G126" t="n">
-        <v>1.48420095443726</v>
+        <v>1.48420107364655</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G127" t="n">
-        <v>1.51580440998077</v>
+        <v>1.51580452919006</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>2.67600011825562</v>
       </c>
       <c r="G132" t="n">
-        <v>1.56613612174988</v>
+        <v>1.56613636016846</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.69600009918213</v>
       </c>
       <c r="G134" t="n">
-        <v>1.57784140110016</v>
+        <v>1.57784116268158</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>2.79399991035461</v>
       </c>
       <c r="G143" t="n">
-        <v>1.63519632816315</v>
+        <v>1.63519608974457</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>2.79800009727478</v>
       </c>
       <c r="G144" t="n">
-        <v>1.63753712177277</v>
+        <v>1.63753724098206</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G149" t="n">
-        <v>1.65041303634644</v>
+        <v>1.65041267871857</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G153" t="n">
-        <v>1.62115001678467</v>
+        <v>1.62115013599396</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>2.78800010681152</v>
       </c>
       <c r="G154" t="n">
-        <v>1.63168466091156</v>
+        <v>1.63168478012085</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>2.89599990844727</v>
       </c>
       <c r="G158" t="n">
-        <v>1.69489169120789</v>
+        <v>1.69489181041718</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>2.87599992752075</v>
       </c>
       <c r="G159" t="n">
-        <v>1.68318665027618</v>
+        <v>1.68318676948547</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G160" t="n">
-        <v>1.66211748123169</v>
+        <v>1.66211771965027</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>2.83800005912781</v>
       </c>
       <c r="G161" t="n">
-        <v>1.66094708442688</v>
+        <v>1.66094720363617</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G162" t="n">
-        <v>1.65041303634644</v>
+        <v>1.65041267871857</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>2.83400011062622</v>
       </c>
       <c r="G163" t="n">
-        <v>1.65860617160797</v>
+        <v>1.65860629081726</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>2.83800005912781</v>
       </c>
       <c r="G164" t="n">
-        <v>1.66094708442688</v>
+        <v>1.66094720363617</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G165" t="n">
-        <v>1.67967510223389</v>
+        <v>1.67967522144318</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G167" t="n">
-        <v>1.67382252216339</v>
+        <v>1.67382276058197</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>2.8840000629425</v>
       </c>
       <c r="G168" t="n">
-        <v>1.68786907196045</v>
+        <v>1.68786871433258</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>2.86199998855591</v>
       </c>
       <c r="G169" t="n">
-        <v>1.67499327659607</v>
+        <v>1.67499315738678</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G170" t="n">
-        <v>1.67382252216339</v>
+        <v>1.67382276058197</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>2.86199998855591</v>
       </c>
       <c r="G172" t="n">
-        <v>1.67499327659607</v>
+        <v>1.67499315738678</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>2.75</v>
       </c>
       <c r="G178" t="n">
-        <v>1.60944533348083</v>
+        <v>1.60944485664368</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>2.6159999370575</v>
       </c>
       <c r="G179" t="n">
-        <v>1.53102111816406</v>
+        <v>1.53102099895477</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>2.6159999370575</v>
       </c>
       <c r="G180" t="n">
-        <v>1.53102111816406</v>
+        <v>1.53102099895477</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>2.6159999370575</v>
       </c>
       <c r="G181" t="n">
-        <v>1.53102111816406</v>
+        <v>1.53102099895477</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>2.6159999370575</v>
       </c>
       <c r="G182" t="n">
-        <v>1.53102111816406</v>
+        <v>1.53102099895477</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>2.64800000190735</v>
       </c>
       <c r="G183" t="n">
-        <v>1.54974937438965</v>
+        <v>1.54974913597107</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>2.6159999370575</v>
       </c>
       <c r="G184" t="n">
-        <v>1.53102111816406</v>
+        <v>1.53102099895477</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>2.60400009155273</v>
       </c>
       <c r="G186" t="n">
-        <v>1.52399790287018</v>
+        <v>1.52399802207947</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>2.6159999370575</v>
       </c>
       <c r="G188" t="n">
-        <v>1.53102111816406</v>
+        <v>1.53102099895477</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>2.62400007247925</v>
       </c>
       <c r="G189" t="n">
-        <v>1.53570330142975</v>
+        <v>1.53570318222046</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>2.6159999370575</v>
       </c>
       <c r="G190" t="n">
-        <v>1.53102111816406</v>
+        <v>1.53102099895477</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>2.66599988937378</v>
       </c>
       <c r="G191" t="n">
-        <v>1.56028366088867</v>
+        <v>1.56028354167938</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>2.68400001525879</v>
       </c>
       <c r="G192" t="n">
-        <v>1.57081806659698</v>
+        <v>1.57081830501556</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G195" t="n">
-        <v>1.55091965198517</v>
+        <v>1.55091977119446</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>2.6159999370575</v>
       </c>
       <c r="G196" t="n">
-        <v>1.53102111816406</v>
+        <v>1.53102099895477</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>2.6159999370575</v>
       </c>
       <c r="G198" t="n">
-        <v>1.53102111816406</v>
+        <v>1.53102099895477</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>2.61800003051758</v>
       </c>
       <c r="G199" t="n">
-        <v>1.53219163417816</v>
+        <v>1.53219151496887</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>2.6159999370575</v>
       </c>
       <c r="G200" t="n">
-        <v>1.53102111816406</v>
+        <v>1.53102099895477</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>2.61800003051758</v>
       </c>
       <c r="G201" t="n">
-        <v>1.53219163417816</v>
+        <v>1.53219151496887</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>2.62199997901917</v>
       </c>
       <c r="G202" t="n">
-        <v>1.53453266620636</v>
+        <v>1.53453254699707</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>2.62599992752075</v>
       </c>
       <c r="G203" t="n">
-        <v>1.53687381744385</v>
+        <v>1.53687357902527</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>2.67400002479553</v>
       </c>
       <c r="G205" t="n">
-        <v>1.56496572494507</v>
+        <v>1.56496584415436</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G206" t="n">
-        <v>1.56847715377808</v>
+        <v>1.5684769153595</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>2.68799996376038</v>
       </c>
       <c r="G208" t="n">
-        <v>1.57315933704376</v>
+        <v>1.57315921783447</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>2.62599992752075</v>
       </c>
       <c r="G210" t="n">
-        <v>1.53687381744385</v>
+        <v>1.53687357902527</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G213" t="n">
-        <v>1.56262457370758</v>
+        <v>1.56262469291687</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G215" t="n">
-        <v>1.55091965198517</v>
+        <v>1.55091977119446</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>2.65199995040894</v>
       </c>
       <c r="G216" t="n">
-        <v>1.55209016799927</v>
+        <v>1.55209004878998</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>2.65199995040894</v>
       </c>
       <c r="G217" t="n">
-        <v>1.55209016799927</v>
+        <v>1.55209004878998</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G218" t="n">
-        <v>1.55091965198517</v>
+        <v>1.55091977119446</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G219" t="n">
-        <v>1.55091965198517</v>
+        <v>1.55091977119446</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G220" t="n">
-        <v>1.55091965198517</v>
+        <v>1.55091977119446</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>2.49200010299683</v>
       </c>
       <c r="G225" t="n">
-        <v>1.45844984054565</v>
+        <v>1.45844995975494</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G230" t="n">
-        <v>1.48068928718567</v>
+        <v>1.48068940639496</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>2.50200009346008</v>
       </c>
       <c r="G237" t="n">
-        <v>1.46430253982544</v>
+        <v>1.46430242061615</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>2.50799989700317</v>
       </c>
       <c r="G238" t="n">
-        <v>1.46781384944916</v>
+        <v>1.46781396865845</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>2.50799989700317</v>
       </c>
       <c r="G239" t="n">
-        <v>1.46781384944916</v>
+        <v>1.46781396865845</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G241" t="n">
-        <v>1.49239420890808</v>
+        <v>1.49239456653595</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>2.57399988174438</v>
       </c>
       <c r="G242" t="n">
-        <v>1.50644028186798</v>
+        <v>1.50644052028656</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G244" t="n">
-        <v>1.52165710926056</v>
+        <v>1.52165687084198</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>2.58599996566772</v>
       </c>
       <c r="G245" t="n">
-        <v>1.51346337795258</v>
+        <v>1.51346349716187</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>2.57599997520447</v>
       </c>
       <c r="G246" t="n">
-        <v>1.50761079788208</v>
+        <v>1.50761103630066</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>2.60400009155273</v>
       </c>
       <c r="G247" t="n">
-        <v>1.52399790287018</v>
+        <v>1.52399802207947</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>2.68799996376038</v>
       </c>
       <c r="G248" t="n">
-        <v>1.57315933704376</v>
+        <v>1.57315921783447</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>2.65599989891052</v>
       </c>
       <c r="G249" t="n">
-        <v>1.55443120002747</v>
+        <v>1.5544308423996</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>2.65199995040894</v>
       </c>
       <c r="G250" t="n">
-        <v>1.55209016799927</v>
+        <v>1.55209004878998</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>2.70199990272522</v>
       </c>
       <c r="G252" t="n">
-        <v>1.58135259151459</v>
+        <v>1.58135271072388</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G254" t="n">
-        <v>1.59188747406006</v>
+        <v>1.59188735485077</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>2.71399998664856</v>
       </c>
       <c r="G255" t="n">
-        <v>1.58837568759918</v>
+        <v>1.58837616443634</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>2.71399998664856</v>
       </c>
       <c r="G256" t="n">
-        <v>1.58837568759918</v>
+        <v>1.58837616443634</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G259" t="n">
-        <v>1.65041303634644</v>
+        <v>1.65041267871857</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>2.75</v>
       </c>
       <c r="G261" t="n">
-        <v>1.60944533348083</v>
+        <v>1.60944485664368</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G263" t="n">
-        <v>1.58603489398956</v>
+        <v>1.58603477478027</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G264" t="n">
-        <v>1.58603489398956</v>
+        <v>1.58603477478027</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>2.72199988365173</v>
       </c>
       <c r="G265" t="n">
-        <v>1.59305799007416</v>
+        <v>1.59305810928345</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G266" t="n">
-        <v>1.59188747406006</v>
+        <v>1.59188735485077</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>2.73799991607666</v>
       </c>
       <c r="G269" t="n">
-        <v>1.60242187976837</v>
+        <v>1.60242199897766</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>2.75</v>
       </c>
       <c r="G271" t="n">
-        <v>1.60944533348083</v>
+        <v>1.60944485664368</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G272" t="n">
-        <v>1.62115001678467</v>
+        <v>1.62115013599396</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>2.75</v>
       </c>
       <c r="G275" t="n">
-        <v>1.60944533348083</v>
+        <v>1.60944485664368</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>2.75</v>
       </c>
       <c r="G276" t="n">
-        <v>1.60944533348083</v>
+        <v>1.60944485664368</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>2.73399996757507</v>
       </c>
       <c r="G278" t="n">
-        <v>1.60008108615875</v>
+        <v>1.60008096694946</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>2.82599997520447</v>
       </c>
       <c r="G283" t="n">
-        <v>1.65392422676086</v>
+        <v>1.65392410755157</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>2.83800005912781</v>
       </c>
       <c r="G285" t="n">
-        <v>1.66094708442688</v>
+        <v>1.66094720363617</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>2.80800008773804</v>
       </c>
       <c r="G286" t="n">
-        <v>1.64338982105255</v>
+        <v>1.64338946342468</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G287" t="n">
-        <v>1.67967510223389</v>
+        <v>1.67967522144318</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G288" t="n">
-        <v>1.67382252216339</v>
+        <v>1.67382276058197</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>2.88800001144409</v>
       </c>
       <c r="G290" t="n">
-        <v>1.69021010398865</v>
+        <v>1.69020998477936</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>2.83599996566772</v>
       </c>
       <c r="G292" t="n">
-        <v>1.65977668762207</v>
+        <v>1.65977692604065</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G293" t="n">
-        <v>1.69138050079346</v>
+        <v>1.69138038158417</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G294" t="n">
-        <v>1.69138050079346</v>
+        <v>1.69138038158417</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>2.89599990844727</v>
       </c>
       <c r="G297" t="n">
-        <v>1.69489169120789</v>
+        <v>1.69489181041718</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G299" t="n">
-        <v>1.69138050079346</v>
+        <v>1.69138038158417</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G300" t="n">
-        <v>1.72649538516998</v>
+        <v>1.72649526596069</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G302" t="n">
-        <v>1.74405288696289</v>
+        <v>1.74405312538147</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>3.05599999427795</v>
       </c>
       <c r="G304" t="n">
-        <v>1.78853249549866</v>
+        <v>1.78853225708008</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>3.08200001716614</v>
       </c>
       <c r="G305" t="n">
-        <v>1.80374896526337</v>
+        <v>1.80374908447266</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>3.09599995613098</v>
       </c>
       <c r="G306" t="n">
-        <v>1.81194221973419</v>
+        <v>1.81194233894348</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G307" t="n">
-        <v>1.80843091011047</v>
+        <v>1.8084305524826</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>3.15599989891052</v>
       </c>
       <c r="G308" t="n">
-        <v>1.84705746173859</v>
+        <v>1.84705758094788</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>3.21799993515015</v>
       </c>
       <c r="G310" t="n">
-        <v>1.88334286212921</v>
+        <v>1.88334310054779</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G311" t="n">
-        <v>1.90792369842529</v>
+        <v>1.90792393684387</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>3.29200005531311</v>
       </c>
       <c r="G312" t="n">
-        <v>1.92665183544159</v>
+        <v>1.92665195465088</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>3.32200002670288</v>
       </c>
       <c r="G313" t="n">
-        <v>1.94420957565308</v>
+        <v>1.94420945644379</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G314" t="n">
-        <v>1.91377592086792</v>
+        <v>1.91377627849579</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>3.2739999294281</v>
       </c>
       <c r="G315" t="n">
-        <v>1.91611707210541</v>
+        <v>1.9161171913147</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G316" t="n">
-        <v>1.95474410057068</v>
+        <v>1.9547438621521</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>3.33200001716614</v>
       </c>
       <c r="G317" t="n">
-        <v>1.95006203651428</v>
+        <v>1.95006191730499</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>3.35800004005432</v>
       </c>
       <c r="G318" t="n">
-        <v>1.96527886390686</v>
+        <v>1.96527862548828</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G320" t="n">
-        <v>1.98985946178436</v>
+        <v>1.98985922336578</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>3.40799999237061</v>
       </c>
       <c r="G321" t="n">
-        <v>1.99454152584076</v>
+        <v>1.99454128742218</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>3.5</v>
       </c>
       <c r="G327" t="n">
-        <v>2.04838466644287</v>
+        <v>2.04838442802429</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G328" t="n">
-        <v>2.07179427146912</v>
+        <v>2.0717945098877</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>3.5220000743866</v>
       </c>
       <c r="G330" t="n">
-        <v>2.06125974655151</v>
+        <v>2.06126022338867</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>3.59400010108948</v>
       </c>
       <c r="G333" t="n">
-        <v>2.10339832305908</v>
+        <v>2.10339856147766</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>3.54399991035461</v>
       </c>
       <c r="G334" t="n">
-        <v>2.07413578033447</v>
+        <v>2.07413554191589</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>3.53800010681152</v>
       </c>
       <c r="G335" t="n">
-        <v>2.07062387466431</v>
+        <v>2.07062411308289</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G336" t="n">
-        <v>2.10690999031067</v>
+        <v>2.10690975189209</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>3.59400010108948</v>
       </c>
       <c r="G338" t="n">
-        <v>2.10339832305908</v>
+        <v>2.10339856147766</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>3.62199997901917</v>
       </c>
       <c r="G340" t="n">
-        <v>2.11978578567505</v>
+        <v>2.11978530883789</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G341" t="n">
-        <v>2.16543483734131</v>
+        <v>2.16543531417847</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G342" t="n">
-        <v>2.16543483734131</v>
+        <v>2.16543531417847</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>3.78200006484985</v>
       </c>
       <c r="G344" t="n">
-        <v>2.21342611312866</v>
+        <v>2.21342587471008</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>3.62599992752075</v>
       </c>
       <c r="G346" t="n">
-        <v>2.22817420959473</v>
+        <v>2.22817373275757</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>3.60599994659424</v>
       </c>
       <c r="G347" t="n">
-        <v>2.21588397026062</v>
+        <v>2.21588373184204</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>3.57800006866455</v>
       </c>
       <c r="G348" t="n">
-        <v>2.19867777824402</v>
+        <v>2.1986780166626</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>3.48600006103516</v>
       </c>
       <c r="G349" t="n">
-        <v>2.14214396476746</v>
+        <v>2.14214372634888</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G354" t="n">
-        <v>2.18761682510376</v>
+        <v>2.18761658668518</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>3.58400011062622</v>
       </c>
       <c r="G355" t="n">
-        <v>2.20236492156982</v>
+        <v>2.2023651599884</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>3.6340000629425</v>
       </c>
       <c r="G357" t="n">
-        <v>2.23309016227722</v>
+        <v>2.23308992385864</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G359" t="n">
-        <v>2.23677706718445</v>
+        <v>2.23677682876587</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>3.55599999427795</v>
       </c>
       <c r="G360" t="n">
-        <v>2.18515872955322</v>
+        <v>2.18515849113464</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>3.62400007247925</v>
       </c>
       <c r="G362" t="n">
-        <v>2.22694516181946</v>
+        <v>2.22694492340088</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>3.61800003051758</v>
       </c>
       <c r="G365" t="n">
-        <v>2.22325754165649</v>
+        <v>2.22325801849365</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G366" t="n">
-        <v>2.21219730377197</v>
+        <v>2.21219682693481</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G367" t="n">
-        <v>2.23063230514526</v>
+        <v>2.23063206672668</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>3.63199996948242</v>
       </c>
       <c r="G368" t="n">
-        <v>2.23186111450195</v>
+        <v>2.23186063766479</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>3.62199997901917</v>
       </c>
       <c r="G369" t="n">
-        <v>2.22571587562561</v>
+        <v>2.22571611404419</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G370" t="n">
-        <v>2.21219730377197</v>
+        <v>2.21219682693481</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>3.60199999809265</v>
       </c>
       <c r="G371" t="n">
-        <v>2.21342635154724</v>
+        <v>2.21342587471008</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G372" t="n">
-        <v>2.23063230514526</v>
+        <v>2.23063206672668</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>3.61800003051758</v>
       </c>
       <c r="G373" t="n">
-        <v>2.22325754165649</v>
+        <v>2.22325801849365</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>3.71799993515015</v>
       </c>
       <c r="G374" t="n">
-        <v>2.28470754623413</v>
+        <v>2.28470778465271</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>3.61800003051758</v>
       </c>
       <c r="G376" t="n">
-        <v>2.22325754165649</v>
+        <v>2.22325801849365</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>3.59599995613098</v>
       </c>
       <c r="G377" t="n">
-        <v>2.20973920822144</v>
+        <v>2.20973873138428</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>3.54800009727478</v>
       </c>
       <c r="G379" t="n">
-        <v>2.18024277687073</v>
+        <v>2.18024301528931</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G380" t="n">
-        <v>2.181471824646</v>
+        <v>2.18147158622742</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>3.50799989700317</v>
       </c>
       <c r="G390" t="n">
-        <v>2.15566277503967</v>
+        <v>2.15566325187683</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>3.49399995803833</v>
       </c>
       <c r="G391" t="n">
-        <v>2.14706015586853</v>
+        <v>2.14705991744995</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G392" t="n">
-        <v>2.14460206031799</v>
+        <v>2.14460182189941</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>3.49600005149841</v>
       </c>
       <c r="G393" t="n">
-        <v>2.1482892036438</v>
+        <v>2.14828896522522</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>3.49399995803833</v>
       </c>
       <c r="G394" t="n">
-        <v>2.14706015586853</v>
+        <v>2.14705991744995</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>3.50399994850159</v>
       </c>
       <c r="G396" t="n">
-        <v>2.15320491790771</v>
+        <v>2.15320515632629</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G399" t="n">
-        <v>2.09544229507446</v>
+        <v>2.09544205665588</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>3.39599990844727</v>
       </c>
       <c r="G400" t="n">
-        <v>2.086838722229</v>
+        <v>2.08683896064758</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G402" t="n">
-        <v>2.10773205757141</v>
+        <v>2.10773229598999</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>3.46399998664856</v>
       </c>
       <c r="G405" t="n">
-        <v>2.12862491607666</v>
+        <v>2.12862515449524</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G406" t="n">
-        <v>2.10773205757141</v>
+        <v>2.10773229598999</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G407" t="n">
-        <v>2.20605206489563</v>
+        <v>2.20605182647705</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G408" t="n">
-        <v>2.181471824646</v>
+        <v>2.18147158622742</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>3.58200001716614</v>
       </c>
       <c r="G409" t="n">
-        <v>2.20113587379456</v>
+        <v>2.20113611221313</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G412" t="n">
-        <v>2.18761682510376</v>
+        <v>2.18761658668518</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>3.58200001716614</v>
       </c>
       <c r="G413" t="n">
-        <v>2.20113587379456</v>
+        <v>2.20113611221313</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>3.55599999427795</v>
       </c>
       <c r="G415" t="n">
-        <v>2.18515872955322</v>
+        <v>2.18515849113464</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>3.5220000743866</v>
       </c>
       <c r="G417" t="n">
-        <v>2.16426587104797</v>
+        <v>2.16426610946655</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>3.53800010681152</v>
       </c>
       <c r="G419" t="n">
-        <v>2.17409777641296</v>
+        <v>2.17409801483154</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>3.4760000705719</v>
       </c>
       <c r="G420" t="n">
-        <v>2.13599896430969</v>
+        <v>2.13599872589111</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G421" t="n">
-        <v>2.14460206031799</v>
+        <v>2.14460182189941</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G422" t="n">
-        <v>2.14460206031799</v>
+        <v>2.14460182189941</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G423" t="n">
-        <v>2.14460206031799</v>
+        <v>2.14460182189941</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G426" t="n">
-        <v>2.14460206031799</v>
+        <v>2.14460182189941</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>3.60199999809265</v>
       </c>
       <c r="G428" t="n">
-        <v>2.21342635154724</v>
+        <v>2.21342587471008</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>3.63199996948242</v>
       </c>
       <c r="G429" t="n">
-        <v>2.23186111450195</v>
+        <v>2.23186063766479</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G431" t="n">
-        <v>2.21834182739258</v>
+        <v>2.21834206581116</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>3.61800003051758</v>
       </c>
       <c r="G434" t="n">
-        <v>2.22325754165649</v>
+        <v>2.22325801849365</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>3.64400005340576</v>
       </c>
       <c r="G435" t="n">
-        <v>2.23923492431641</v>
+        <v>2.23923468589783</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G436" t="n">
-        <v>2.21834182739258</v>
+        <v>2.21834206581116</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G439" t="n">
-        <v>2.181471824646</v>
+        <v>2.18147158622742</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>3.53200006484985</v>
       </c>
       <c r="G440" t="n">
-        <v>2.1704113483429</v>
+        <v>2.17041087150574</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>3.53399991989136</v>
       </c>
       <c r="G442" t="n">
-        <v>2.17164015769958</v>
+        <v>2.17163991928101</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G446" t="n">
-        <v>2.14460206031799</v>
+        <v>2.14460182189941</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>3.51399993896484</v>
       </c>
       <c r="G447" t="n">
-        <v>2.15935015678406</v>
+        <v>2.15934991836548</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G451" t="n">
-        <v>2.21219730377197</v>
+        <v>2.21219682693481</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G452" t="n">
-        <v>2.23063230514526</v>
+        <v>2.23063206672668</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G453" t="n">
-        <v>2.23677706718445</v>
+        <v>2.23677682876587</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G454" t="n">
-        <v>2.23063230514526</v>
+        <v>2.23063206672668</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>3.60599994659424</v>
       </c>
       <c r="G458" t="n">
-        <v>2.21588397026062</v>
+        <v>2.21588373184204</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>3.63199996948242</v>
       </c>
       <c r="G460" t="n">
-        <v>2.23186111450195</v>
+        <v>2.23186063766479</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>3.63199996948242</v>
       </c>
       <c r="G461" t="n">
-        <v>2.23186111450195</v>
+        <v>2.23186063766479</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G462" t="n">
-        <v>2.1937620639801</v>
+        <v>2.19376158714294</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G463" t="n">
-        <v>2.18761682510376</v>
+        <v>2.18761658668518</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>3.60800004005432</v>
       </c>
       <c r="G464" t="n">
-        <v>2.21711301803589</v>
+        <v>2.21711277961731</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>3.62400007247925</v>
       </c>
       <c r="G467" t="n">
-        <v>2.22694516181946</v>
+        <v>2.22694492340088</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>3.63199996948242</v>
       </c>
       <c r="G468" t="n">
-        <v>2.23186111450195</v>
+        <v>2.23186063766479</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>3.63800001144409</v>
       </c>
       <c r="G469" t="n">
-        <v>2.23554801940918</v>
+        <v>2.2355477809906</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>3.60599994659424</v>
       </c>
       <c r="G470" t="n">
-        <v>2.21588397026062</v>
+        <v>2.21588373184204</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G472" t="n">
-        <v>2.28593683242798</v>
+        <v>2.2859365940094</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>3.81399989128113</v>
       </c>
       <c r="G474" t="n">
-        <v>2.34369969367981</v>
+        <v>2.34369945526123</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>3.78200006484985</v>
       </c>
       <c r="G475" t="n">
-        <v>2.32403588294983</v>
+        <v>2.32403564453125</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G481" t="n">
-        <v>2.1937620639801</v>
+        <v>2.19376158714294</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>3.59599995613098</v>
       </c>
       <c r="G484" t="n">
-        <v>2.20973920822144</v>
+        <v>2.20973873138428</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G485" t="n">
-        <v>2.22448682785034</v>
+        <v>2.22448706626892</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G488" t="n">
-        <v>2.23677706718445</v>
+        <v>2.23677682876587</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G490" t="n">
-        <v>2.21219730377197</v>
+        <v>2.21219682693481</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>3.72199988365173</v>
       </c>
       <c r="G492" t="n">
-        <v>2.28716564178467</v>
+        <v>2.28716540336609</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>3.64400005340576</v>
       </c>
       <c r="G493" t="n">
-        <v>2.23923492431641</v>
+        <v>2.23923468589783</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>3.65199995040894</v>
       </c>
       <c r="G496" t="n">
-        <v>2.2441508769989</v>
+        <v>2.24415063858032</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G499" t="n">
-        <v>2.23063230514526</v>
+        <v>2.23063206672668</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G500" t="n">
-        <v>2.19990658760071</v>
+        <v>2.19990682601929</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>3.63800001144409</v>
       </c>
       <c r="G501" t="n">
-        <v>2.23554801940918</v>
+        <v>2.2355477809906</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G502" t="n">
-        <v>2.23677706718445</v>
+        <v>2.23677682876587</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G503" t="n">
-        <v>2.23063230514526</v>
+        <v>2.23063206672668</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>3.62599992752075</v>
       </c>
       <c r="G504" t="n">
-        <v>2.22817420959473</v>
+        <v>2.22817373275757</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>3.58200001716614</v>
       </c>
       <c r="G505" t="n">
-        <v>2.20113587379456</v>
+        <v>2.20113611221313</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G507" t="n">
-        <v>2.22448682785034</v>
+        <v>2.22448706626892</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G508" t="n">
-        <v>2.20605206489563</v>
+        <v>2.20605182647705</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>3.58200001716614</v>
       </c>
       <c r="G509" t="n">
-        <v>2.20113587379456</v>
+        <v>2.20113611221313</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>3.60199999809265</v>
       </c>
       <c r="G510" t="n">
-        <v>2.21342635154724</v>
+        <v>2.21342587471008</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>3.54800009727478</v>
       </c>
       <c r="G512" t="n">
-        <v>2.18024277687073</v>
+        <v>2.18024301528931</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G513" t="n">
-        <v>2.20605206489563</v>
+        <v>2.20605182647705</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G514" t="n">
-        <v>2.23677706718445</v>
+        <v>2.23677682876587</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G519" t="n">
-        <v>2.21219730377197</v>
+        <v>2.21219682693481</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G521" t="n">
-        <v>2.26135683059692</v>
+        <v>2.2613570690155</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G523" t="n">
-        <v>2.25521206855774</v>
+        <v>2.25521183013916</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G524" t="n">
-        <v>2.25828409194946</v>
+        <v>2.25828433036804</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G525" t="n">
-        <v>2.23677706718445</v>
+        <v>2.23677682876587</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G527" t="n">
-        <v>2.25828409194946</v>
+        <v>2.25828433036804</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G528" t="n">
-        <v>2.23063230514526</v>
+        <v>2.23063206672668</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G529" t="n">
-        <v>2.22448682785034</v>
+        <v>2.22448706626892</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G530" t="n">
-        <v>2.22448682785034</v>
+        <v>2.22448706626892</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G531" t="n">
-        <v>2.20605206489563</v>
+        <v>2.20605182647705</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G532" t="n">
-        <v>2.20297980308533</v>
+        <v>2.20297956466675</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G533" t="n">
-        <v>2.181471824646</v>
+        <v>2.18147158622742</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G534" t="n">
-        <v>2.181471824646</v>
+        <v>2.18147158622742</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G536" t="n">
-        <v>2.0278468132019</v>
+        <v>2.02784729003906</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G537" t="n">
-        <v>1.94181728363037</v>
+        <v>1.94181716442108</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>3.25</v>
       </c>
       <c r="G538" t="n">
-        <v>1.99712240695953</v>
+        <v>1.99712204933167</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G539" t="n">
-        <v>1.9694699048996</v>
+        <v>1.96947002410889</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>3.25</v>
       </c>
       <c r="G541" t="n">
-        <v>1.99712240695953</v>
+        <v>1.99712204933167</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G542" t="n">
-        <v>1.98483228683472</v>
+        <v>1.98483216762543</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>3.21499991416931</v>
       </c>
       <c r="G543" t="n">
-        <v>1.97561478614807</v>
+        <v>1.97561466693878</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>3.21499991416931</v>
       </c>
       <c r="G544" t="n">
-        <v>1.97561478614807</v>
+        <v>1.97561466693878</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G546" t="n">
-        <v>1.98483228683472</v>
+        <v>1.98483216762543</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>3.25</v>
       </c>
       <c r="G547" t="n">
-        <v>1.99712240695953</v>
+        <v>1.99712204933167</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G548" t="n">
-        <v>2.01555705070496</v>
+        <v>2.01555681228638</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G549" t="n">
-        <v>1.96332490444183</v>
+        <v>1.96332478523254</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G552" t="n">
-        <v>1.92645478248596</v>
+        <v>1.92645442485809</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G553" t="n">
-        <v>1.91723728179932</v>
+        <v>1.91723692417145</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G554" t="n">
-        <v>1.91723728179932</v>
+        <v>1.91723692417145</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G557" t="n">
-        <v>1.91416478157043</v>
+        <v>1.91416454315186</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G558" t="n">
-        <v>1.9233820438385</v>
+        <v>1.92338240146637</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G559" t="n">
-        <v>1.9233820438385</v>
+        <v>1.92338240146637</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G560" t="n">
-        <v>1.94488966464996</v>
+        <v>1.94488954544067</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>3.15499997138977</v>
       </c>
       <c r="G562" t="n">
-        <v>1.9387446641922</v>
+        <v>1.93874454498291</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>3.15499997138977</v>
       </c>
       <c r="G563" t="n">
-        <v>1.9387446641922</v>
+        <v>1.93874454498291</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G564" t="n">
-        <v>1.96639704704285</v>
+        <v>1.96639740467072</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G566" t="n">
-        <v>2.01862955093384</v>
+        <v>2.01862978935242</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G567" t="n">
-        <v>2.01862955093384</v>
+        <v>2.01862978935242</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>3.25</v>
       </c>
       <c r="G569" t="n">
-        <v>1.99712240695953</v>
+        <v>1.99712204933167</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G570" t="n">
-        <v>1.9694699048996</v>
+        <v>1.96947002410889</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G571" t="n">
-        <v>1.95717978477478</v>
+        <v>1.95717990398407</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G573" t="n">
-        <v>1.99404954910278</v>
+        <v>1.99404978752136</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G574" t="n">
-        <v>2.00326681137085</v>
+        <v>2.00326728820801</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>3.25</v>
       </c>
       <c r="G575" t="n">
-        <v>1.99712240695953</v>
+        <v>1.99712204933167</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G577" t="n">
-        <v>2.00326681137085</v>
+        <v>2.00326728820801</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G578" t="n">
-        <v>2.01862955093384</v>
+        <v>2.01862978935242</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G580" t="n">
-        <v>2.01555705070496</v>
+        <v>2.01555681228638</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G581" t="n">
-        <v>2.00326681137085</v>
+        <v>2.00326728820801</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G583" t="n">
-        <v>2.01248455047607</v>
+        <v>2.01248478889465</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G584" t="n">
-        <v>2.02170181274414</v>
+        <v>2.0217022895813</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G585" t="n">
-        <v>2.02170181274414</v>
+        <v>2.0217022895813</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G586" t="n">
-        <v>2.02170181274414</v>
+        <v>2.0217022895813</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G587" t="n">
-        <v>2.0278468132019</v>
+        <v>2.02784729003906</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G588" t="n">
-        <v>2.0278468132019</v>
+        <v>2.02784729003906</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G589" t="n">
-        <v>2.0278468132019</v>
+        <v>2.02784729003906</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>3.32500004768372</v>
       </c>
       <c r="G590" t="n">
-        <v>2.04320955276489</v>
+        <v>2.04320979118347</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G591" t="n">
-        <v>2.0278468132019</v>
+        <v>2.02784729003906</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G595" t="n">
-        <v>2.16918206214905</v>
+        <v>2.16918182373047</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G597" t="n">
-        <v>2.15381956100464</v>
+        <v>2.15381932258606</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G599" t="n">
-        <v>2.13762497901917</v>
+        <v>2.13762521743774</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G600" t="n">
-        <v>2.13762497901917</v>
+        <v>2.13762521743774</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G602" t="n">
-        <v>2.0728485584259</v>
+        <v>2.07284879684448</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G603" t="n">
-        <v>2.11171436309814</v>
+        <v>2.11171460151672</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G605" t="n">
-        <v>2.02750492095947</v>
+        <v>2.02750515937805</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G606" t="n">
-        <v>2.02750492095947</v>
+        <v>2.02750515937805</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G608" t="n">
-        <v>2.01131105422974</v>
+        <v>2.01131081581116</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G610" t="n">
-        <v>1.99511706829071</v>
+        <v>1.99511682987213</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G611" t="n">
-        <v>1.99511706829071</v>
+        <v>1.99511682987213</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G612" t="n">
-        <v>1.97892260551453</v>
+        <v>1.97892284393311</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G620" t="n">
-        <v>1.93034017086029</v>
+        <v>1.93034040927887</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>2.97499990463257</v>
       </c>
       <c r="G627" t="n">
-        <v>1.92710161209106</v>
+        <v>1.92710137367249</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G628" t="n">
-        <v>1.93681788444519</v>
+        <v>1.93681812286377</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>2.97499990463257</v>
       </c>
       <c r="G629" t="n">
-        <v>1.92710161209106</v>
+        <v>1.92710137367249</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G630" t="n">
-        <v>1.94005656242371</v>
+        <v>1.94005680084229</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G631" t="n">
-        <v>1.89147436618805</v>
+        <v>1.89147460460663</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>3.06500005722046</v>
       </c>
       <c r="G632" t="n">
-        <v>1.98540055751801</v>
+        <v>1.98540031909943</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G634" t="n">
-        <v>1.96596741676331</v>
+        <v>1.96596765518188</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G637" t="n">
-        <v>1.93681788444519</v>
+        <v>1.93681812286377</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>2.97499990463257</v>
       </c>
       <c r="G641" t="n">
-        <v>1.92710161209106</v>
+        <v>1.92710137367249</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G642" t="n">
-        <v>1.94005656242371</v>
+        <v>1.94005680084229</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G646" t="n">
-        <v>1.87204158306122</v>
+        <v>1.87204134464264</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>2.88499999046326</v>
       </c>
       <c r="G647" t="n">
-        <v>1.86880266666412</v>
+        <v>1.8688029050827</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>2.86500000953674</v>
       </c>
       <c r="G648" t="n">
-        <v>1.85584723949432</v>
+        <v>1.8558474779129</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G649" t="n">
-        <v>1.85908591747284</v>
+        <v>1.85908615589142</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G650" t="n">
-        <v>1.87204158306122</v>
+        <v>1.87204134464264</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G651" t="n">
-        <v>1.87851917743683</v>
+        <v>1.87851929664612</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G652" t="n">
-        <v>1.87204158306122</v>
+        <v>1.87204134464264</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G653" t="n">
-        <v>1.8526086807251</v>
+        <v>1.85260844230652</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G654" t="n">
-        <v>1.84613072872162</v>
+        <v>1.84613084793091</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G655" t="n">
-        <v>1.87851917743683</v>
+        <v>1.87851929664612</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G660" t="n">
-        <v>2.29308891296387</v>
+        <v>2.29308867454529</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>3.26500010490417</v>
       </c>
       <c r="G663" t="n">
-        <v>2.11495351791382</v>
+        <v>2.1149537563324</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>3.25</v>
       </c>
       <c r="G665" t="n">
-        <v>2.10523724555969</v>
+        <v>2.10523700714111</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G667" t="n">
-        <v>2.03074407577515</v>
+        <v>2.03074383735657</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G669" t="n">
-        <v>2.02750492095947</v>
+        <v>2.02750515937805</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G670" t="n">
-        <v>1.95948970317841</v>
+        <v>1.95948994159698</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G672" t="n">
-        <v>1.96596741676331</v>
+        <v>1.96596765518188</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G673" t="n">
-        <v>1.99511706829071</v>
+        <v>1.99511682987213</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G674" t="n">
-        <v>2.02102756500244</v>
+        <v>2.02102732658386</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G677" t="n">
-        <v>1.99835550785065</v>
+        <v>1.99835574626923</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G684" t="n">
-        <v>2.01131105422974</v>
+        <v>2.01131081581116</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G687" t="n">
-        <v>2.02750492095947</v>
+        <v>2.02750515937805</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G688" t="n">
-        <v>2.02750492095947</v>
+        <v>2.02750515937805</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G689" t="n">
-        <v>2.05017685890198</v>
+        <v>2.0501766204834</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G690" t="n">
-        <v>2.04693818092346</v>
+        <v>2.04693794250488</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G693" t="n">
-        <v>2.05341577529907</v>
+        <v>2.05341601371765</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G694" t="n">
-        <v>2.05341577529907</v>
+        <v>2.05341601371765</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G695" t="n">
-        <v>2.04693818092346</v>
+        <v>2.04693794250488</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G696" t="n">
-        <v>2.05341577529907</v>
+        <v>2.05341601371765</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G697" t="n">
-        <v>2.04693818092346</v>
+        <v>2.04693794250488</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G698" t="n">
-        <v>2.04693818092346</v>
+        <v>2.04693794250488</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G699" t="n">
-        <v>2.04693818092346</v>
+        <v>2.04693794250488</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G702" t="n">
-        <v>1.93034017086029</v>
+        <v>1.93034040927887</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>2.97499990463257</v>
       </c>
       <c r="G703" t="n">
-        <v>1.92710161209106</v>
+        <v>1.92710137367249</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>2.97499990463257</v>
       </c>
       <c r="G704" t="n">
-        <v>1.92710161209106</v>
+        <v>1.92710137367249</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G706" t="n">
-        <v>1.90442943572998</v>
+        <v>1.90442979335785</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G707" t="n">
-        <v>1.90442943572998</v>
+        <v>1.90442979335785</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G711" t="n">
-        <v>1.95625078678131</v>
+        <v>1.95625102519989</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G714" t="n">
-        <v>1.99835550785065</v>
+        <v>1.99835574626923</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G716" t="n">
-        <v>1.93681788444519</v>
+        <v>1.93681812286377</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>2.97499990463257</v>
       </c>
       <c r="G717" t="n">
-        <v>1.92710161209106</v>
+        <v>1.92710137367249</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G719" t="n">
-        <v>1.85908591747284</v>
+        <v>1.85908615589142</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G720" t="n">
-        <v>1.84613072872162</v>
+        <v>1.84613084793091</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G721" t="n">
-        <v>1.82669770717621</v>
+        <v>1.82669794559479</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G723" t="n">
-        <v>1.87204158306122</v>
+        <v>1.87204134464264</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G724" t="n">
-        <v>1.87851917743683</v>
+        <v>1.87851929664612</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G725" t="n">
-        <v>1.88499665260315</v>
+        <v>1.88499689102173</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>2.97499990463257</v>
       </c>
       <c r="G726" t="n">
-        <v>1.92710161209106</v>
+        <v>1.92710137367249</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>3.04500007629395</v>
       </c>
       <c r="G728" t="n">
-        <v>1.9724452495575</v>
+        <v>1.97244489192963</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G730" t="n">
-        <v>1.99835550785065</v>
+        <v>1.99835574626923</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G733" t="n">
-        <v>1.96596741676331</v>
+        <v>1.96596765518188</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G735" t="n">
-        <v>1.93681788444519</v>
+        <v>1.93681812286377</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G736" t="n">
-        <v>1.96920597553253</v>
+        <v>1.96920621395111</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G742" t="n">
-        <v>1.99511706829071</v>
+        <v>1.99511682987213</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G744" t="n">
-        <v>1.95625078678131</v>
+        <v>1.95625102519989</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G747" t="n">
-        <v>1.99835550785065</v>
+        <v>1.99835574626923</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G749" t="n">
-        <v>2.0728485584259</v>
+        <v>2.07284879684448</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G750" t="n">
-        <v>1.99835550785065</v>
+        <v>1.99835574626923</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G752" t="n">
-        <v>1.99835550785065</v>
+        <v>1.99835574626923</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G753" t="n">
-        <v>1.99511706829071</v>
+        <v>1.99511682987213</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G754" t="n">
-        <v>2.02102756500244</v>
+        <v>2.02102732658386</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G759" t="n">
-        <v>1.99511706829071</v>
+        <v>1.99511682987213</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G766" t="n">
-        <v>2.12790870666504</v>
+        <v>2.12790894508362</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G774" t="n">
-        <v>2.05017685890198</v>
+        <v>2.0501766204834</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G777" t="n">
-        <v>2.0728485584259</v>
+        <v>2.07284879684448</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G782" t="n">
-        <v>2.0728485584259</v>
+        <v>2.07284879684448</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G783" t="n">
-        <v>2.0728485584259</v>
+        <v>2.07284879684448</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>3.25</v>
       </c>
       <c r="G788" t="n">
-        <v>2.10523724555969</v>
+        <v>2.10523700714111</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G789" t="n">
-        <v>2.12143111228943</v>
+        <v>2.12143135070801</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G790" t="n">
-        <v>2.11171436309814</v>
+        <v>2.11171460151672</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>3.25</v>
       </c>
       <c r="G791" t="n">
-        <v>2.10523724555969</v>
+        <v>2.10523700714111</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G794" t="n">
-        <v>2.11171436309814</v>
+        <v>2.11171460151672</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G795" t="n">
-        <v>2.12466979026794</v>
+        <v>2.12466955184937</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G796" t="n">
-        <v>2.13762497901917</v>
+        <v>2.13762521743774</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>3.3050000667572</v>
       </c>
       <c r="G797" t="n">
-        <v>2.14086389541626</v>
+        <v>2.14086413383484</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G798" t="n">
-        <v>2.12790870666504</v>
+        <v>2.12790894508362</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G799" t="n">
-        <v>2.12466979026794</v>
+        <v>2.12466955184937</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G801" t="n">
-        <v>2.18944644927979</v>
+        <v>2.18944668769836</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G802" t="n">
-        <v>2.18296885490417</v>
+        <v>2.1829686164856</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>3.36500000953674</v>
       </c>
       <c r="G803" t="n">
-        <v>2.17973017692566</v>
+        <v>2.17972993850708</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>3.36500000953674</v>
       </c>
       <c r="G804" t="n">
-        <v>2.17973017692566</v>
+        <v>2.17972993850708</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>3.36500000953674</v>
       </c>
       <c r="G805" t="n">
-        <v>2.17973017692566</v>
+        <v>2.17972993850708</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G807" t="n">
-        <v>2.19916319847107</v>
+        <v>2.19916296005249</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G808" t="n">
-        <v>2.18944644927979</v>
+        <v>2.18944668769836</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G809" t="n">
-        <v>2.18296885490417</v>
+        <v>2.1829686164856</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G812" t="n">
-        <v>2.24126768112183</v>
+        <v>2.24126744270325</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G813" t="n">
-        <v>2.21535706520081</v>
+        <v>2.21535730361938</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G814" t="n">
-        <v>2.24774551391602</v>
+        <v>2.24774527549744</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G815" t="n">
-        <v>2.21211838722229</v>
+        <v>2.21211814880371</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G818" t="n">
-        <v>2.20887970924377</v>
+        <v>2.2088794708252</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G819" t="n">
-        <v>2.20887970924377</v>
+        <v>2.2088794708252</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G821" t="n">
-        <v>2.21211838722229</v>
+        <v>2.21211814880371</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G823" t="n">
-        <v>2.24774551391602</v>
+        <v>2.24774527549744</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G825" t="n">
-        <v>2.29308891296387</v>
+        <v>2.29308867454529</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>3.5</v>
       </c>
       <c r="G827" t="n">
-        <v>2.26717853546143</v>
+        <v>2.26717829704285</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G828" t="n">
-        <v>2.25746202468872</v>
+        <v>2.25746154785156</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>3.5</v>
       </c>
       <c r="G829" t="n">
-        <v>2.26717853546143</v>
+        <v>2.26717829704285</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G830" t="n">
-        <v>2.29956650733948</v>
+        <v>2.2995662689209</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G831" t="n">
-        <v>2.29956650733948</v>
+        <v>2.2995662689209</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G833" t="n">
-        <v>2.31252217292786</v>
+        <v>2.3125216960907</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G834" t="n">
-        <v>2.30928325653076</v>
+        <v>2.30928301811218</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G836" t="n">
-        <v>2.3384325504303</v>
+        <v>2.33843278884888</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G837" t="n">
-        <v>2.37405967712402</v>
+        <v>2.37405943870544</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>3.68499994277954</v>
       </c>
       <c r="G838" t="n">
-        <v>2.38701486587524</v>
+        <v>2.38701462745667</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>3.70499992370605</v>
       </c>
       <c r="G841" t="n">
-        <v>2.39997005462646</v>
+        <v>2.39997029304504</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G844" t="n">
-        <v>2.4679856300354</v>
+        <v>2.46798539161682</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G845" t="n">
-        <v>2.49389624595642</v>
+        <v>2.49389600753784</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>3.83500003814697</v>
       </c>
       <c r="G846" t="n">
-        <v>2.48417997360229</v>
+        <v>2.48417973518372</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G848" t="n">
-        <v>2.74367237091064</v>
+        <v>2.74367260932922</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>3.49499988555908</v>
       </c>
       <c r="G849" t="n">
-        <v>2.48423171043396</v>
+        <v>2.48423194885254</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G850" t="n">
-        <v>2.48067808151245</v>
+        <v>2.48067784309387</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G860" t="n">
-        <v>2.50910973548889</v>
+        <v>2.50910949707031</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G861" t="n">
-        <v>2.53043365478516</v>
+        <v>2.53043341636658</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G862" t="n">
-        <v>2.52687954902649</v>
+        <v>2.52687978744507</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G863" t="n">
-        <v>2.58018946647644</v>
+        <v>2.58018970489502</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G865" t="n">
-        <v>2.5908510684967</v>
+        <v>2.59085130691528</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>3.61500000953674</v>
       </c>
       <c r="G867" t="n">
-        <v>2.56952738761902</v>
+        <v>2.5695276260376</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G868" t="n">
-        <v>2.5908510684967</v>
+        <v>2.59085130691528</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G872" t="n">
-        <v>2.59440541267395</v>
+        <v>2.59440517425537</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G874" t="n">
-        <v>2.58018946647644</v>
+        <v>2.58018970489502</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G876" t="n">
-        <v>2.5908510684967</v>
+        <v>2.59085130691528</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G878" t="n">
-        <v>2.59440541267395</v>
+        <v>2.59440517425537</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G879" t="n">
-        <v>2.5908510684967</v>
+        <v>2.59085130691528</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G881" t="n">
-        <v>2.65126895904541</v>
+        <v>2.65126919746399</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G882" t="n">
-        <v>2.67970085144043</v>
+        <v>2.67970061302185</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G886" t="n">
-        <v>2.68680834770203</v>
+        <v>2.68680858612061</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G888" t="n">
-        <v>2.68680834770203</v>
+        <v>2.68680858612061</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>3.83500003814697</v>
       </c>
       <c r="G890" t="n">
-        <v>2.72590255737305</v>
+        <v>2.72590279579163</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>3.91499996185303</v>
       </c>
       <c r="G892" t="n">
-        <v>2.78276610374451</v>
+        <v>2.78276634216309</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>3.92499995231628</v>
       </c>
       <c r="G895" t="n">
-        <v>2.78987431526184</v>
+        <v>2.78987407684326</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G903" t="n">
-        <v>2.94980335235596</v>
+        <v>2.94980359077454</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G904" t="n">
-        <v>2.96401929855347</v>
+        <v>2.96401906013489</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G909" t="n">
-        <v>2.96401929855347</v>
+        <v>2.96401906013489</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>4.15500020980835</v>
       </c>
       <c r="G912" t="n">
-        <v>2.95335745811462</v>
+        <v>2.95335721969604</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>4.00500011444092</v>
       </c>
       <c r="G915" t="n">
-        <v>2.8467378616333</v>
+        <v>2.84673762321472</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G918" t="n">
-        <v>2.76499676704407</v>
+        <v>2.76499652862549</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G919" t="n">
-        <v>2.76499676704407</v>
+        <v>2.76499652862549</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>3.91499996185303</v>
       </c>
       <c r="G921" t="n">
-        <v>2.78276610374451</v>
+        <v>2.78276634216309</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>4.10500001907349</v>
       </c>
       <c r="G923" t="n">
-        <v>2.91781735420227</v>
+        <v>2.91781759262085</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G924" t="n">
-        <v>2.9142632484436</v>
+        <v>2.91426301002502</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G926" t="n">
-        <v>2.86806178092957</v>
+        <v>2.86806154251099</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>4.0149998664856</v>
       </c>
       <c r="G927" t="n">
-        <v>2.85384583473206</v>
+        <v>2.85384559631348</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>3.93499994277954</v>
       </c>
       <c r="G932" t="n">
-        <v>2.79698204994202</v>
+        <v>2.79698181152344</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G933" t="n">
-        <v>2.8005359172821</v>
+        <v>2.80053615570068</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>3.95499992370605</v>
       </c>
       <c r="G935" t="n">
-        <v>2.81119799613953</v>
+        <v>2.81119823455811</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G936" t="n">
-        <v>2.76499676704407</v>
+        <v>2.76499652862549</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G937" t="n">
-        <v>2.70457863807678</v>
+        <v>2.70457887649536</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G938" t="n">
-        <v>2.65126895904541</v>
+        <v>2.65126919746399</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G940" t="n">
-        <v>2.66193056106567</v>
+        <v>2.66193079948425</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G941" t="n">
-        <v>2.69747066497803</v>
+        <v>2.69747090339661</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>3.83500003814697</v>
       </c>
       <c r="G944" t="n">
-        <v>2.72590255737305</v>
+        <v>2.72590279579163</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G945" t="n">
-        <v>2.71879458427429</v>
+        <v>2.71879482269287</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G946" t="n">
-        <v>2.74367237091064</v>
+        <v>2.74367260932922</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G947" t="n">
-        <v>2.72234845161438</v>
+        <v>2.7223482131958</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G950" t="n">
-        <v>2.75078010559082</v>
+        <v>2.7507803440094</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>3.88499999046326</v>
       </c>
       <c r="G952" t="n">
-        <v>2.76144242286682</v>
+        <v>2.76144218444824</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G956" t="n">
-        <v>2.74722623825073</v>
+        <v>2.74722647666931</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G957" t="n">
-        <v>2.74367237091064</v>
+        <v>2.74367260932922</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G959" t="n">
-        <v>2.72234845161438</v>
+        <v>2.7223482131958</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G960" t="n">
-        <v>2.71879458427429</v>
+        <v>2.71879482269287</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G961" t="n">
-        <v>2.72234845161438</v>
+        <v>2.7223482131958</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>3.83500003814697</v>
       </c>
       <c r="G962" t="n">
-        <v>2.72590255737305</v>
+        <v>2.72590279579163</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G973" t="n">
-        <v>2.66193056106567</v>
+        <v>2.66193079948425</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G975" t="n">
-        <v>2.62283730506897</v>
+        <v>2.62283754348755</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G976" t="n">
-        <v>2.65126895904541</v>
+        <v>2.65126919746399</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>3.83500003814697</v>
       </c>
       <c r="G978" t="n">
-        <v>2.72590255737305</v>
+        <v>2.72590279579163</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G979" t="n">
-        <v>2.71879458427429</v>
+        <v>2.71879482269287</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G981" t="n">
-        <v>2.70457863807678</v>
+        <v>2.70457887649536</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G982" t="n">
-        <v>2.72234845161438</v>
+        <v>2.7223482131958</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>3.96499991416931</v>
       </c>
       <c r="G987" t="n">
-        <v>2.81830596923828</v>
+        <v>2.8183057308197</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G988" t="n">
-        <v>2.8005359172821</v>
+        <v>2.80053615570068</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>3.88499999046326</v>
       </c>
       <c r="G991" t="n">
-        <v>2.76144242286682</v>
+        <v>2.76144218444824</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G993" t="n">
-        <v>2.72234845161438</v>
+        <v>2.7223482131958</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>3.92499995231628</v>
       </c>
       <c r="G994" t="n">
-        <v>2.78987431526184</v>
+        <v>2.78987407684326</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>3.95499992370605</v>
       </c>
       <c r="G995" t="n">
-        <v>2.81119799613953</v>
+        <v>2.81119823455811</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G997" t="n">
-        <v>2.86806178092957</v>
+        <v>2.86806154251099</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>3.88499999046326</v>
       </c>
       <c r="G998" t="n">
-        <v>2.76144242286682</v>
+        <v>2.76144218444824</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G999" t="n">
-        <v>2.74011826515198</v>
+        <v>2.74011850357056</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>3.88499999046326</v>
       </c>
       <c r="G1000" t="n">
-        <v>2.76144242286682</v>
+        <v>2.76144218444824</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>3.88499999046326</v>
       </c>
       <c r="G1001" t="n">
-        <v>2.76144242286682</v>
+        <v>2.76144218444824</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1007" t="n">
-        <v>2.64416122436523</v>
+        <v>2.64416098594666</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G1008" t="n">
-        <v>2.67614698410034</v>
+        <v>2.67614722251892</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1014" t="n">
-        <v>2.72234845161438</v>
+        <v>2.7223482131958</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G1016" t="n">
-        <v>2.70457863807678</v>
+        <v>2.70457887649536</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G1017" t="n">
-        <v>2.70457863807678</v>
+        <v>2.70457887649536</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G1018" t="n">
-        <v>2.70457863807678</v>
+        <v>2.70457887649536</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G1020" t="n">
-        <v>2.70457863807678</v>
+        <v>2.70457887649536</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1022" t="n">
-        <v>2.75078010559082</v>
+        <v>2.7507803440094</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1023" t="n">
-        <v>2.74367237091064</v>
+        <v>2.74367260932922</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1027" t="n">
-        <v>2.8005359172821</v>
+        <v>2.80053615570068</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>3.96499991416931</v>
       </c>
       <c r="G1030" t="n">
-        <v>2.81830596923828</v>
+        <v>2.8183057308197</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1033" t="n">
-        <v>2.8005359172821</v>
+        <v>2.80053615570068</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1037" t="n">
-        <v>3.14171814918518</v>
+        <v>3.14171862602234</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G1038" t="n">
-        <v>3.2163519859314</v>
+        <v>3.21635174751282</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G1039" t="n">
-        <v>3.15948843955994</v>
+        <v>3.15948820114136</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>4.49499988555908</v>
       </c>
       <c r="G1041" t="n">
-        <v>3.19502806663513</v>
+        <v>3.19502782821655</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>4.57499980926514</v>
       </c>
       <c r="G1042" t="n">
-        <v>3.25189161300659</v>
+        <v>3.25189137458801</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1046" t="n">
-        <v>3.07774615287781</v>
+        <v>3.07774639129639</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1049" t="n">
-        <v>3.14171814918518</v>
+        <v>3.14171862602234</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>4.40500020980835</v>
       </c>
       <c r="G1051" t="n">
-        <v>3.13105630874634</v>
+        <v>3.13105607032776</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G1053" t="n">
-        <v>2.98178935050964</v>
+        <v>2.98178911209106</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>4.10500001907349</v>
       </c>
       <c r="G1054" t="n">
-        <v>2.91781735420227</v>
+        <v>2.91781759262085</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>4.09499979019165</v>
       </c>
       <c r="G1056" t="n">
-        <v>2.91070938110352</v>
+        <v>2.91070961952209</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>4.09499979019165</v>
       </c>
       <c r="G1059" t="n">
-        <v>2.91070938110352</v>
+        <v>2.91070961952209</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G1067" t="n">
-        <v>2.14304971694946</v>
+        <v>2.14304995536804</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1069" t="n">
-        <v>2.26033091545105</v>
+        <v>2.26033115386963</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>3.25500011444092</v>
       </c>
       <c r="G1071" t="n">
-        <v>2.313640832901</v>
+        <v>2.31364107131958</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1073" t="n">
-        <v>2.3598427772522</v>
+        <v>2.35984253883362</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1074" t="n">
-        <v>2.38827443122864</v>
+        <v>2.38827466964722</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G1075" t="n">
-        <v>2.3420729637146</v>
+        <v>2.34207272529602</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1077" t="n">
-        <v>2.26033091545105</v>
+        <v>2.26033115386963</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1078" t="n">
-        <v>2.28165483474731</v>
+        <v>2.28165507316589</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>3.36500000953674</v>
       </c>
       <c r="G1079" t="n">
-        <v>2.3918285369873</v>
+        <v>2.39182829856873</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G1080" t="n">
-        <v>2.2638852596283</v>
+        <v>2.26388502120972</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G1086" t="n">
-        <v>2.27810096740723</v>
+        <v>2.27810120582581</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G1087" t="n">
-        <v>2.3420729637146</v>
+        <v>2.34207272529602</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1093" t="n">
-        <v>2.28876304626465</v>
+        <v>2.28876328468323</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1094" t="n">
-        <v>2.3314106464386</v>
+        <v>2.33141040802002</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1095" t="n">
-        <v>2.3314106464386</v>
+        <v>2.33141040802002</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1096" t="n">
-        <v>2.34562683105469</v>
+        <v>2.34562706947327</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>3.36500000953674</v>
       </c>
       <c r="G1098" t="n">
-        <v>2.3918285369873</v>
+        <v>2.39182829856873</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1099" t="n">
-        <v>2.36695075035095</v>
+        <v>2.36695051193237</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1100" t="n">
-        <v>2.3598427772522</v>
+        <v>2.35984253883362</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1101" t="n">
-        <v>2.3314106464386</v>
+        <v>2.33141040802002</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G1102" t="n">
-        <v>2.3420729637146</v>
+        <v>2.34207272529602</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1104" t="n">
-        <v>2.34562683105469</v>
+        <v>2.34562706947327</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1105" t="n">
-        <v>2.3314106464386</v>
+        <v>2.33141040802002</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G1107" t="n">
-        <v>2.3420729637146</v>
+        <v>2.34207272529602</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1108" t="n">
-        <v>2.34562683105469</v>
+        <v>2.34562706947327</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G1110" t="n">
-        <v>2.37761235237122</v>
+        <v>2.37761259078979</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1114" t="n">
-        <v>2.46646213531494</v>
+        <v>2.46646189689636</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G1115" t="n">
-        <v>2.64771485328674</v>
+        <v>2.64771509170532</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>3.95499992370605</v>
       </c>
       <c r="G1118" t="n">
-        <v>2.81119799613953</v>
+        <v>2.81119823455811</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1120" t="n">
-        <v>2.9142632484436</v>
+        <v>2.91426301002502</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1121" t="n">
-        <v>2.94980335235596</v>
+        <v>2.94980359077454</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>4.25500011444092</v>
       </c>
       <c r="G1125" t="n">
-        <v>3.17926263809204</v>
+        <v>3.17926239967346</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1131" t="n">
-        <v>2.94389986991882</v>
+        <v>2.9439001083374</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>3.875</v>
       </c>
       <c r="G1132" t="n">
-        <v>2.89533305168152</v>
+        <v>2.89533281326294</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>3.875</v>
       </c>
       <c r="G1136" t="n">
-        <v>2.89533305168152</v>
+        <v>2.89533281326294</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G1143" t="n">
-        <v>2.82808661460876</v>
+        <v>2.82808685302734</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1154" t="n">
-        <v>2.60019588470459</v>
+        <v>2.60019612312317</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1159" t="n">
-        <v>2.54042148590088</v>
+        <v>2.5404212474823</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1161" t="n">
-        <v>2.48811864852905</v>
+        <v>2.48811841011047</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1163" t="n">
-        <v>2.45823121070862</v>
+        <v>2.4582314491272</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G1164" t="n">
-        <v>2.47691082954407</v>
+        <v>2.47691059112549</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G1165" t="n">
-        <v>2.47691082954407</v>
+        <v>2.47691059112549</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G1166" t="n">
-        <v>2.47691082954407</v>
+        <v>2.47691059112549</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1167" t="n">
-        <v>2.54042148590088</v>
+        <v>2.5404212474823</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1168" t="n">
-        <v>2.48811864852905</v>
+        <v>2.48811841011047</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1169" t="n">
-        <v>2.48811864852905</v>
+        <v>2.48811841011047</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1171" t="n">
-        <v>2.56283664703369</v>
+        <v>2.56283688545227</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1173" t="n">
-        <v>2.59272432327271</v>
+        <v>2.59272408485413</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1180" t="n">
-        <v>2.48811864852905</v>
+        <v>2.48811841011047</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1181" t="n">
-        <v>2.45823121070862</v>
+        <v>2.4582314491272</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1182" t="n">
-        <v>2.45075917243958</v>
+        <v>2.450758934021</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1183" t="n">
-        <v>2.45075917243958</v>
+        <v>2.450758934021</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1184" t="n">
-        <v>2.45823121070862</v>
+        <v>2.4582314491272</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>3.36500000953674</v>
       </c>
       <c r="G1187" t="n">
-        <v>2.51427006721497</v>
+        <v>2.51426982879639</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1194" t="n">
-        <v>2.48811864852905</v>
+        <v>2.48811841011047</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>3.36500000953674</v>
       </c>
       <c r="G1196" t="n">
-        <v>2.51427006721497</v>
+        <v>2.51426982879639</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1200" t="n">
-        <v>2.45823121070862</v>
+        <v>2.4582314491272</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1201" t="n">
-        <v>2.39845657348633</v>
+        <v>2.39845633506775</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G1207" t="n">
-        <v>2.37977743148804</v>
+        <v>2.37977719306946</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G1211" t="n">
-        <v>2.39472055435181</v>
+        <v>2.39472079277039</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1214" t="n">
-        <v>2.39845657348633</v>
+        <v>2.39845633506775</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G1216" t="n">
-        <v>2.3424174785614</v>
+        <v>2.34241771697998</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G1225" t="n">
-        <v>2.23781204223633</v>
+        <v>2.23781228065491</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>3.04500007629395</v>
       </c>
       <c r="G1226" t="n">
-        <v>2.27517175674438</v>
+        <v>2.27517151832581</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1227" t="n">
-        <v>2.18177366256714</v>
+        <v>2.18177342414856</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>2.97499990463257</v>
       </c>
       <c r="G1229" t="n">
-        <v>2.22286868095398</v>
+        <v>2.2228684425354</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1233" t="n">
-        <v>2.21913242340088</v>
+        <v>2.21913266181946</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1236" t="n">
-        <v>2.39845657348633</v>
+        <v>2.39845633506775</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1239" t="n">
-        <v>2.48811864852905</v>
+        <v>2.48811841011047</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1240" t="n">
-        <v>2.54042148590088</v>
+        <v>2.5404212474823</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1245" t="n">
-        <v>2.61887574195862</v>
+        <v>2.61887550354004</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1252" t="n">
-        <v>2.60019588470459</v>
+        <v>2.60019612312317</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1253" t="n">
-        <v>2.59272432327271</v>
+        <v>2.59272408485413</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G1259" t="n">
-        <v>2.56657290458679</v>
+        <v>2.56657266616821</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1265" t="n">
-        <v>2.60019588470459</v>
+        <v>2.60019612312317</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1279" t="n">
-        <v>2.86918139457703</v>
+        <v>2.86918115615845</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G1282" t="n">
-        <v>2.81314325332642</v>
+        <v>2.813143491745</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>3.6949999332428</v>
       </c>
       <c r="G1294" t="n">
-        <v>2.76084017753601</v>
+        <v>2.76083993911743</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G1323" t="n">
-        <v>2.8579740524292</v>
+        <v>2.85797381401062</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G1325" t="n">
-        <v>2.82808661460876</v>
+        <v>2.82808685302734</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1326" t="n">
-        <v>2.83929419517517</v>
+        <v>2.83929443359375</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G1327" t="n">
-        <v>2.81314325332642</v>
+        <v>2.813143491745</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1335" t="n">
-        <v>2.86918139457703</v>
+        <v>2.86918115615845</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1338" t="n">
-        <v>2.90654110908508</v>
+        <v>2.9065408706665</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>3.875</v>
       </c>
       <c r="G1340" t="n">
-        <v>2.89533305168152</v>
+        <v>2.89533281326294</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1345" t="n">
-        <v>2.891597032547</v>
+        <v>2.89159727096558</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>3.9449999332428</v>
       </c>
       <c r="G1348" t="n">
-        <v>2.94763588905334</v>
+        <v>2.94763565063477</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1351" t="n">
-        <v>3.03356170654297</v>
+        <v>3.03356194496155</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1354" t="n">
-        <v>3.0492730140686</v>
+        <v>3.04927277565002</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1360" t="n">
-        <v>2.93259143829346</v>
+        <v>2.93259119987488</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G1362" t="n">
-        <v>2.89758658409119</v>
+        <v>2.89758682250977</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1372" t="n">
-        <v>2.85480380058289</v>
+        <v>2.85480403900146</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1374" t="n">
-        <v>2.85480380058289</v>
+        <v>2.85480403900146</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1375" t="n">
-        <v>2.85480380058289</v>
+        <v>2.85480403900146</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G1385" t="n">
-        <v>2.92870211601257</v>
+        <v>2.92870187759399</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G1388" t="n">
-        <v>2.83535671234131</v>
+        <v>2.83535695075989</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36483,7 +36483,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G1389" t="n">
-        <v>2.84313583374023</v>
+        <v>2.84313559532166</v>
       </c>
       <c r="H1389" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G1391" t="n">
-        <v>2.78868460655212</v>
+        <v>2.78868436813354</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G1393" t="n">
-        <v>2.75756931304932</v>
+        <v>2.7575695514679</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36639,7 +36639,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G1395" t="n">
-        <v>2.76534819602966</v>
+        <v>2.76534795761108</v>
       </c>
       <c r="H1395" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1396" t="n">
-        <v>2.76145887374878</v>
+        <v>2.7614586353302</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1398" t="n">
-        <v>2.76145887374878</v>
+        <v>2.7614586353302</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G1399" t="n">
-        <v>2.76534819602966</v>
+        <v>2.76534795761108</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G1401" t="n">
-        <v>2.76534819602966</v>
+        <v>2.76534795761108</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G1404" t="n">
-        <v>2.77312684059143</v>
+        <v>2.77312707901001</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36899,7 +36899,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1405" t="n">
-        <v>2.79257392883301</v>
+        <v>2.79257369041443</v>
       </c>
       <c r="H1405" t="s">
         <v>8</v>
@@ -36925,7 +36925,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G1406" t="n">
-        <v>2.76534819602966</v>
+        <v>2.76534795761108</v>
       </c>
       <c r="H1406" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G1408" t="n">
-        <v>2.71089696884155</v>
+        <v>2.71089673042297</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G1423" t="n">
-        <v>2.78090572357178</v>
+        <v>2.78090596199036</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37419,7 +37419,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G1425" t="n">
-        <v>2.84313583374023</v>
+        <v>2.84313559532166</v>
       </c>
       <c r="H1425" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1426" t="n">
-        <v>2.84702515602112</v>
+        <v>2.84702491760254</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37497,7 +37497,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1428" t="n">
-        <v>2.84702515602112</v>
+        <v>2.84702491760254</v>
       </c>
       <c r="H1428" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G1430" t="n">
-        <v>2.83535671234131</v>
+        <v>2.83535695075989</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G1435" t="n">
-        <v>2.78868460655212</v>
+        <v>2.78868436813354</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1436" t="n">
-        <v>2.76145887374878</v>
+        <v>2.7614586353302</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G1437" t="n">
-        <v>2.77312684059143</v>
+        <v>2.77312707901001</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1439" t="n">
-        <v>2.77701592445374</v>
+        <v>2.77701616287231</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G1440" t="n">
-        <v>2.78090572357178</v>
+        <v>2.78090596199036</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1445" t="n">
-        <v>2.76145887374878</v>
+        <v>2.7614586353302</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1447" t="n">
-        <v>2.76145887374878</v>
+        <v>2.7614586353302</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G1449" t="n">
-        <v>2.75756931304932</v>
+        <v>2.7575695514679</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1450" t="n">
-        <v>2.78479480743408</v>
+        <v>2.78479504585266</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38433,7 +38433,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G1464" t="n">
-        <v>2.6720027923584</v>
+        <v>2.67200303077698</v>
       </c>
       <c r="H1464" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1474" t="n">
-        <v>2.70700764656067</v>
+        <v>2.70700740814209</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1475" t="n">
-        <v>2.70700764656067</v>
+        <v>2.70700740814209</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38771,7 +38771,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1477" t="n">
-        <v>2.78479480743408</v>
+        <v>2.78479504585266</v>
       </c>
       <c r="H1477" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1478" t="n">
-        <v>2.79257392883301</v>
+        <v>2.79257369041443</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1482" t="n">
-        <v>2.76923751831055</v>
+        <v>2.76923727989197</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1486" t="n">
-        <v>2.77701592445374</v>
+        <v>2.77701616287231</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39109,7 +39109,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1490" t="n">
-        <v>2.76923751831055</v>
+        <v>2.76923727989197</v>
       </c>
       <c r="H1490" t="s">
         <v>8</v>
@@ -39135,7 +39135,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1491" t="n">
-        <v>2.76145887374878</v>
+        <v>2.7614586353302</v>
       </c>
       <c r="H1491" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G1493" t="n">
-        <v>2.75756931304932</v>
+        <v>2.7575695514679</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G1494" t="n">
-        <v>2.75756931304932</v>
+        <v>2.7575695514679</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G1505" t="n">
-        <v>2.6720027923584</v>
+        <v>2.67200303077698</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G1506" t="n">
-        <v>2.6720027923584</v>
+        <v>2.67200303077698</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39629,7 +39629,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1510" t="n">
-        <v>2.70700764656067</v>
+        <v>2.70700740814209</v>
       </c>
       <c r="H1510" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1515" t="n">
-        <v>2.78479480743408</v>
+        <v>2.78479504585266</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1516" t="n">
-        <v>2.69922852516174</v>
+        <v>2.69922876358032</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39811,7 +39811,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G1517" t="n">
-        <v>2.6720027923584</v>
+        <v>2.67200303077698</v>
       </c>
       <c r="H1517" t="s">
         <v>8</v>
@@ -39837,7 +39837,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1518" t="n">
-        <v>2.65255618095398</v>
+        <v>2.65255641937256</v>
       </c>
       <c r="H1518" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1519" t="n">
-        <v>2.65255618095398</v>
+        <v>2.65255641937256</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1522" t="n">
-        <v>2.65255618095398</v>
+        <v>2.65255641937256</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1525" t="n">
-        <v>2.70700764656067</v>
+        <v>2.70700740814209</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40045,7 +40045,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1526" t="n">
-        <v>2.69922852516174</v>
+        <v>2.69922876358032</v>
       </c>
       <c r="H1526" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1528" t="n">
-        <v>2.76145887374878</v>
+        <v>2.7614586353302</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -40149,7 +40149,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1530" t="n">
-        <v>2.70700764656067</v>
+        <v>2.70700740814209</v>
       </c>
       <c r="H1530" t="s">
         <v>8</v>
@@ -40331,7 +40331,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G1537" t="n">
-        <v>2.75756931304932</v>
+        <v>2.7575695514679</v>
       </c>
       <c r="H1537" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1540" t="n">
-        <v>2.76145887374878</v>
+        <v>2.7614586353302</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G1542" t="n">
-        <v>2.69533920288086</v>
+        <v>2.69533944129944</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1543" t="n">
-        <v>2.69922852516174</v>
+        <v>2.69922876358032</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40513,7 +40513,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1544" t="n">
-        <v>2.70700764656067</v>
+        <v>2.70700740814209</v>
       </c>
       <c r="H1544" t="s">
         <v>8</v>
@@ -40565,7 +40565,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G1546" t="n">
-        <v>2.75756931304932</v>
+        <v>2.7575695514679</v>
       </c>
       <c r="H1546" t="s">
         <v>8</v>
@@ -40617,7 +40617,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1548" t="n">
-        <v>2.78479480743408</v>
+        <v>2.78479504585266</v>
       </c>
       <c r="H1548" t="s">
         <v>8</v>
@@ -40669,7 +40669,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G1550" t="n">
-        <v>2.78868460655212</v>
+        <v>2.78868436813354</v>
       </c>
       <c r="H1550" t="s">
         <v>8</v>
@@ -40773,7 +40773,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1554" t="n">
-        <v>2.69922852516174</v>
+        <v>2.69922876358032</v>
       </c>
       <c r="H1554" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1558" t="n">
-        <v>2.70700764656067</v>
+        <v>2.70700740814209</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G1559" t="n">
-        <v>2.69533920288086</v>
+        <v>2.69533944129944</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -41345,7 +41345,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G1576" t="n">
-        <v>2.69533920288086</v>
+        <v>2.69533944129944</v>
       </c>
       <c r="H1576" t="s">
         <v>8</v>
@@ -41605,7 +41605,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G1586" t="n">
-        <v>2.60199427604675</v>
+        <v>2.60199403762817</v>
       </c>
       <c r="H1586" t="s">
         <v>8</v>
@@ -41631,7 +41631,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1587" t="n">
-        <v>2.65255618095398</v>
+        <v>2.65255641937256</v>
       </c>
       <c r="H1587" t="s">
         <v>8</v>
@@ -41657,7 +41657,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1588" t="n">
-        <v>2.69922852516174</v>
+        <v>2.69922876358032</v>
       </c>
       <c r="H1588" t="s">
         <v>8</v>
@@ -41839,7 +41839,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G1595" t="n">
-        <v>2.71089696884155</v>
+        <v>2.71089673042297</v>
       </c>
       <c r="H1595" t="s">
         <v>8</v>
@@ -41891,7 +41891,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G1597" t="n">
-        <v>2.76534819602966</v>
+        <v>2.76534795761108</v>
       </c>
       <c r="H1597" t="s">
         <v>8</v>
@@ -41917,7 +41917,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G1598" t="n">
-        <v>2.75756931304932</v>
+        <v>2.7575695514679</v>
       </c>
       <c r="H1598" t="s">
         <v>8</v>
@@ -42021,7 +42021,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G1602" t="n">
-        <v>2.75756931304932</v>
+        <v>2.7575695514679</v>
       </c>
       <c r="H1602" t="s">
         <v>8</v>
@@ -42047,7 +42047,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1603" t="n">
-        <v>2.77701592445374</v>
+        <v>2.77701616287231</v>
       </c>
       <c r="H1603" t="s">
         <v>8</v>
@@ -42073,7 +42073,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1604" t="n">
-        <v>2.77701592445374</v>
+        <v>2.77701616287231</v>
       </c>
       <c r="H1604" t="s">
         <v>8</v>
@@ -42151,7 +42151,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1607" t="n">
-        <v>2.70700764656067</v>
+        <v>2.70700740814209</v>
       </c>
       <c r="H1607" t="s">
         <v>8</v>
@@ -42385,7 +42385,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G1616" t="n">
-        <v>2.68953156471252</v>
+        <v>2.68953132629395</v>
       </c>
       <c r="H1616" t="s">
         <v>8</v>
@@ -42567,7 +42567,7 @@
         <v>3.25500011444092</v>
       </c>
       <c r="G1623" t="n">
-        <v>2.65688157081604</v>
+        <v>2.65688180923462</v>
       </c>
       <c r="H1623" t="s">
         <v>8</v>
@@ -42619,7 +42619,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G1625" t="n">
-        <v>2.68953156471252</v>
+        <v>2.68953132629395</v>
       </c>
       <c r="H1625" t="s">
         <v>8</v>
@@ -42827,7 +42827,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1633" t="n">
-        <v>2.75891256332397</v>
+        <v>2.7589123249054</v>
       </c>
       <c r="H1633" t="s">
         <v>8</v>
@@ -42957,7 +42957,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G1638" t="n">
-        <v>2.68953156471252</v>
+        <v>2.68953132629395</v>
       </c>
       <c r="H1638" t="s">
         <v>8</v>
@@ -43139,7 +43139,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1645" t="n">
-        <v>2.51403856277466</v>
+        <v>2.51403832435608</v>
       </c>
       <c r="H1645" t="s">
         <v>8</v>
@@ -43243,7 +43243,7 @@
         <v>3</v>
       </c>
       <c r="G1649" t="n">
-        <v>2.44873881340027</v>
+        <v>2.44873905181885</v>
       </c>
       <c r="H1649" t="s">
         <v>8</v>
@@ -43295,7 +43295,7 @@
         <v>3</v>
       </c>
       <c r="G1651" t="n">
-        <v>2.44873881340027</v>
+        <v>2.44873905181885</v>
       </c>
       <c r="H1651" t="s">
         <v>8</v>
@@ -43425,7 +43425,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1656" t="n">
-        <v>2.30181455612183</v>
+        <v>2.30181431770325</v>
       </c>
       <c r="H1656" t="s">
         <v>8</v>
@@ -43581,7 +43581,7 @@
         <v>2.74499988555908</v>
       </c>
       <c r="G1662" t="n">
-        <v>2.2405960559845</v>
+        <v>2.24059581756592</v>
       </c>
       <c r="H1662" t="s">
         <v>8</v>
@@ -43737,7 +43737,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1668" t="n">
-        <v>2.15489029884338</v>
+        <v>2.1548900604248</v>
       </c>
       <c r="H1668" t="s">
         <v>8</v>
@@ -43789,7 +43789,7 @@
         <v>2.75</v>
       </c>
       <c r="G1670" t="n">
-        <v>2.24467754364014</v>
+        <v>2.24467730522156</v>
       </c>
       <c r="H1670" t="s">
         <v>8</v>
@@ -43867,7 +43867,7 @@
         <v>2.73499989509583</v>
       </c>
       <c r="G1673" t="n">
-        <v>2.2324333190918</v>
+        <v>2.23243355751038</v>
       </c>
       <c r="H1673" t="s">
         <v>8</v>
@@ -43919,7 +43919,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G1675" t="n">
-        <v>2.31405806541443</v>
+        <v>2.31405830383301</v>
       </c>
       <c r="H1675" t="s">
         <v>8</v>
@@ -43971,7 +43971,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G1677" t="n">
-        <v>2.31405806541443</v>
+        <v>2.31405830383301</v>
       </c>
       <c r="H1677" t="s">
         <v>8</v>
@@ -44101,7 +44101,7 @@
         <v>2.75</v>
       </c>
       <c r="G1682" t="n">
-        <v>2.24467754364014</v>
+        <v>2.24467730522156</v>
       </c>
       <c r="H1682" t="s">
         <v>8</v>
@@ -44127,7 +44127,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1683" t="n">
-        <v>2.21202731132507</v>
+        <v>2.21202707290649</v>
       </c>
       <c r="H1683" t="s">
         <v>8</v>
@@ -44205,7 +44205,7 @@
         <v>2.73499989509583</v>
       </c>
       <c r="G1686" t="n">
-        <v>2.2324333190918</v>
+        <v>2.23243355751038</v>
       </c>
       <c r="H1686" t="s">
         <v>8</v>
@@ -44309,7 +44309,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1690" t="n">
-        <v>2.21202731132507</v>
+        <v>2.21202707290649</v>
       </c>
       <c r="H1690" t="s">
         <v>8</v>
@@ -44647,7 +44647,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1703" t="n">
-        <v>2.0161280632019</v>
+        <v>2.01612830162048</v>
       </c>
       <c r="H1703" t="s">
         <v>8</v>
@@ -44699,7 +44699,7 @@
         <v>2.50500011444092</v>
       </c>
       <c r="G1705" t="n">
-        <v>2.04469704627991</v>
+        <v>2.04469680786133</v>
       </c>
       <c r="H1705" t="s">
         <v>8</v>
@@ -44725,7 +44725,7 @@
         <v>2.52500009536743</v>
       </c>
       <c r="G1706" t="n">
-        <v>2.06102180480957</v>
+        <v>2.06102204322815</v>
       </c>
       <c r="H1706" t="s">
         <v>8</v>
@@ -44907,7 +44907,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1713" t="n">
-        <v>1.78757929801941</v>
+        <v>1.7875794172287</v>
       </c>
       <c r="H1713" t="s">
         <v>8</v>
@@ -44933,7 +44933,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1714" t="n">
-        <v>1.84471642971039</v>
+        <v>1.84471666812897</v>
       </c>
       <c r="H1714" t="s">
         <v>8</v>
@@ -44985,7 +44985,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1716" t="n">
-        <v>1.78757929801941</v>
+        <v>1.7875794172287</v>
       </c>
       <c r="H1716" t="s">
         <v>8</v>
@@ -45011,7 +45011,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1717" t="n">
-        <v>1.76309192180634</v>
+        <v>1.76309204101562</v>
       </c>
       <c r="H1717" t="s">
         <v>8</v>
@@ -45089,7 +45089,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1720" t="n">
-        <v>1.76309192180634</v>
+        <v>1.76309204101562</v>
       </c>
       <c r="H1720" t="s">
         <v>8</v>
@@ -45245,7 +45245,7 @@
         <v>1.91199994087219</v>
       </c>
       <c r="G1726" t="n">
-        <v>1.56066286563873</v>
+        <v>1.56066274642944</v>
       </c>
       <c r="H1726" t="s">
         <v>8</v>
@@ -45271,7 +45271,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1727" t="n">
-        <v>1.54270541667938</v>
+        <v>1.54270553588867</v>
       </c>
       <c r="H1727" t="s">
         <v>8</v>
@@ -45323,7 +45323,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1729" t="n">
-        <v>1.64065504074097</v>
+        <v>1.64065492153168</v>
       </c>
       <c r="H1729" t="s">
         <v>8</v>
@@ -45375,7 +45375,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1731" t="n">
-        <v>1.82839167118073</v>
+        <v>1.82839155197144</v>
       </c>
       <c r="H1731" t="s">
         <v>8</v>
@@ -45401,7 +45401,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G1732" t="n">
-        <v>1.75084829330444</v>
+        <v>1.75084817409515</v>
       </c>
       <c r="H1732" t="s">
         <v>8</v>
@@ -45453,7 +45453,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1734" t="n">
-        <v>1.76309192180634</v>
+        <v>1.76309204101562</v>
       </c>
       <c r="H1734" t="s">
         <v>8</v>
@@ -45531,7 +45531,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1737" t="n">
-        <v>1.87736630439758</v>
+        <v>1.87736654281616</v>
       </c>
       <c r="H1737" t="s">
         <v>8</v>
@@ -45609,7 +45609,7 @@
         <v>2.38499999046326</v>
       </c>
       <c r="G1740" t="n">
-        <v>1.94674742221832</v>
+        <v>1.94674718379974</v>
       </c>
       <c r="H1740" t="s">
         <v>8</v>
@@ -45635,7 +45635,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1741" t="n">
-        <v>1.86104154586792</v>
+        <v>1.86104142665863</v>
       </c>
       <c r="H1741" t="s">
         <v>8</v>
@@ -45843,7 +45843,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G1749" t="n">
-        <v>2.07326579093933</v>
+        <v>2.07326555252075</v>
       </c>
       <c r="H1749" t="s">
         <v>8</v>
@@ -46051,7 +46051,7 @@
         <v>2.54500007629395</v>
       </c>
       <c r="G1757" t="n">
-        <v>2.07734680175781</v>
+        <v>2.07734656333923</v>
       </c>
       <c r="H1757" t="s">
         <v>8</v>
@@ -46155,7 +46155,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1761" t="n">
-        <v>2.0161280632019</v>
+        <v>2.01612830162048</v>
       </c>
       <c r="H1761" t="s">
         <v>8</v>
@@ -46181,7 +46181,7 @@
         <v>2.50500011444092</v>
       </c>
       <c r="G1762" t="n">
-        <v>2.04469704627991</v>
+        <v>2.04469680786133</v>
       </c>
       <c r="H1762" t="s">
         <v>8</v>
@@ -46207,7 +46207,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1763" t="n">
-        <v>2.08959031105042</v>
+        <v>2.08959054946899</v>
       </c>
       <c r="H1763" t="s">
         <v>8</v>
@@ -46285,7 +46285,7 @@
         <v>2.54500007629395</v>
       </c>
       <c r="G1766" t="n">
-        <v>2.07734680175781</v>
+        <v>2.07734656333923</v>
       </c>
       <c r="H1766" t="s">
         <v>8</v>
@@ -46311,7 +46311,7 @@
         <v>2.50500011444092</v>
       </c>
       <c r="G1767" t="n">
-        <v>2.04469704627991</v>
+        <v>2.04469680786133</v>
       </c>
       <c r="H1767" t="s">
         <v>8</v>
@@ -46675,7 +46675,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1781" t="n">
-        <v>1.9916410446167</v>
+        <v>1.99164092540741</v>
       </c>
       <c r="H1781" t="s">
         <v>8</v>
@@ -47013,7 +47013,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1794" t="n">
-        <v>2.21202731132507</v>
+        <v>2.21202707290649</v>
       </c>
       <c r="H1794" t="s">
         <v>8</v>
@@ -47039,7 +47039,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G1795" t="n">
-        <v>2.18345904350281</v>
+        <v>2.18345880508423</v>
       </c>
       <c r="H1795" t="s">
         <v>8</v>
@@ -47065,7 +47065,7 @@
         <v>2.60500001907349</v>
       </c>
       <c r="G1796" t="n">
-        <v>2.12632155418396</v>
+        <v>2.12632131576538</v>
       </c>
       <c r="H1796" t="s">
         <v>8</v>
@@ -47325,7 +47325,7 @@
         <v>2.70499992370605</v>
       </c>
       <c r="G1806" t="n">
-        <v>2.20794606208801</v>
+        <v>2.20794630050659</v>
       </c>
       <c r="H1806" t="s">
         <v>8</v>
@@ -47351,7 +47351,7 @@
         <v>2.63499999046326</v>
       </c>
       <c r="G1807" t="n">
-        <v>2.15080881118774</v>
+        <v>2.15080904960632</v>
       </c>
       <c r="H1807" t="s">
         <v>8</v>
@@ -47585,7 +47585,7 @@
         <v>2.75</v>
       </c>
       <c r="G1816" t="n">
-        <v>2.24467754364014</v>
+        <v>2.24467730522156</v>
       </c>
       <c r="H1816" t="s">
         <v>8</v>
@@ -47637,7 +47637,7 @@
         <v>2.71499991416931</v>
       </c>
       <c r="G1818" t="n">
-        <v>2.21610856056213</v>
+        <v>2.21610832214355</v>
       </c>
       <c r="H1818" t="s">
         <v>8</v>
@@ -47715,7 +47715,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1821" t="n">
-        <v>2.14672756195068</v>
+        <v>2.14672780036926</v>
       </c>
       <c r="H1821" t="s">
         <v>8</v>
@@ -47741,7 +47741,7 @@
         <v>2.66499996185303</v>
       </c>
       <c r="G1822" t="n">
-        <v>2.17529630661011</v>
+        <v>2.17529654502869</v>
       </c>
       <c r="H1822" t="s">
         <v>8</v>
@@ -47793,7 +47793,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1824" t="n">
-        <v>2.21202731132507</v>
+        <v>2.21202707290649</v>
       </c>
       <c r="H1824" t="s">
         <v>8</v>
@@ -47949,7 +47949,7 @@
         <v>2.71499991416931</v>
       </c>
       <c r="G1830" t="n">
-        <v>2.21610856056213</v>
+        <v>2.21610832214355</v>
       </c>
       <c r="H1830" t="s">
         <v>8</v>
@@ -48001,7 +48001,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1832" t="n">
-        <v>2.14672756195068</v>
+        <v>2.14672780036926</v>
       </c>
       <c r="H1832" t="s">
         <v>8</v>
@@ -48027,7 +48027,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1833" t="n">
-        <v>2.08959031105042</v>
+        <v>2.08959054946899</v>
       </c>
       <c r="H1833" t="s">
         <v>8</v>
@@ -48131,7 +48131,7 @@
         <v>2.54500007629395</v>
       </c>
       <c r="G1837" t="n">
-        <v>2.07734680175781</v>
+        <v>2.07734656333923</v>
       </c>
       <c r="H1837" t="s">
         <v>8</v>
@@ -48157,7 +48157,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1838" t="n">
-        <v>2.15489029884338</v>
+        <v>2.1548900604248</v>
       </c>
       <c r="H1838" t="s">
         <v>8</v>
@@ -48209,7 +48209,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G1840" t="n">
-        <v>2.15897154808044</v>
+        <v>2.15897130966187</v>
       </c>
       <c r="H1840" t="s">
         <v>8</v>
@@ -48235,7 +48235,7 @@
         <v>2.63499999046326</v>
       </c>
       <c r="G1841" t="n">
-        <v>2.15080881118774</v>
+        <v>2.15080904960632</v>
       </c>
       <c r="H1841" t="s">
         <v>8</v>
@@ -48443,7 +48443,7 @@
         <v>2.70499992370605</v>
       </c>
       <c r="G1849" t="n">
-        <v>2.20794606208801</v>
+        <v>2.20794630050659</v>
       </c>
       <c r="H1849" t="s">
         <v>8</v>
@@ -48521,7 +48521,7 @@
         <v>2.73499989509583</v>
       </c>
       <c r="G1852" t="n">
-        <v>2.2324333190918</v>
+        <v>2.23243355751038</v>
       </c>
       <c r="H1852" t="s">
         <v>8</v>
@@ -48703,7 +48703,7 @@
         <v>2.75</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.24467754364014</v>
+        <v>2.24467730522156</v>
       </c>
       <c r="H1859" t="s">
         <v>8</v>
@@ -48859,7 +48859,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.37527680397034</v>
+        <v>2.37527656555176</v>
       </c>
       <c r="H1865" t="s">
         <v>8</v>
@@ -48911,7 +48911,7 @@
         <v>2.63499999046326</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.2513861656189</v>
+        <v>2.25138640403748</v>
       </c>
       <c r="H1867" t="s">
         <v>8</v>
@@ -48937,7 +48937,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.24711418151855</v>
+        <v>2.24711441993713</v>
       </c>
       <c r="H1868" t="s">
         <v>8</v>
@@ -48989,7 +48989,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.31546759605408</v>
+        <v>2.3154673576355</v>
       </c>
       <c r="H1870" t="s">
         <v>8</v>
@@ -49015,7 +49015,7 @@
         <v>2.71499991416931</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.31973958015442</v>
+        <v>2.31973934173584</v>
       </c>
       <c r="H1871" t="s">
         <v>8</v>
@@ -49041,7 +49041,7 @@
         <v>2.71499991416931</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.31973958015442</v>
+        <v>2.31973934173584</v>
       </c>
       <c r="H1872" t="s">
         <v>8</v>
@@ -49067,7 +49067,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.31546759605408</v>
+        <v>2.3154673576355</v>
       </c>
       <c r="H1873" t="s">
         <v>8</v>
@@ -49093,7 +49093,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.31546759605408</v>
+        <v>2.3154673576355</v>
       </c>
       <c r="H1874" t="s">
         <v>8</v>
@@ -49119,7 +49119,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.33255577087402</v>
+        <v>2.3325560092926</v>
       </c>
       <c r="H1875" t="s">
         <v>8</v>
@@ -49197,7 +49197,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.18730497360229</v>
+        <v>2.18730521202087</v>
       </c>
       <c r="H1878" t="s">
         <v>8</v>
@@ -49691,7 +49691,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.08477544784546</v>
+        <v>2.08477520942688</v>
       </c>
       <c r="H1897" t="s">
         <v>8</v>
@@ -49821,7 +49821,7 @@
         <v>2.38499999046326</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.0377824306488</v>
+        <v>2.03778219223022</v>
       </c>
       <c r="H1902" t="s">
         <v>8</v>
@@ -49951,7 +49951,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.02496600151062</v>
+        <v>2.0249662399292</v>
       </c>
       <c r="H1907" t="s">
         <v>8</v>
@@ -49977,7 +49977,7 @@
         <v>2.36500000953674</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.02069401741028</v>
+        <v>2.02069425582886</v>
       </c>
       <c r="H1908" t="s">
         <v>8</v>
@@ -50055,7 +50055,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.02496600151062</v>
+        <v>2.0249662399292</v>
       </c>
       <c r="H1911" t="s">
         <v>8</v>
@@ -50107,7 +50107,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.9480687379837</v>
+        <v>1.94806861877441</v>
       </c>
       <c r="H1913" t="s">
         <v>8</v>
@@ -50159,7 +50159,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.9480687379837</v>
+        <v>1.94806861877441</v>
       </c>
       <c r="H1915" t="s">
         <v>8</v>
@@ -50185,7 +50185,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.94379687309265</v>
+        <v>1.94379663467407</v>
       </c>
       <c r="H1916" t="s">
         <v>8</v>
@@ -50211,7 +50211,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.94379687309265</v>
+        <v>1.94379663467407</v>
       </c>
       <c r="H1917" t="s">
         <v>8</v>
@@ -50263,7 +50263,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.96515691280365</v>
+        <v>1.96515715122223</v>
       </c>
       <c r="H1919" t="s">
         <v>8</v>
@@ -50289,7 +50289,7 @@
         <v>2.26500010490417</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.93525242805481</v>
+        <v>1.93525266647339</v>
       </c>
       <c r="H1920" t="s">
         <v>8</v>
@@ -50445,7 +50445,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1926" t="n">
-        <v>1.96515691280365</v>
+        <v>1.96515715122223</v>
       </c>
       <c r="H1926" t="s">
         <v>8</v>
@@ -50497,7 +50497,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1928" t="n">
-        <v>1.97370135784149</v>
+        <v>1.97370111942291</v>
       </c>
       <c r="H1928" t="s">
         <v>8</v>
@@ -50523,7 +50523,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1929" t="n">
-        <v>1.97370135784149</v>
+        <v>1.97370111942291</v>
       </c>
       <c r="H1929" t="s">
         <v>8</v>
@@ -50575,7 +50575,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G1931" t="n">
-        <v>1.94379687309265</v>
+        <v>1.94379663467407</v>
       </c>
       <c r="H1931" t="s">
         <v>8</v>
@@ -50601,7 +50601,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1932" t="n">
-        <v>1.91389203071594</v>
+        <v>1.91389191150665</v>
       </c>
       <c r="H1932" t="s">
         <v>8</v>
@@ -50627,7 +50627,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G1933" t="n">
-        <v>1.87544322013855</v>
+        <v>1.87544333934784</v>
       </c>
       <c r="H1933" t="s">
         <v>8</v>
@@ -50705,7 +50705,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G1936" t="n">
-        <v>1.8327225446701</v>
+        <v>1.83272242546082</v>
       </c>
       <c r="H1936" t="s">
         <v>8</v>
@@ -50783,7 +50783,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1939" t="n">
-        <v>1.84553873538971</v>
+        <v>1.845538854599</v>
       </c>
       <c r="H1939" t="s">
         <v>8</v>
@@ -50809,7 +50809,7 @@
         <v>2.15499997138977</v>
       </c>
       <c r="G1940" t="n">
-        <v>1.84126663208008</v>
+        <v>1.84126675128937</v>
       </c>
       <c r="H1940" t="s">
         <v>8</v>
@@ -50835,7 +50835,7 @@
         <v>2.125</v>
       </c>
       <c r="G1941" t="n">
-        <v>1.81563401222229</v>
+        <v>1.81563425064087</v>
       </c>
       <c r="H1941" t="s">
         <v>8</v>
@@ -50887,7 +50887,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1943" t="n">
-        <v>1.82845056056976</v>
+        <v>1.82845044136047</v>
       </c>
       <c r="H1943" t="s">
         <v>8</v>
@@ -50939,7 +50939,7 @@
         <v>2.125</v>
       </c>
       <c r="G1945" t="n">
-        <v>1.81563401222229</v>
+        <v>1.81563425064087</v>
       </c>
       <c r="H1945" t="s">
         <v>8</v>
@@ -50991,7 +50991,7 @@
         <v>2.125</v>
       </c>
       <c r="G1947" t="n">
-        <v>1.81563401222229</v>
+        <v>1.81563425064087</v>
       </c>
       <c r="H1947" t="s">
         <v>8</v>
@@ -51017,7 +51017,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1948" t="n">
-        <v>1.84553873538971</v>
+        <v>1.845538854599</v>
       </c>
       <c r="H1948" t="s">
         <v>8</v>
@@ -51121,7 +51121,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1952" t="n">
-        <v>1.84553873538971</v>
+        <v>1.845538854599</v>
       </c>
       <c r="H1952" t="s">
         <v>8</v>
@@ -51199,7 +51199,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1955" t="n">
-        <v>1.85408306121826</v>
+        <v>1.85408282279968</v>
       </c>
       <c r="H1955" t="s">
         <v>8</v>
@@ -51225,7 +51225,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G1956" t="n">
-        <v>1.82417833805084</v>
+        <v>1.82417821884155</v>
       </c>
       <c r="H1956" t="s">
         <v>8</v>
@@ -51251,7 +51251,7 @@
         <v>2.125</v>
       </c>
       <c r="G1957" t="n">
-        <v>1.81563401222229</v>
+        <v>1.81563425064087</v>
       </c>
       <c r="H1957" t="s">
         <v>8</v>
@@ -51277,7 +51277,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G1958" t="n">
-        <v>1.8327225446701</v>
+        <v>1.83272242546082</v>
       </c>
       <c r="H1958" t="s">
         <v>8</v>
@@ -51303,7 +51303,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1959" t="n">
-        <v>1.84553873538971</v>
+        <v>1.845538854599</v>
       </c>
       <c r="H1959" t="s">
         <v>8</v>
@@ -51329,7 +51329,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G1960" t="n">
-        <v>1.82417833805084</v>
+        <v>1.82417821884155</v>
       </c>
       <c r="H1960" t="s">
         <v>8</v>
@@ -51381,7 +51381,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G1962" t="n">
-        <v>1.8327225446701</v>
+        <v>1.83272242546082</v>
       </c>
       <c r="H1962" t="s">
         <v>8</v>
@@ -51407,7 +51407,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1963" t="n">
-        <v>1.84553873538971</v>
+        <v>1.845538854599</v>
       </c>
       <c r="H1963" t="s">
         <v>8</v>
@@ -51433,7 +51433,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G1964" t="n">
-        <v>1.8327225446701</v>
+        <v>1.83272242546082</v>
       </c>
       <c r="H1964" t="s">
         <v>8</v>
@@ -51459,7 +51459,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G1965" t="n">
-        <v>1.8327225446701</v>
+        <v>1.83272242546082</v>
       </c>
       <c r="H1965" t="s">
         <v>8</v>
@@ -51485,7 +51485,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G1966" t="n">
-        <v>1.8327225446701</v>
+        <v>1.83272242546082</v>
       </c>
       <c r="H1966" t="s">
         <v>8</v>
@@ -51511,7 +51511,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1967" t="n">
-        <v>1.79427373409271</v>
+        <v>1.794273853302</v>
       </c>
       <c r="H1967" t="s">
         <v>8</v>
@@ -51563,7 +51563,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G1969" t="n">
-        <v>1.74728083610535</v>
+        <v>1.74728095531464</v>
       </c>
       <c r="H1969" t="s">
         <v>8</v>
@@ -51589,7 +51589,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1970" t="n">
-        <v>1.72592043876648</v>
+        <v>1.72592055797577</v>
       </c>
       <c r="H1970" t="s">
         <v>8</v>
@@ -51641,7 +51641,7 @@
         <v>1.96599996089935</v>
       </c>
       <c r="G1972" t="n">
-        <v>1.67978191375732</v>
+        <v>1.67978203296661</v>
       </c>
       <c r="H1972" t="s">
         <v>8</v>
@@ -51849,7 +51849,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1980" t="n">
-        <v>1.71737635135651</v>
+        <v>1.71737623214722</v>
       </c>
       <c r="H1980" t="s">
         <v>8</v>
@@ -51901,7 +51901,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1982" t="n">
-        <v>1.71737635135651</v>
+        <v>1.71737623214722</v>
       </c>
       <c r="H1982" t="s">
         <v>8</v>
@@ -51927,7 +51927,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G1983" t="n">
-        <v>1.74728083610535</v>
+        <v>1.74728095531464</v>
       </c>
       <c r="H1983" t="s">
         <v>8</v>
@@ -51953,7 +51953,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G1984" t="n">
-        <v>1.72164857387543</v>
+        <v>1.72164845466614</v>
       </c>
       <c r="H1984" t="s">
         <v>8</v>
@@ -52005,7 +52005,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1986" t="n">
-        <v>1.72592043876648</v>
+        <v>1.72592055797577</v>
       </c>
       <c r="H1986" t="s">
         <v>8</v>
@@ -52057,7 +52057,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1988" t="n">
-        <v>1.71737635135651</v>
+        <v>1.71737623214722</v>
       </c>
       <c r="H1988" t="s">
         <v>8</v>
@@ -52239,7 +52239,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1995" t="n">
-        <v>1.79427373409271</v>
+        <v>1.794273853302</v>
       </c>
       <c r="H1995" t="s">
         <v>8</v>
@@ -52265,7 +52265,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1996" t="n">
-        <v>1.79427373409271</v>
+        <v>1.794273853302</v>
       </c>
       <c r="H1996" t="s">
         <v>8</v>
@@ -52291,7 +52291,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1997" t="n">
-        <v>1.87117123603821</v>
+        <v>1.8711713552475</v>
       </c>
       <c r="H1997" t="s">
         <v>8</v>
@@ -52343,7 +52343,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1999" t="n">
-        <v>1.84553873538971</v>
+        <v>1.845538854599</v>
       </c>
       <c r="H1999" t="s">
         <v>8</v>
@@ -52369,7 +52369,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G2000" t="n">
-        <v>1.84553873538971</v>
+        <v>1.845538854599</v>
       </c>
       <c r="H2000" t="s">
         <v>8</v>
@@ -52395,7 +52395,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G2001" t="n">
-        <v>1.84553873538971</v>
+        <v>1.845538854599</v>
       </c>
       <c r="H2001" t="s">
         <v>8</v>
@@ -52421,7 +52421,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G2002" t="n">
-        <v>1.87117123603821</v>
+        <v>1.8711713552475</v>
       </c>
       <c r="H2002" t="s">
         <v>8</v>
@@ -52447,7 +52447,7 @@
         <v>2.125</v>
       </c>
       <c r="G2003" t="n">
-        <v>1.81563401222229</v>
+        <v>1.81563425064087</v>
       </c>
       <c r="H2003" t="s">
         <v>8</v>
@@ -52499,7 +52499,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G2005" t="n">
-        <v>1.85408306121826</v>
+        <v>1.85408282279968</v>
       </c>
       <c r="H2005" t="s">
         <v>8</v>
@@ -52525,7 +52525,7 @@
         <v>2.15499997138977</v>
       </c>
       <c r="G2006" t="n">
-        <v>1.84126663208008</v>
+        <v>1.84126675128937</v>
       </c>
       <c r="H2006" t="s">
         <v>8</v>
@@ -52551,7 +52551,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G2007" t="n">
-        <v>1.84553873538971</v>
+        <v>1.845538854599</v>
       </c>
       <c r="H2007" t="s">
         <v>8</v>
@@ -52577,7 +52577,7 @@
         <v>2.20499992370605</v>
       </c>
       <c r="G2008" t="n">
-        <v>1.88398742675781</v>
+        <v>1.88398730754852</v>
       </c>
       <c r="H2008" t="s">
         <v>8</v>
@@ -52655,7 +52655,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G2011" t="n">
-        <v>1.85408306121826</v>
+        <v>1.85408282279968</v>
       </c>
       <c r="H2011" t="s">
         <v>8</v>
@@ -52733,7 +52733,7 @@
         <v>2.23499989509583</v>
       </c>
       <c r="G2014" t="n">
-        <v>1.90961968898773</v>
+        <v>1.90961992740631</v>
       </c>
       <c r="H2014" t="s">
         <v>8</v>
@@ -52759,7 +52759,7 @@
         <v>2.26500010490417</v>
       </c>
       <c r="G2015" t="n">
-        <v>1.93525242805481</v>
+        <v>1.93525266647339</v>
       </c>
       <c r="H2015" t="s">
         <v>8</v>
@@ -52785,7 +52785,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G2016" t="n">
-        <v>1.93098020553589</v>
+        <v>1.93098044395447</v>
       </c>
       <c r="H2016" t="s">
         <v>8</v>
@@ -52811,7 +52811,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G2017" t="n">
-        <v>1.93098020553589</v>
+        <v>1.93098044395447</v>
       </c>
       <c r="H2017" t="s">
         <v>8</v>
@@ -52837,7 +52837,7 @@
         <v>2.26500010490417</v>
       </c>
       <c r="G2018" t="n">
-        <v>1.93525242805481</v>
+        <v>1.93525266647339</v>
       </c>
       <c r="H2018" t="s">
         <v>8</v>
@@ -52993,7 +52993,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G2024" t="n">
-        <v>1.96515691280365</v>
+        <v>1.96515715122223</v>
       </c>
       <c r="H2024" t="s">
         <v>8</v>
@@ -53045,7 +53045,7 @@
         <v>2.26500010490417</v>
       </c>
       <c r="G2026" t="n">
-        <v>1.93525242805481</v>
+        <v>1.93525266647339</v>
       </c>
       <c r="H2026" t="s">
         <v>8</v>
@@ -53097,7 +53097,7 @@
         <v>2.26500010490417</v>
       </c>
       <c r="G2028" t="n">
-        <v>1.93525242805481</v>
+        <v>1.93525266647339</v>
       </c>
       <c r="H2028" t="s">
         <v>8</v>
@@ -53123,7 +53123,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G2029" t="n">
-        <v>1.91389203071594</v>
+        <v>1.91389191150665</v>
       </c>
       <c r="H2029" t="s">
         <v>8</v>
@@ -53175,7 +53175,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G2031" t="n">
-        <v>1.9480687379837</v>
+        <v>1.94806861877441</v>
       </c>
       <c r="H2031" t="s">
         <v>8</v>
@@ -53201,7 +53201,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G2032" t="n">
-        <v>1.91389203071594</v>
+        <v>1.91389191150665</v>
       </c>
       <c r="H2032" t="s">
         <v>8</v>
@@ -53227,7 +53227,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G2033" t="n">
-        <v>1.93098020553589</v>
+        <v>1.93098044395447</v>
       </c>
       <c r="H2033" t="s">
         <v>8</v>
@@ -53253,7 +53253,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G2034" t="n">
-        <v>1.93098020553589</v>
+        <v>1.93098044395447</v>
       </c>
       <c r="H2034" t="s">
         <v>8</v>
@@ -53279,7 +53279,7 @@
         <v>2.26500010490417</v>
       </c>
       <c r="G2035" t="n">
-        <v>1.93525242805481</v>
+        <v>1.93525266647339</v>
       </c>
       <c r="H2035" t="s">
         <v>8</v>
@@ -53357,7 +53357,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G2038" t="n">
-        <v>1.91389203071594</v>
+        <v>1.91389191150665</v>
       </c>
       <c r="H2038" t="s">
         <v>8</v>
@@ -53383,7 +53383,7 @@
         <v>2.23499989509583</v>
       </c>
       <c r="G2039" t="n">
-        <v>1.90961968898773</v>
+        <v>1.90961992740631</v>
       </c>
       <c r="H2039" t="s">
         <v>8</v>
@@ -53409,7 +53409,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G2040" t="n">
-        <v>1.93098020553589</v>
+        <v>1.93098044395447</v>
       </c>
       <c r="H2040" t="s">
         <v>8</v>
@@ -53435,7 +53435,7 @@
         <v>2.26500010490417</v>
       </c>
       <c r="G2041" t="n">
-        <v>1.93525242805481</v>
+        <v>1.93525266647339</v>
       </c>
       <c r="H2041" t="s">
         <v>8</v>
@@ -53461,7 +53461,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G2042" t="n">
-        <v>1.94379687309265</v>
+        <v>1.94379663467407</v>
       </c>
       <c r="H2042" t="s">
         <v>8</v>
@@ -53487,7 +53487,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G2043" t="n">
-        <v>1.93098020553589</v>
+        <v>1.93098044395447</v>
       </c>
       <c r="H2043" t="s">
         <v>8</v>
@@ -53669,7 +53669,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G2050" t="n">
-        <v>1.87117123603821</v>
+        <v>1.8711713552475</v>
       </c>
       <c r="H2050" t="s">
         <v>8</v>
@@ -53773,7 +53773,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G2054" t="n">
-        <v>1.91389203071594</v>
+        <v>1.91389191150665</v>
       </c>
       <c r="H2054" t="s">
         <v>8</v>
@@ -53825,7 +53825,7 @@
         <v>2.20499992370605</v>
       </c>
       <c r="G2056" t="n">
-        <v>1.88398742675781</v>
+        <v>1.88398730754852</v>
       </c>
       <c r="H2056" t="s">
         <v>8</v>
@@ -53903,7 +53903,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G2059" t="n">
-        <v>1.91389203071594</v>
+        <v>1.91389191150665</v>
       </c>
       <c r="H2059" t="s">
         <v>8</v>
@@ -53955,7 +53955,7 @@
         <v>2.23499989509583</v>
       </c>
       <c r="G2061" t="n">
-        <v>1.90961968898773</v>
+        <v>1.90961992740631</v>
       </c>
       <c r="H2061" t="s">
         <v>8</v>
@@ -54007,7 +54007,7 @@
         <v>2.20499992370605</v>
       </c>
       <c r="G2063" t="n">
-        <v>1.88398742675781</v>
+        <v>1.88398730754852</v>
       </c>
       <c r="H2063" t="s">
         <v>8</v>
@@ -54033,7 +54033,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G2064" t="n">
-        <v>1.87544322013855</v>
+        <v>1.87544333934784</v>
       </c>
       <c r="H2064" t="s">
         <v>8</v>
@@ -54059,7 +54059,7 @@
         <v>2.20499992370605</v>
       </c>
       <c r="G2065" t="n">
-        <v>1.88398742675781</v>
+        <v>1.88398730754852</v>
       </c>
       <c r="H2065" t="s">
         <v>8</v>
@@ -54137,7 +54137,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G2068" t="n">
-        <v>1.91389203071594</v>
+        <v>1.91389191150665</v>
       </c>
       <c r="H2068" t="s">
         <v>8</v>
@@ -54371,7 +54371,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G2077" t="n">
-        <v>1.9480687379837</v>
+        <v>1.94806861877441</v>
       </c>
       <c r="H2077" t="s">
         <v>8</v>
@@ -54397,7 +54397,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G2078" t="n">
-        <v>1.93098020553589</v>
+        <v>1.93098044395447</v>
       </c>
       <c r="H2078" t="s">
         <v>8</v>
@@ -54423,7 +54423,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G2079" t="n">
-        <v>1.96515691280365</v>
+        <v>1.96515715122223</v>
       </c>
       <c r="H2079" t="s">
         <v>8</v>
@@ -54449,7 +54449,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G2080" t="n">
-        <v>1.97370135784149</v>
+        <v>1.97370111942291</v>
       </c>
       <c r="H2080" t="s">
         <v>8</v>
@@ -54735,7 +54735,7 @@
         <v>2.38499999046326</v>
       </c>
       <c r="G2091" t="n">
-        <v>2.0377824306488</v>
+        <v>2.03778219223022</v>
       </c>
       <c r="H2091" t="s">
         <v>8</v>
@@ -54813,7 +54813,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G2094" t="n">
-        <v>1.96515691280365</v>
+        <v>1.96515715122223</v>
       </c>
       <c r="H2094" t="s">
         <v>8</v>
@@ -54839,7 +54839,7 @@
         <v>2.36500000953674</v>
       </c>
       <c r="G2095" t="n">
-        <v>2.02069401741028</v>
+        <v>2.02069425582886</v>
       </c>
       <c r="H2095" t="s">
         <v>8</v>
@@ -54891,7 +54891,7 @@
         <v>2.36500000953674</v>
       </c>
       <c r="G2097" t="n">
-        <v>2.02069401741028</v>
+        <v>2.02069425582886</v>
       </c>
       <c r="H2097" t="s">
         <v>8</v>
@@ -54917,7 +54917,7 @@
         <v>2.38499999046326</v>
       </c>
       <c r="G2098" t="n">
-        <v>2.0377824306488</v>
+        <v>2.03778219223022</v>
       </c>
       <c r="H2098" t="s">
         <v>8</v>
@@ -54943,7 +54943,7 @@
         <v>2.36500000953674</v>
       </c>
       <c r="G2099" t="n">
-        <v>2.02069401741028</v>
+        <v>2.02069425582886</v>
       </c>
       <c r="H2099" t="s">
         <v>8</v>
@@ -55229,7 +55229,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G2110" t="n">
-        <v>1.97370135784149</v>
+        <v>1.97370111942291</v>
       </c>
       <c r="H2110" t="s">
         <v>8</v>
@@ -55463,7 +55463,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G2119" t="n">
-        <v>2.11040759086609</v>
+        <v>2.11040782928467</v>
       </c>
       <c r="H2119" t="s">
         <v>8</v>
@@ -55567,7 +55567,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G2123" t="n">
-        <v>2.08503580093384</v>
+        <v>2.08503603935242</v>
       </c>
       <c r="H2123" t="s">
         <v>8</v>
@@ -55593,7 +55593,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G2124" t="n">
-        <v>2.06690526008606</v>
+        <v>2.06690502166748</v>
       </c>
       <c r="H2124" t="s">
         <v>8</v>
@@ -55619,7 +55619,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G2125" t="n">
-        <v>2.03064370155334</v>
+        <v>2.03064346313477</v>
       </c>
       <c r="H2125" t="s">
         <v>8</v>
@@ -55723,7 +55723,7 @@
         <v>2.23499989509583</v>
       </c>
       <c r="G2129" t="n">
-        <v>2.02611064910889</v>
+        <v>2.02611088752747</v>
       </c>
       <c r="H2129" t="s">
         <v>8</v>
@@ -55775,7 +55775,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G2131" t="n">
-        <v>1.98984932899475</v>
+        <v>1.98984944820404</v>
       </c>
       <c r="H2131" t="s">
         <v>8</v>
@@ -55801,7 +55801,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G2132" t="n">
-        <v>1.98531675338745</v>
+        <v>1.98531687259674</v>
       </c>
       <c r="H2132" t="s">
         <v>8</v>
@@ -55827,7 +55827,7 @@
         <v>2.20499992370605</v>
       </c>
       <c r="G2133" t="n">
-        <v>1.99891483783722</v>
+        <v>1.99891471862793</v>
       </c>
       <c r="H2133" t="s">
         <v>8</v>
@@ -55905,7 +55905,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G2136" t="n">
-        <v>1.96718621253967</v>
+        <v>1.96718597412109</v>
       </c>
       <c r="H2136" t="s">
         <v>8</v>
@@ -55957,7 +55957,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G2138" t="n">
-        <v>1.98531675338745</v>
+        <v>1.98531687259674</v>
       </c>
       <c r="H2138" t="s">
         <v>8</v>
@@ -56009,7 +56009,7 @@
         <v>2.20499992370605</v>
       </c>
       <c r="G2140" t="n">
-        <v>1.99891483783722</v>
+        <v>1.99891471862793</v>
       </c>
       <c r="H2140" t="s">
         <v>8</v>
@@ -56061,7 +56061,7 @@
         <v>2.23499989509583</v>
       </c>
       <c r="G2142" t="n">
-        <v>2.02611064910889</v>
+        <v>2.02611088752747</v>
       </c>
       <c r="H2142" t="s">
         <v>8</v>
@@ -56087,7 +56087,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G2143" t="n">
-        <v>2.04877424240112</v>
+        <v>2.0487744808197</v>
       </c>
       <c r="H2143" t="s">
         <v>8</v>
@@ -56139,7 +56139,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G2145" t="n">
-        <v>2.06237268447876</v>
+        <v>2.06237244606018</v>
       </c>
       <c r="H2145" t="s">
         <v>8</v>
@@ -56165,7 +56165,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G2146" t="n">
-        <v>2.06237268447876</v>
+        <v>2.06237244606018</v>
       </c>
       <c r="H2146" t="s">
         <v>8</v>
@@ -56217,7 +56217,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G2148" t="n">
-        <v>2.06690526008606</v>
+        <v>2.06690502166748</v>
       </c>
       <c r="H2148" t="s">
         <v>8</v>
@@ -56243,7 +56243,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G2149" t="n">
-        <v>2.03064370155334</v>
+        <v>2.03064346313477</v>
       </c>
       <c r="H2149" t="s">
         <v>8</v>
@@ -56295,7 +56295,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G2151" t="n">
-        <v>2.04877424240112</v>
+        <v>2.0487744808197</v>
       </c>
       <c r="H2151" t="s">
         <v>8</v>
@@ -56373,7 +56373,7 @@
         <v>2.23499989509583</v>
       </c>
       <c r="G2154" t="n">
-        <v>2.02611064910889</v>
+        <v>2.02611088752747</v>
       </c>
       <c r="H2154" t="s">
         <v>8</v>
@@ -56399,7 +56399,7 @@
         <v>2.23499989509583</v>
       </c>
       <c r="G2155" t="n">
-        <v>2.02611064910889</v>
+        <v>2.02611088752747</v>
       </c>
       <c r="H2155" t="s">
         <v>8</v>
@@ -56477,7 +56477,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G2158" t="n">
-        <v>2.04877424240112</v>
+        <v>2.0487744808197</v>
       </c>
       <c r="H2158" t="s">
         <v>8</v>
@@ -56529,7 +56529,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G2160" t="n">
-        <v>2.0941014289856</v>
+        <v>2.09410119056702</v>
       </c>
       <c r="H2160" t="s">
         <v>8</v>
@@ -56555,7 +56555,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G2161" t="n">
-        <v>2.04877424240112</v>
+        <v>2.0487744808197</v>
       </c>
       <c r="H2161" t="s">
         <v>8</v>
@@ -56581,7 +56581,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G2162" t="n">
-        <v>2.06237268447876</v>
+        <v>2.06237244606018</v>
       </c>
       <c r="H2162" t="s">
         <v>8</v>
@@ -56711,7 +56711,7 @@
         <v>2.38499999046326</v>
       </c>
       <c r="G2167" t="n">
-        <v>2.16209173202515</v>
+        <v>2.16209149360657</v>
       </c>
       <c r="H2167" t="s">
         <v>8</v>
@@ -56867,7 +56867,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G2173" t="n">
-        <v>2.14849328994751</v>
+        <v>2.14849352836609</v>
       </c>
       <c r="H2173" t="s">
         <v>8</v>
@@ -57257,7 +57257,7 @@
         <v>2.52500009536743</v>
       </c>
       <c r="G2188" t="n">
-        <v>2.28900671005249</v>
+        <v>2.28900694847107</v>
       </c>
       <c r="H2188" t="s">
         <v>8</v>
@@ -57283,7 +57283,7 @@
         <v>2.52500009536743</v>
       </c>
       <c r="G2189" t="n">
-        <v>2.28900671005249</v>
+        <v>2.28900694847107</v>
       </c>
       <c r="H2189" t="s">
         <v>8</v>
@@ -57335,7 +57335,7 @@
         <v>2.60500001907349</v>
       </c>
       <c r="G2191" t="n">
-        <v>2.36152982711792</v>
+        <v>2.36152958869934</v>
       </c>
       <c r="H2191" t="s">
         <v>8</v>
@@ -57413,7 +57413,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G2194" t="n">
-        <v>2.39325881004333</v>
+        <v>2.39325857162476</v>
       </c>
       <c r="H2194" t="s">
         <v>8</v>
@@ -57439,7 +57439,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G2195" t="n">
-        <v>2.42045474052429</v>
+        <v>2.42045497894287</v>
       </c>
       <c r="H2195" t="s">
         <v>8</v>
@@ -57465,7 +57465,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G2196" t="n">
-        <v>2.42498755455017</v>
+        <v>2.42498731613159</v>
       </c>
       <c r="H2196" t="s">
         <v>8</v>
@@ -57491,7 +57491,7 @@
         <v>2.70499992370605</v>
       </c>
       <c r="G2197" t="n">
-        <v>2.45218324661255</v>
+        <v>2.45218348503113</v>
       </c>
       <c r="H2197" t="s">
         <v>8</v>
@@ -57569,7 +57569,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G2200" t="n">
-        <v>2.39325881004333</v>
+        <v>2.39325857162476</v>
       </c>
       <c r="H2200" t="s">
         <v>8</v>
@@ -57595,7 +57595,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G2201" t="n">
-        <v>2.42045474052429</v>
+        <v>2.42045497894287</v>
       </c>
       <c r="H2201" t="s">
         <v>8</v>
@@ -57725,7 +57725,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G2206" t="n">
-        <v>2.45671629905701</v>
+        <v>2.45671606063843</v>
       </c>
       <c r="H2206" t="s">
         <v>8</v>
@@ -57751,7 +57751,7 @@
         <v>2.71499991416931</v>
       </c>
       <c r="G2207" t="n">
-        <v>2.46124887466431</v>
+        <v>2.46124863624573</v>
       </c>
       <c r="H2207" t="s">
         <v>8</v>
@@ -57829,7 +57829,7 @@
         <v>2.70499992370605</v>
       </c>
       <c r="G2210" t="n">
-        <v>2.45218324661255</v>
+        <v>2.45218348503113</v>
       </c>
       <c r="H2210" t="s">
         <v>8</v>
@@ -57855,7 +57855,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G2211" t="n">
-        <v>2.42045474052429</v>
+        <v>2.42045497894287</v>
       </c>
       <c r="H2211" t="s">
         <v>8</v>
@@ -57907,7 +57907,7 @@
         <v>2.75</v>
       </c>
       <c r="G2213" t="n">
-        <v>2.49297785758972</v>
+        <v>2.49297761917114</v>
       </c>
       <c r="H2213" t="s">
         <v>8</v>
@@ -58089,7 +58089,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G2220" t="n">
-        <v>2.57456588745117</v>
+        <v>2.57456612586975</v>
       </c>
       <c r="H2220" t="s">
         <v>8</v>
@@ -58193,7 +58193,7 @@
         <v>2.85500001907349</v>
       </c>
       <c r="G2224" t="n">
-        <v>2.58816432952881</v>
+        <v>2.58816409111023</v>
       </c>
       <c r="H2224" t="s">
         <v>8</v>
@@ -58323,7 +58323,7 @@
         <v>2.85500001907349</v>
       </c>
       <c r="G2229" t="n">
-        <v>2.58816432952881</v>
+        <v>2.58816409111023</v>
       </c>
       <c r="H2229" t="s">
         <v>8</v>
@@ -58739,7 +58739,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G2245" t="n">
-        <v>2.57003331184387</v>
+        <v>2.57003355026245</v>
       </c>
       <c r="H2245" t="s">
         <v>8</v>
@@ -58765,7 +58765,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G2246" t="n">
-        <v>2.55643534660339</v>
+        <v>2.55643510818481</v>
       </c>
       <c r="H2246" t="s">
         <v>8</v>
@@ -58921,7 +58921,7 @@
         <v>2.75</v>
       </c>
       <c r="G2252" t="n">
-        <v>2.49297785758972</v>
+        <v>2.49297761917114</v>
       </c>
       <c r="H2252" t="s">
         <v>8</v>
@@ -58973,7 +58973,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G2254" t="n">
-        <v>2.39325881004333</v>
+        <v>2.39325857162476</v>
       </c>
       <c r="H2254" t="s">
         <v>8</v>
@@ -59051,7 +59051,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G2257" t="n">
-        <v>2.45671629905701</v>
+        <v>2.45671606063843</v>
       </c>
       <c r="H2257" t="s">
         <v>8</v>
@@ -59077,7 +59077,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G2258" t="n">
-        <v>2.42498755455017</v>
+        <v>2.42498731613159</v>
       </c>
       <c r="H2258" t="s">
         <v>8</v>
@@ -59233,7 +59233,7 @@
         <v>2.73499989509583</v>
       </c>
       <c r="G2264" t="n">
-        <v>2.47937941551208</v>
+        <v>2.47937965393066</v>
       </c>
       <c r="H2264" t="s">
         <v>8</v>
@@ -59285,7 +59285,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G2266" t="n">
-        <v>2.57003331184387</v>
+        <v>2.57003355026245</v>
       </c>
       <c r="H2266" t="s">
         <v>8</v>
@@ -59493,7 +59493,7 @@
         <v>2.75</v>
       </c>
       <c r="G2274" t="n">
-        <v>2.49297785758972</v>
+        <v>2.49297761917114</v>
       </c>
       <c r="H2274" t="s">
         <v>8</v>
@@ -59545,7 +59545,7 @@
         <v>2.74499988555908</v>
       </c>
       <c r="G2276" t="n">
-        <v>2.48844504356384</v>
+        <v>2.48844480514526</v>
       </c>
       <c r="H2276" t="s">
         <v>8</v>
@@ -59649,7 +59649,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G2280" t="n">
-        <v>2.39779138565063</v>
+        <v>2.39779114723206</v>
       </c>
       <c r="H2280" t="s">
         <v>8</v>
@@ -59675,7 +59675,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G2281" t="n">
-        <v>2.42498755455017</v>
+        <v>2.42498731613159</v>
       </c>
       <c r="H2281" t="s">
         <v>8</v>
@@ -59701,7 +59701,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G2282" t="n">
-        <v>2.42045474052429</v>
+        <v>2.42045497894287</v>
       </c>
       <c r="H2282" t="s">
         <v>8</v>
@@ -59779,7 +59779,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G2285" t="n">
-        <v>2.39325881004333</v>
+        <v>2.39325857162476</v>
       </c>
       <c r="H2285" t="s">
         <v>8</v>
@@ -59805,7 +59805,7 @@
         <v>2.70499992370605</v>
       </c>
       <c r="G2286" t="n">
-        <v>2.45218324661255</v>
+        <v>2.45218348503113</v>
       </c>
       <c r="H2286" t="s">
         <v>8</v>
@@ -59857,7 +59857,7 @@
         <v>2.75</v>
       </c>
       <c r="G2288" t="n">
-        <v>2.49297785758972</v>
+        <v>2.49297761917114</v>
       </c>
       <c r="H2288" t="s">
         <v>8</v>
@@ -59883,7 +59883,7 @@
         <v>2.75</v>
       </c>
       <c r="G2289" t="n">
-        <v>2.49297785758972</v>
+        <v>2.49297761917114</v>
       </c>
       <c r="H2289" t="s">
         <v>8</v>
@@ -59961,7 +59961,7 @@
         <v>2.71499991416931</v>
       </c>
       <c r="G2292" t="n">
-        <v>2.46124887466431</v>
+        <v>2.46124863624573</v>
       </c>
       <c r="H2292" t="s">
         <v>8</v>
@@ -59987,7 +59987,7 @@
         <v>2.70499992370605</v>
       </c>
       <c r="G2293" t="n">
-        <v>2.45218324661255</v>
+        <v>2.45218348503113</v>
       </c>
       <c r="H2293" t="s">
         <v>8</v>
@@ -60039,7 +60039,7 @@
         <v>2.75</v>
       </c>
       <c r="G2295" t="n">
-        <v>2.49297785758972</v>
+        <v>2.49297761917114</v>
       </c>
       <c r="H2295" t="s">
         <v>8</v>
@@ -60143,7 +60143,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G2299" t="n">
-        <v>2.45671629905701</v>
+        <v>2.45671606063843</v>
       </c>
       <c r="H2299" t="s">
         <v>8</v>
@@ -60169,7 +60169,7 @@
         <v>2.74499988555908</v>
       </c>
       <c r="G2300" t="n">
-        <v>2.48844504356384</v>
+        <v>2.48844480514526</v>
       </c>
       <c r="H2300" t="s">
         <v>8</v>
@@ -60403,7 +60403,7 @@
         <v>2.73499989509583</v>
       </c>
       <c r="G2309" t="n">
-        <v>2.47937941551208</v>
+        <v>2.47937965393066</v>
       </c>
       <c r="H2309" t="s">
         <v>8</v>
@@ -60533,7 +60533,7 @@
         <v>2.83500003814697</v>
       </c>
       <c r="G2314" t="n">
-        <v>2.57003331184387</v>
+        <v>2.57003355026245</v>
       </c>
       <c r="H2314" t="s">
         <v>8</v>
@@ -60819,7 +60819,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G2325" t="n">
-        <v>2.61989283561707</v>
+        <v>2.61989307403564</v>
       </c>
       <c r="H2325" t="s">
         <v>8</v>
@@ -61157,7 +61157,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G2338" t="n">
-        <v>2.638023853302</v>
+        <v>2.63802361488342</v>
       </c>
       <c r="H2338" t="s">
         <v>8</v>
@@ -61443,7 +61443,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G2349" t="n">
-        <v>2.66521978378296</v>
+        <v>2.66522002220154</v>
       </c>
       <c r="H2349" t="s">
         <v>8</v>
@@ -61729,7 +61729,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G2360" t="n">
-        <v>2.73321032524109</v>
+        <v>2.73321008682251</v>
       </c>
       <c r="H2360" t="s">
         <v>8</v>
@@ -61833,7 +61833,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2364" t="n">
-        <v>2.91905045509338</v>
+        <v>2.9190502166748</v>
       </c>
       <c r="H2364" t="s">
         <v>8</v>
@@ -61859,7 +61859,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2365" t="n">
-        <v>2.91905045509338</v>
+        <v>2.9190502166748</v>
       </c>
       <c r="H2365" t="s">
         <v>8</v>
@@ -61937,7 +61937,7 @@
         <v>3.25500011444092</v>
       </c>
       <c r="G2368" t="n">
-        <v>2.95077896118164</v>
+        <v>2.95077919960022</v>
       </c>
       <c r="H2368" t="s">
         <v>8</v>
@@ -62015,7 +62015,7 @@
         <v>3.25500011444092</v>
       </c>
       <c r="G2371" t="n">
-        <v>2.95077896118164</v>
+        <v>2.95077919960022</v>
       </c>
       <c r="H2371" t="s">
         <v>8</v>
@@ -62041,7 +62041,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G2372" t="n">
-        <v>2.98704075813293</v>
+        <v>2.98704051971436</v>
       </c>
       <c r="H2372" t="s">
         <v>8</v>
@@ -71222,6 +71222,32 @@
         <v>2.67000007629395</v>
       </c>
       <c r="H2725" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2726">
+      <c r="A2726" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B2726" t="n">
+        <v>168539</v>
+      </c>
+      <c r="C2726" t="n">
+        <v>2.70000004768372</v>
+      </c>
+      <c r="D2726" t="n">
+        <v>2.65000009536743</v>
+      </c>
+      <c r="E2726" t="n">
+        <v>2.69000005722046</v>
+      </c>
+      <c r="F2726" t="n">
+        <v>2.70000004768372</v>
+      </c>
+      <c r="G2726" t="n">
+        <v>2.70000004768372</v>
+      </c>
+      <c r="H2726" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ASC.MI.xlsx
+++ b/data/ASC.MI.xlsx
@@ -421,7 +421,7 @@
         <v>2.21600008010864</v>
       </c>
       <c r="G2" t="n">
-        <v>1.21448886394501</v>
+        <v>1.21448874473572</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>2.21799993515015</v>
       </c>
       <c r="G3" t="n">
-        <v>1.21558487415314</v>
+        <v>1.21558475494385</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>2.19799995422363</v>
       </c>
       <c r="G4" t="n">
-        <v>1.20462357997894</v>
+        <v>1.20462346076965</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G5" t="n">
-        <v>1.20571959018707</v>
+        <v>1.20571970939636</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>2.17600011825562</v>
       </c>
       <c r="G6" t="n">
-        <v>1.1925665140152</v>
+        <v>1.19256663322449</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>2.16400003433228</v>
       </c>
       <c r="G7" t="n">
-        <v>1.18598985671997</v>
+        <v>1.18598973751068</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>2.21799993515015</v>
       </c>
       <c r="G8" t="n">
-        <v>1.21558487415314</v>
+        <v>1.21558475494385</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G9" t="n">
-        <v>1.21120047569275</v>
+        <v>1.21120023727417</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>2.16599988937378</v>
       </c>
       <c r="G10" t="n">
-        <v>1.18708598613739</v>
+        <v>1.1870858669281</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G11" t="n">
-        <v>1.17064428329468</v>
+        <v>1.17064416408539</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G12" t="n">
-        <v>1.13447272777557</v>
+        <v>1.13447260856628</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G15" t="n">
-        <v>1.12351143360138</v>
+        <v>1.12351155281067</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>2.16400003433228</v>
       </c>
       <c r="G16" t="n">
-        <v>1.18598985671997</v>
+        <v>1.18598973751068</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G17" t="n">
-        <v>1.19475877285004</v>
+        <v>1.19475865364075</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>2.17400002479553</v>
       </c>
       <c r="G18" t="n">
-        <v>1.19147062301636</v>
+        <v>1.19147026538849</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>2.16199994087219</v>
       </c>
       <c r="G19" t="n">
-        <v>1.18489372730255</v>
+        <v>1.18489360809326</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G20" t="n">
-        <v>1.19475877285004</v>
+        <v>1.19475865364075</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>2.21399998664856</v>
       </c>
       <c r="G22" t="n">
-        <v>1.21339273452759</v>
+        <v>1.21339249610901</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>2.21799993515015</v>
       </c>
       <c r="G23" t="n">
-        <v>1.21558487415314</v>
+        <v>1.21558475494385</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G24" t="n">
-        <v>1.21120047569275</v>
+        <v>1.21120023727417</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>2.16400003433228</v>
       </c>
       <c r="G26" t="n">
-        <v>1.18598985671997</v>
+        <v>1.18598973751068</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G27" t="n">
-        <v>1.1454336643219</v>
+        <v>1.14543378353119</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G28" t="n">
-        <v>1.15091407299042</v>
+        <v>1.150914311409</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>2.09800004959106</v>
       </c>
       <c r="G29" t="n">
-        <v>1.14981806278229</v>
+        <v>1.14981818199158</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>2.09400010108948</v>
       </c>
       <c r="G31" t="n">
-        <v>1.14762592315674</v>
+        <v>1.14762616157532</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>2.1340000629425</v>
       </c>
       <c r="G32" t="n">
-        <v>1.16954827308655</v>
+        <v>1.16954815387726</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G33" t="n">
-        <v>1.16735601425171</v>
+        <v>1.16735589504242</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G34" t="n">
-        <v>1.16735601425171</v>
+        <v>1.16735589504242</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G35" t="n">
-        <v>1.17283654212952</v>
+        <v>1.17283666133881</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>2.14400005340576</v>
       </c>
       <c r="G36" t="n">
-        <v>1.17502868175507</v>
+        <v>1.17502892017365</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>2.13599991798401</v>
       </c>
       <c r="G37" t="n">
-        <v>1.17064428329468</v>
+        <v>1.17064416408539</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G38" t="n">
-        <v>1.16735601425171</v>
+        <v>1.16735589504242</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G39" t="n">
-        <v>1.16735601425171</v>
+        <v>1.16735589504242</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>2.17400002479553</v>
       </c>
       <c r="G40" t="n">
-        <v>1.19147062301636</v>
+        <v>1.19147026538849</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G41" t="n">
-        <v>1.19475877285004</v>
+        <v>1.19475865364075</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G44" t="n">
-        <v>1.22216153144836</v>
+        <v>1.22216141223907</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G45" t="n">
-        <v>1.22435355186462</v>
+        <v>1.22435367107391</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G49" t="n">
-        <v>1.21120047569275</v>
+        <v>1.21120023727417</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>2.2039999961853</v>
       </c>
       <c r="G51" t="n">
-        <v>1.20791208744049</v>
+        <v>1.2079119682312</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>2.2960000038147</v>
       </c>
       <c r="G56" t="n">
-        <v>1.25833296775818</v>
+        <v>1.25833308696747</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>2.2739999294281</v>
       </c>
       <c r="G58" t="n">
-        <v>1.24627578258514</v>
+        <v>1.24627566337585</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>2.26600003242493</v>
       </c>
       <c r="G59" t="n">
-        <v>1.24189126491547</v>
+        <v>1.24189138412476</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>2.29800009727478</v>
       </c>
       <c r="G60" t="n">
-        <v>1.2594290971756</v>
+        <v>1.25942921638489</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>2.28800010681152</v>
       </c>
       <c r="G62" t="n">
-        <v>1.25394856929779</v>
+        <v>1.2539484500885</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>2.29800009727478</v>
       </c>
       <c r="G67" t="n">
-        <v>1.2594290971756</v>
+        <v>1.25942921638489</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>2.30200004577637</v>
       </c>
       <c r="G68" t="n">
-        <v>1.26162147521973</v>
+        <v>1.26162135601044</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G71" t="n">
-        <v>1.27696692943573</v>
+        <v>1.27696681022644</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>2.33400011062622</v>
       </c>
       <c r="G72" t="n">
-        <v>1.27915906906128</v>
+        <v>1.27915918827057</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G73" t="n">
-        <v>1.28244721889496</v>
+        <v>1.28244733810425</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>2.34800004959106</v>
       </c>
       <c r="G74" t="n">
-        <v>1.28683173656464</v>
+        <v>1.28683185577393</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>2.34800004959106</v>
       </c>
       <c r="G75" t="n">
-        <v>1.28683173656464</v>
+        <v>1.28683185577393</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>2.33400011062622</v>
       </c>
       <c r="G76" t="n">
-        <v>1.27915906906128</v>
+        <v>1.27915918827057</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>2.33200001716614</v>
       </c>
       <c r="G80" t="n">
-        <v>1.27806282043457</v>
+        <v>1.27806293964386</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G82" t="n">
-        <v>1.30436956882477</v>
+        <v>1.30436968803406</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>2.39199995994568</v>
       </c>
       <c r="G83" t="n">
-        <v>1.31094598770142</v>
+        <v>1.31094634532928</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>2.38800001144409</v>
       </c>
       <c r="G84" t="n">
-        <v>1.30875396728516</v>
+        <v>1.30875408649445</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G85" t="n">
-        <v>1.29888892173767</v>
+        <v>1.29888904094696</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G86" t="n">
-        <v>1.29888892173767</v>
+        <v>1.29888904094696</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>2.26399993896484</v>
       </c>
       <c r="G90" t="n">
-        <v>1.32501208782196</v>
+        <v>1.32501196861267</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>2.26600003242493</v>
       </c>
       <c r="G92" t="n">
-        <v>1.32618260383606</v>
+        <v>1.32618272304535</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G93" t="n">
-        <v>1.34022867679596</v>
+        <v>1.34022855758667</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>2.31599998474121</v>
       </c>
       <c r="G94" t="n">
-        <v>1.35544526576996</v>
+        <v>1.35544550418854</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G95" t="n">
-        <v>1.35193383693695</v>
+        <v>1.35193395614624</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>2.33200001716614</v>
       </c>
       <c r="G96" t="n">
-        <v>1.36480927467346</v>
+        <v>1.36480939388275</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>2.33200001716614</v>
       </c>
       <c r="G97" t="n">
-        <v>1.36480927467346</v>
+        <v>1.36480939388275</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>2.34400010108948</v>
       </c>
       <c r="G98" t="n">
-        <v>1.37183237075806</v>
+        <v>1.37183248996735</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>2.34599995613098</v>
       </c>
       <c r="G99" t="n">
-        <v>1.37300288677216</v>
+        <v>1.37300276756287</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>2.36199998855591</v>
       </c>
       <c r="G101" t="n">
-        <v>1.38236677646637</v>
+        <v>1.38236689567566</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>2.41599988937378</v>
       </c>
       <c r="G104" t="n">
-        <v>1.41397047042847</v>
+        <v>1.41397035121918</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>2.44199991226196</v>
       </c>
       <c r="G108" t="n">
-        <v>1.42918717861176</v>
+        <v>1.42918694019318</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G109" t="n">
-        <v>1.43972194194794</v>
+        <v>1.43972158432007</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>2.43199992179871</v>
       </c>
       <c r="G110" t="n">
-        <v>1.42333483695984</v>
+        <v>1.42333471775055</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>2.5</v>
       </c>
       <c r="G111" t="n">
-        <v>1.46313190460205</v>
+        <v>1.46313166618347</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G113" t="n">
-        <v>1.53336203098297</v>
+        <v>1.53336215019226</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>2.59200000762939</v>
       </c>
       <c r="G114" t="n">
-        <v>1.51697480678558</v>
+        <v>1.51697516441345</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>2.5</v>
       </c>
       <c r="G115" t="n">
-        <v>1.46313190460205</v>
+        <v>1.46313166618347</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>2.5</v>
       </c>
       <c r="G116" t="n">
-        <v>1.46313190460205</v>
+        <v>1.46313166618347</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>2.47399997711182</v>
       </c>
       <c r="G117" t="n">
-        <v>1.44791531562805</v>
+        <v>1.44791519641876</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>2.59800004959106</v>
       </c>
       <c r="G120" t="n">
-        <v>1.52048659324646</v>
+        <v>1.52048683166504</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G122" t="n">
-        <v>1.53336203098297</v>
+        <v>1.53336215019226</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G123" t="n">
-        <v>1.53336203098297</v>
+        <v>1.53336215019226</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G125" t="n">
-        <v>1.44557440280914</v>
+        <v>1.44557428359985</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>2.53600001335144</v>
       </c>
       <c r="G126" t="n">
-        <v>1.48420107364655</v>
+        <v>1.48420095443726</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G128" t="n">
-        <v>1.58018219470978</v>
+        <v>1.58018243312836</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G129" t="n">
-        <v>1.58018219470978</v>
+        <v>1.58018243312836</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>2.58800005912781</v>
       </c>
       <c r="G131" t="n">
-        <v>1.51463413238525</v>
+        <v>1.51463425159454</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>2.67600011825562</v>
       </c>
       <c r="G132" t="n">
-        <v>1.56613636016846</v>
+        <v>1.56613624095917</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>2.69400000572205</v>
       </c>
       <c r="G133" t="n">
-        <v>1.57667076587677</v>
+        <v>1.57667052745819</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.69600009918213</v>
       </c>
       <c r="G134" t="n">
-        <v>1.57784116268158</v>
+        <v>1.57784140110016</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>2.69400000572205</v>
       </c>
       <c r="G135" t="n">
-        <v>1.57667076587677</v>
+        <v>1.57667052745819</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G136" t="n">
-        <v>1.58018219470978</v>
+        <v>1.58018243312836</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G137" t="n">
-        <v>1.58018219470978</v>
+        <v>1.58018243312836</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G138" t="n">
-        <v>1.58018219470978</v>
+        <v>1.58018243312836</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G139" t="n">
-        <v>1.58018219470978</v>
+        <v>1.58018243312836</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G140" t="n">
-        <v>1.58018219470978</v>
+        <v>1.58018243312836</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G141" t="n">
-        <v>1.58018219470978</v>
+        <v>1.58018243312836</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>2.78600001335144</v>
       </c>
       <c r="G142" t="n">
-        <v>1.63051402568817</v>
+        <v>1.63051414489746</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>2.79399991035461</v>
       </c>
       <c r="G143" t="n">
-        <v>1.63519608974457</v>
+        <v>1.63519597053528</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>2.74200010299683</v>
       </c>
       <c r="G145" t="n">
-        <v>1.60476315021515</v>
+        <v>1.60476303100586</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G147" t="n">
-        <v>1.63870763778687</v>
+        <v>1.63870751857758</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G148" t="n">
-        <v>1.63870763778687</v>
+        <v>1.63870751857758</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G149" t="n">
-        <v>1.65041267871857</v>
+        <v>1.65041279792786</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G150" t="n">
-        <v>1.63870763778687</v>
+        <v>1.63870751857758</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G152" t="n">
-        <v>1.61529755592346</v>
+        <v>1.61529743671417</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G153" t="n">
-        <v>1.62115013599396</v>
+        <v>1.62114989757538</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>2.78800010681152</v>
       </c>
       <c r="G154" t="n">
-        <v>1.63168478012085</v>
+        <v>1.63168466091156</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>2.85400009155273</v>
       </c>
       <c r="G155" t="n">
-        <v>1.67031121253967</v>
+        <v>1.67031145095825</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G156" t="n">
-        <v>1.70308554172516</v>
+        <v>1.70308542251587</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>2.89599990844727</v>
       </c>
       <c r="G158" t="n">
-        <v>1.69489181041718</v>
+        <v>1.69489192962646</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>2.83800005912781</v>
       </c>
       <c r="G161" t="n">
-        <v>1.66094720363617</v>
+        <v>1.66094708442688</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G162" t="n">
-        <v>1.65041267871857</v>
+        <v>1.65041279792786</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>2.83400011062622</v>
       </c>
       <c r="G163" t="n">
-        <v>1.65860629081726</v>
+        <v>1.65860617160797</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>2.83800005912781</v>
       </c>
       <c r="G164" t="n">
-        <v>1.66094720363617</v>
+        <v>1.66094708442688</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G167" t="n">
-        <v>1.67382276058197</v>
+        <v>1.67382252216339</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>2.8840000629425</v>
       </c>
       <c r="G168" t="n">
-        <v>1.68786871433258</v>
+        <v>1.68786919116974</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>2.86199998855591</v>
       </c>
       <c r="G169" t="n">
-        <v>1.67499315738678</v>
+        <v>1.67499327659607</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G170" t="n">
-        <v>1.67382276058197</v>
+        <v>1.67382252216339</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>2.86199998855591</v>
       </c>
       <c r="G172" t="n">
-        <v>1.67499315738678</v>
+        <v>1.67499327659607</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G174" t="n">
-        <v>1.63870763778687</v>
+        <v>1.63870751857758</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G175" t="n">
-        <v>1.57432973384857</v>
+        <v>1.57432985305786</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>2.70799994468689</v>
       </c>
       <c r="G176" t="n">
-        <v>1.58486425876617</v>
+        <v>1.58486413955688</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>2.82800006866455</v>
       </c>
       <c r="G177" t="n">
-        <v>1.65509474277496</v>
+        <v>1.65509462356567</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>2.75</v>
       </c>
       <c r="G178" t="n">
-        <v>1.60944485664368</v>
+        <v>1.60944497585297</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>2.60400009155273</v>
       </c>
       <c r="G186" t="n">
-        <v>1.52399802207947</v>
+        <v>1.52399826049805</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>2.62400007247925</v>
       </c>
       <c r="G189" t="n">
-        <v>1.53570318222046</v>
+        <v>1.53570306301117</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>2.66599988937378</v>
       </c>
       <c r="G191" t="n">
-        <v>1.56028354167938</v>
+        <v>1.56028366088867</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>2.68400001525879</v>
       </c>
       <c r="G192" t="n">
-        <v>1.57081830501556</v>
+        <v>1.57081818580627</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G193" t="n">
-        <v>1.57432973384857</v>
+        <v>1.57432985305786</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G194" t="n">
-        <v>1.53921461105347</v>
+        <v>1.53921473026276</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G195" t="n">
-        <v>1.55091977119446</v>
+        <v>1.55092000961304</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>2.62199997901917</v>
       </c>
       <c r="G202" t="n">
-        <v>1.53453254699707</v>
+        <v>1.53453290462494</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>2.62599992752075</v>
       </c>
       <c r="G203" t="n">
-        <v>1.53687357902527</v>
+        <v>1.53687345981598</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>2.66199994087219</v>
       </c>
       <c r="G204" t="n">
-        <v>1.55794274806976</v>
+        <v>1.55794262886047</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>2.67400002479553</v>
       </c>
       <c r="G205" t="n">
-        <v>1.56496584415436</v>
+        <v>1.56496596336365</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G206" t="n">
-        <v>1.5684769153595</v>
+        <v>1.56847739219666</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G207" t="n">
-        <v>1.58018219470978</v>
+        <v>1.58018243312836</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>2.68799996376038</v>
       </c>
       <c r="G208" t="n">
-        <v>1.57315921783447</v>
+        <v>1.57315909862518</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G209" t="n">
-        <v>1.53336203098297</v>
+        <v>1.53336215019226</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>2.62599992752075</v>
       </c>
       <c r="G210" t="n">
-        <v>1.53687357902527</v>
+        <v>1.53687345981598</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G211" t="n">
-        <v>1.53336203098297</v>
+        <v>1.53336215019226</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>2.62800002098083</v>
       </c>
       <c r="G212" t="n">
-        <v>1.53804397583008</v>
+        <v>1.53804421424866</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G213" t="n">
-        <v>1.56262469291687</v>
+        <v>1.56262493133545</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>2.66400003433228</v>
       </c>
       <c r="G214" t="n">
-        <v>1.55911338329315</v>
+        <v>1.55911326408386</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G215" t="n">
-        <v>1.55091977119446</v>
+        <v>1.55092000961304</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>2.65199995040894</v>
       </c>
       <c r="G216" t="n">
-        <v>1.55209004878998</v>
+        <v>1.55209028720856</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>2.65199995040894</v>
       </c>
       <c r="G217" t="n">
-        <v>1.55209004878998</v>
+        <v>1.55209028720856</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G218" t="n">
-        <v>1.55091977119446</v>
+        <v>1.55092000961304</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G219" t="n">
-        <v>1.55091977119446</v>
+        <v>1.55092000961304</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G220" t="n">
-        <v>1.55091977119446</v>
+        <v>1.55092000961304</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G221" t="n">
-        <v>1.53921461105347</v>
+        <v>1.53921473026276</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>2.58200001716614</v>
       </c>
       <c r="G222" t="n">
-        <v>1.51112246513367</v>
+        <v>1.51112258434296</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G223" t="n">
-        <v>1.53336203098297</v>
+        <v>1.53336215019226</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>2.49200010299683</v>
       </c>
       <c r="G225" t="n">
-        <v>1.45844995975494</v>
+        <v>1.45844984054565</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>2.42400002479553</v>
       </c>
       <c r="G226" t="n">
-        <v>1.41865253448486</v>
+        <v>1.41865265369415</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>2.42600011825562</v>
       </c>
       <c r="G227" t="n">
-        <v>1.41982305049896</v>
+        <v>1.41982328891754</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>2.43400001525879</v>
       </c>
       <c r="G228" t="n">
-        <v>1.42450511455536</v>
+        <v>1.42450499534607</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>2.40599989891052</v>
       </c>
       <c r="G229" t="n">
-        <v>1.40811789035797</v>
+        <v>1.40811812877655</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G230" t="n">
-        <v>1.48068940639496</v>
+        <v>1.48068916797638</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>2.57800006866455</v>
       </c>
       <c r="G231" t="n">
-        <v>1.50878143310547</v>
+        <v>1.50878131389618</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G232" t="n">
-        <v>1.48654198646545</v>
+        <v>1.48654186725616</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G233" t="n">
-        <v>1.45727920532227</v>
+        <v>1.45727932453156</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G234" t="n">
-        <v>1.42216408252716</v>
+        <v>1.42216420173645</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>2.45799994468689</v>
       </c>
       <c r="G235" t="n">
-        <v>1.43855106830597</v>
+        <v>1.43855118751526</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G236" t="n">
-        <v>1.48654198646545</v>
+        <v>1.48654186725616</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>2.50799989700317</v>
       </c>
       <c r="G238" t="n">
-        <v>1.46781396865845</v>
+        <v>1.46781373023987</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>2.50799989700317</v>
       </c>
       <c r="G239" t="n">
-        <v>1.46781396865845</v>
+        <v>1.46781373023987</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G240" t="n">
-        <v>1.48654198646545</v>
+        <v>1.48654186725616</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G241" t="n">
-        <v>1.49239456653595</v>
+        <v>1.49239432811737</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G244" t="n">
-        <v>1.52165687084198</v>
+        <v>1.52165710926056</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>2.58599996566772</v>
       </c>
       <c r="G245" t="n">
-        <v>1.51346349716187</v>
+        <v>1.51346325874329</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>2.57599997520447</v>
       </c>
       <c r="G246" t="n">
-        <v>1.50761103630066</v>
+        <v>1.50761115550995</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>2.60400009155273</v>
       </c>
       <c r="G247" t="n">
-        <v>1.52399802207947</v>
+        <v>1.52399826049805</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>2.68799996376038</v>
       </c>
       <c r="G248" t="n">
-        <v>1.57315921783447</v>
+        <v>1.57315909862518</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>2.65599989891052</v>
       </c>
       <c r="G249" t="n">
-        <v>1.5544308423996</v>
+        <v>1.55443096160889</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>2.65199995040894</v>
       </c>
       <c r="G250" t="n">
-        <v>1.55209004878998</v>
+        <v>1.55209028720856</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>2.70199990272522</v>
       </c>
       <c r="G252" t="n">
-        <v>1.58135271072388</v>
+        <v>1.58135294914246</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>2.68600010871887</v>
       </c>
       <c r="G253" t="n">
-        <v>1.57198882102966</v>
+        <v>1.57198894023895</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G254" t="n">
-        <v>1.59188735485077</v>
+        <v>1.59188759326935</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>2.71399998664856</v>
       </c>
       <c r="G255" t="n">
-        <v>1.58837616443634</v>
+        <v>1.58837580680847</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>2.71399998664856</v>
       </c>
       <c r="G256" t="n">
-        <v>1.58837616443634</v>
+        <v>1.58837580680847</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G259" t="n">
-        <v>1.65041267871857</v>
+        <v>1.65041279792786</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>2.78600001335144</v>
       </c>
       <c r="G260" t="n">
-        <v>1.63051402568817</v>
+        <v>1.63051414489746</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>2.75</v>
       </c>
       <c r="G261" t="n">
-        <v>1.60944485664368</v>
+        <v>1.60944497585297</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>2.74399995803833</v>
       </c>
       <c r="G262" t="n">
-        <v>1.60593342781067</v>
+        <v>1.60593354701996</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G263" t="n">
-        <v>1.58603477478027</v>
+        <v>1.58603489398956</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G264" t="n">
-        <v>1.58603477478027</v>
+        <v>1.58603489398956</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>2.72199988365173</v>
       </c>
       <c r="G265" t="n">
-        <v>1.59305810928345</v>
+        <v>1.59305775165558</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G266" t="n">
-        <v>1.59188735485077</v>
+        <v>1.59188759326935</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>2.73799991607666</v>
       </c>
       <c r="G269" t="n">
-        <v>1.60242199897766</v>
+        <v>1.60242211818695</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G270" t="n">
-        <v>1.61529755592346</v>
+        <v>1.61529743671417</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>2.75</v>
       </c>
       <c r="G271" t="n">
-        <v>1.60944485664368</v>
+        <v>1.60944497585297</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G272" t="n">
-        <v>1.62115013599396</v>
+        <v>1.62114989757538</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>2.76799988746643</v>
       </c>
       <c r="G273" t="n">
-        <v>1.61997938156128</v>
+        <v>1.61997950077057</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>2.78399991989136</v>
       </c>
       <c r="G274" t="n">
-        <v>1.62934350967407</v>
+        <v>1.62934339046478</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>2.75</v>
       </c>
       <c r="G275" t="n">
-        <v>1.60944485664368</v>
+        <v>1.60944497585297</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>2.75</v>
       </c>
       <c r="G276" t="n">
-        <v>1.60944485664368</v>
+        <v>1.60944497585297</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G277" t="n">
-        <v>1.62700271606445</v>
+        <v>1.62700259685516</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>2.86400008201599</v>
       </c>
       <c r="G280" t="n">
-        <v>1.67616403102875</v>
+        <v>1.67616379261017</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>2.85199999809265</v>
       </c>
       <c r="G282" t="n">
-        <v>1.66914057731628</v>
+        <v>1.66914105415344</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>2.82599997520447</v>
       </c>
       <c r="G283" t="n">
-        <v>1.65392410755157</v>
+        <v>1.65392446517944</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>2.82800006866455</v>
       </c>
       <c r="G284" t="n">
-        <v>1.65509474277496</v>
+        <v>1.65509462356567</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>2.83800005912781</v>
       </c>
       <c r="G285" t="n">
-        <v>1.66094720363617</v>
+        <v>1.66094708442688</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>2.80800008773804</v>
       </c>
       <c r="G286" t="n">
-        <v>1.64338946342468</v>
+        <v>1.64338994026184</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G288" t="n">
-        <v>1.67382276058197</v>
+        <v>1.67382252216339</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>2.87800002098083</v>
       </c>
       <c r="G289" t="n">
-        <v>1.68435740470886</v>
+        <v>1.68435752391815</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>2.88800001144409</v>
       </c>
       <c r="G290" t="n">
-        <v>1.69020998477936</v>
+        <v>1.69020986557007</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>2.86400008201599</v>
       </c>
       <c r="G291" t="n">
-        <v>1.67616403102875</v>
+        <v>1.67616379261017</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>2.83599996566772</v>
       </c>
       <c r="G292" t="n">
-        <v>1.65977692604065</v>
+        <v>1.65977668762207</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G293" t="n">
-        <v>1.69138038158417</v>
+        <v>1.69138050079346</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G294" t="n">
-        <v>1.69138038158417</v>
+        <v>1.69138050079346</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>2.90799999237061</v>
       </c>
       <c r="G295" t="n">
-        <v>1.70191490650177</v>
+        <v>1.70191478729248</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>2.8659999370575</v>
       </c>
       <c r="G296" t="n">
-        <v>1.67733430862427</v>
+        <v>1.67733442783356</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>2.89599990844727</v>
       </c>
       <c r="G297" t="n">
-        <v>1.69489181041718</v>
+        <v>1.69489192962646</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>2.86400008201599</v>
       </c>
       <c r="G298" t="n">
-        <v>1.67616403102875</v>
+        <v>1.67616379261017</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G299" t="n">
-        <v>1.69138038158417</v>
+        <v>1.69138050079346</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G300" t="n">
-        <v>1.72649526596069</v>
+        <v>1.72649550437927</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G301" t="n">
-        <v>1.72064304351807</v>
+        <v>1.72064316272736</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G302" t="n">
-        <v>1.74405312538147</v>
+        <v>1.74405324459076</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G303" t="n">
-        <v>1.77331590652466</v>
+        <v>1.77331566810608</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>3.05599999427795</v>
       </c>
       <c r="G304" t="n">
-        <v>1.78853225708008</v>
+        <v>1.78853249549866</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>3.08200001716614</v>
       </c>
       <c r="G305" t="n">
-        <v>1.80374908447266</v>
+        <v>1.80374896526337</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>3.09599995613098</v>
       </c>
       <c r="G306" t="n">
-        <v>1.81194233894348</v>
+        <v>1.81194221973419</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G307" t="n">
-        <v>1.8084305524826</v>
+        <v>1.80843079090118</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>3.15599989891052</v>
       </c>
       <c r="G308" t="n">
-        <v>1.84705758094788</v>
+        <v>1.84705770015717</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>3.29200005531311</v>
       </c>
       <c r="G312" t="n">
-        <v>1.92665195465088</v>
+        <v>1.92665219306946</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>3.33200001716614</v>
       </c>
       <c r="G317" t="n">
-        <v>1.95006191730499</v>
+        <v>1.95006215572357</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G319" t="n">
-        <v>2.00156450271606</v>
+        <v>2.00156426429749</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G322" t="n">
-        <v>2.03082680702209</v>
+        <v>2.03082704544067</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>3.50600004196167</v>
       </c>
       <c r="G324" t="n">
-        <v>2.0518958568573</v>
+        <v>2.05189633369446</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G325" t="n">
-        <v>2.0600893497467</v>
+        <v>2.06009006500244</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>3.52600002288818</v>
       </c>
       <c r="G326" t="n">
-        <v>2.06360101699829</v>
+        <v>2.06360125541687</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>3.5220000743866</v>
       </c>
       <c r="G330" t="n">
-        <v>2.06126022338867</v>
+        <v>2.06125998497009</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>3.49799990653992</v>
       </c>
       <c r="G331" t="n">
-        <v>2.04721403121948</v>
+        <v>2.0472137928009</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>3.59400010108948</v>
       </c>
       <c r="G333" t="n">
-        <v>2.10339856147766</v>
+        <v>2.10339832305908</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>3.58599996566772</v>
       </c>
       <c r="G337" t="n">
-        <v>2.09871625900269</v>
+        <v>2.09871602058411</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>3.59400010108948</v>
       </c>
       <c r="G338" t="n">
-        <v>2.10339856147766</v>
+        <v>2.10339832305908</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>3.59200000762939</v>
       </c>
       <c r="G339" t="n">
-        <v>2.10222792625427</v>
+        <v>2.10222768783569</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>3.62199997901917</v>
       </c>
       <c r="G340" t="n">
-        <v>2.11978530883789</v>
+        <v>2.11978554725647</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>3.64599990844727</v>
       </c>
       <c r="G345" t="n">
-        <v>2.24046349525452</v>
+        <v>2.24046397209167</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>3.62599992752075</v>
       </c>
       <c r="G346" t="n">
-        <v>2.22817373275757</v>
+        <v>2.22817397117615</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>3.57800006866455</v>
       </c>
       <c r="G348" t="n">
-        <v>2.1986780166626</v>
+        <v>2.19867777824402</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>3.48600006103516</v>
       </c>
       <c r="G349" t="n">
-        <v>2.14214372634888</v>
+        <v>2.14214396476746</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>3.46199989318848</v>
       </c>
       <c r="G353" t="n">
-        <v>2.12739610671997</v>
+        <v>2.12739586830139</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>3.6340000629425</v>
       </c>
       <c r="G357" t="n">
-        <v>2.23308992385864</v>
+        <v>2.23308968544006</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G358" t="n">
-        <v>2.2490668296814</v>
+        <v>2.24906706809998</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>3.55599999427795</v>
       </c>
       <c r="G360" t="n">
-        <v>2.18515849113464</v>
+        <v>2.1851589679718</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>3.61400008201599</v>
       </c>
       <c r="G361" t="n">
-        <v>2.22080016136169</v>
+        <v>2.22079968452454</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G363" t="n">
-        <v>2.24292206764221</v>
+        <v>2.24292182922363</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>3.65799999237061</v>
       </c>
       <c r="G364" t="n">
-        <v>2.24783802032471</v>
+        <v>2.24783778190613</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G366" t="n">
-        <v>2.21219682693481</v>
+        <v>2.21219658851624</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G367" t="n">
-        <v>2.23063206672668</v>
+        <v>2.23063182830811</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G370" t="n">
-        <v>2.21219682693481</v>
+        <v>2.21219658851624</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>3.60199999809265</v>
       </c>
       <c r="G371" t="n">
-        <v>2.21342587471008</v>
+        <v>2.21342611312866</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G372" t="n">
-        <v>2.23063206672668</v>
+        <v>2.23063182830811</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>3.71799993515015</v>
       </c>
       <c r="G374" t="n">
-        <v>2.28470778465271</v>
+        <v>2.28470754623413</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G375" t="n">
-        <v>2.24292206764221</v>
+        <v>2.24292182922363</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G380" t="n">
-        <v>2.18147158622742</v>
+        <v>2.18147206306458</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>3.50799989700317</v>
       </c>
       <c r="G390" t="n">
-        <v>2.15566325187683</v>
+        <v>2.15566277503967</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>3.50399994850159</v>
       </c>
       <c r="G396" t="n">
-        <v>2.15320515632629</v>
+        <v>2.15320491790771</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>3.39599990844727</v>
       </c>
       <c r="G400" t="n">
-        <v>2.08683896064758</v>
+        <v>2.086838722229</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G402" t="n">
-        <v>2.10773229598999</v>
+        <v>2.10773205757141</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>3.46399998664856</v>
       </c>
       <c r="G405" t="n">
-        <v>2.12862515449524</v>
+        <v>2.12862491607666</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G406" t="n">
-        <v>2.10773229598999</v>
+        <v>2.10773205757141</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G408" t="n">
-        <v>2.18147158622742</v>
+        <v>2.18147206306458</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>3.58200001716614</v>
       </c>
       <c r="G409" t="n">
-        <v>2.20113611221313</v>
+        <v>2.20113587379456</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>3.59800004959106</v>
       </c>
       <c r="G410" t="n">
-        <v>2.2109682559967</v>
+        <v>2.21096777915955</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>3.57599997520447</v>
       </c>
       <c r="G411" t="n">
-        <v>2.19744873046875</v>
+        <v>2.19744920730591</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>3.58200001716614</v>
       </c>
       <c r="G413" t="n">
-        <v>2.20113611221313</v>
+        <v>2.20113587379456</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>3.5460000038147</v>
       </c>
       <c r="G414" t="n">
-        <v>2.17901396751404</v>
+        <v>2.17901420593262</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>3.55599999427795</v>
       </c>
       <c r="G415" t="n">
-        <v>2.18515849113464</v>
+        <v>2.1851589679718</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G416" t="n">
-        <v>2.16303682327271</v>
+        <v>2.16303658485413</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>3.5220000743866</v>
       </c>
       <c r="G417" t="n">
-        <v>2.16426610946655</v>
+        <v>2.16426587104797</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>3.4760000705719</v>
       </c>
       <c r="G420" t="n">
-        <v>2.13599872589111</v>
+        <v>2.13599920272827</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G425" t="n">
-        <v>2.16303682327271</v>
+        <v>2.16303658485413</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>3.60199999809265</v>
       </c>
       <c r="G428" t="n">
-        <v>2.21342587471008</v>
+        <v>2.21342611312866</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G431" t="n">
-        <v>2.21834206581116</v>
+        <v>2.218341588974</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>3.61400008201599</v>
       </c>
       <c r="G432" t="n">
-        <v>2.22080016136169</v>
+        <v>2.22079968452454</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>3.64400005340576</v>
       </c>
       <c r="G435" t="n">
-        <v>2.23923468589783</v>
+        <v>2.23923492431641</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G436" t="n">
-        <v>2.21834206581116</v>
+        <v>2.218341588974</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>3.59800004959106</v>
       </c>
       <c r="G437" t="n">
-        <v>2.2109682559967</v>
+        <v>2.21096777915955</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G439" t="n">
-        <v>2.18147158622742</v>
+        <v>2.18147206306458</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>3.53200006484985</v>
       </c>
       <c r="G440" t="n">
-        <v>2.17041087150574</v>
+        <v>2.1704113483429</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>3.50600004196167</v>
       </c>
       <c r="G448" t="n">
-        <v>2.15443396568298</v>
+        <v>2.15443420410156</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G449" t="n">
-        <v>2.16303682327271</v>
+        <v>2.16303658485413</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G451" t="n">
-        <v>2.21219682693481</v>
+        <v>2.21219658851624</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G452" t="n">
-        <v>2.23063206672668</v>
+        <v>2.23063182830811</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G454" t="n">
-        <v>2.23063206672668</v>
+        <v>2.23063182830811</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>3.61400008201599</v>
       </c>
       <c r="G455" t="n">
-        <v>2.22080016136169</v>
+        <v>2.22079968452454</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G457" t="n">
-        <v>2.16303682327271</v>
+        <v>2.16303658485413</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>3.60400009155273</v>
       </c>
       <c r="G459" t="n">
-        <v>2.21465516090393</v>
+        <v>2.21465468406677</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G462" t="n">
-        <v>2.19376158714294</v>
+        <v>2.19376182556152</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>3.60800004005432</v>
       </c>
       <c r="G464" t="n">
-        <v>2.21711277961731</v>
+        <v>2.21711301803589</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>3.57599997520447</v>
       </c>
       <c r="G466" t="n">
-        <v>2.19744873046875</v>
+        <v>2.19744920730591</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>3.73600006103516</v>
       </c>
       <c r="G473" t="n">
-        <v>2.29576873779297</v>
+        <v>2.29576897621155</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>3.81399989128113</v>
       </c>
       <c r="G474" t="n">
-        <v>2.34369945526123</v>
+        <v>2.34369969367981</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G476" t="n">
-        <v>2.32280659675598</v>
+        <v>2.32280683517456</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G478" t="n">
-        <v>2.26750206947327</v>
+        <v>2.26750183105469</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G480" t="n">
-        <v>2.2490668296814</v>
+        <v>2.24906706809998</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G481" t="n">
-        <v>2.19376158714294</v>
+        <v>2.19376182556152</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>3.60400009155273</v>
       </c>
       <c r="G482" t="n">
-        <v>2.21465516090393</v>
+        <v>2.21465468406677</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>3.57599997520447</v>
       </c>
       <c r="G483" t="n">
-        <v>2.19744873046875</v>
+        <v>2.19744920730591</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G486" t="n">
-        <v>2.2490668296814</v>
+        <v>2.24906706809998</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>3.65599989891052</v>
       </c>
       <c r="G487" t="n">
-        <v>2.24660873413086</v>
+        <v>2.24660849571228</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>3.60400009155273</v>
       </c>
       <c r="G489" t="n">
-        <v>2.21465516090393</v>
+        <v>2.21465468406677</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G490" t="n">
-        <v>2.21219682693481</v>
+        <v>2.21219658851624</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G491" t="n">
-        <v>2.2490668296814</v>
+        <v>2.24906706809998</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>3.72199988365173</v>
       </c>
       <c r="G492" t="n">
-        <v>2.28716540336609</v>
+        <v>2.28716588020325</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>3.64400005340576</v>
       </c>
       <c r="G493" t="n">
-        <v>2.23923468589783</v>
+        <v>2.23923492431641</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>3.67400002479553</v>
       </c>
       <c r="G495" t="n">
-        <v>2.2576699256897</v>
+        <v>2.25766944885254</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>3.68600010871887</v>
       </c>
       <c r="G497" t="n">
-        <v>2.26504397392273</v>
+        <v>2.26504373550415</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G498" t="n">
-        <v>2.2490668296814</v>
+        <v>2.24906706809998</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G499" t="n">
-        <v>2.23063206672668</v>
+        <v>2.23063182830811</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G500" t="n">
-        <v>2.19990682601929</v>
+        <v>2.19990658760071</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G503" t="n">
-        <v>2.23063206672668</v>
+        <v>2.23063182830811</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>3.62599992752075</v>
       </c>
       <c r="G504" t="n">
-        <v>2.22817373275757</v>
+        <v>2.22817397117615</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>3.58200001716614</v>
       </c>
       <c r="G505" t="n">
-        <v>2.20113611221313</v>
+        <v>2.20113587379456</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>3.58200001716614</v>
       </c>
       <c r="G509" t="n">
-        <v>2.20113611221313</v>
+        <v>2.20113587379456</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>3.60199999809265</v>
       </c>
       <c r="G510" t="n">
-        <v>2.21342587471008</v>
+        <v>2.21342611312866</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>3.5460000038147</v>
       </c>
       <c r="G511" t="n">
-        <v>2.17901396751404</v>
+        <v>2.17901420593262</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G515" t="n">
-        <v>2.26750206947327</v>
+        <v>2.26750183105469</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G516" t="n">
-        <v>2.24599432945251</v>
+        <v>2.24599409103394</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G517" t="n">
-        <v>2.26750206947327</v>
+        <v>2.26750183105469</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G518" t="n">
-        <v>2.24292206764221</v>
+        <v>2.24292182922363</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G519" t="n">
-        <v>2.21219682693481</v>
+        <v>2.21219658851624</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G520" t="n">
-        <v>2.2490668296814</v>
+        <v>2.24906706809998</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G521" t="n">
-        <v>2.2613570690155</v>
+        <v>2.26135659217834</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G522" t="n">
-        <v>2.24292206764221</v>
+        <v>2.24292182922363</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G526" t="n">
-        <v>2.24599432945251</v>
+        <v>2.24599409103394</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G528" t="n">
-        <v>2.23063206672668</v>
+        <v>2.23063182830811</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G532" t="n">
-        <v>2.20297956466675</v>
+        <v>2.20297932624817</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G533" t="n">
-        <v>2.18147158622742</v>
+        <v>2.18147206306458</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G534" t="n">
-        <v>2.18147158622742</v>
+        <v>2.18147206306458</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G536" t="n">
-        <v>2.02784729003906</v>
+        <v>2.02784705162048</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G537" t="n">
-        <v>1.94181716442108</v>
+        <v>1.94181740283966</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G540" t="n">
-        <v>1.9356724023819</v>
+        <v>1.93567264080048</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>3.21499991416931</v>
       </c>
       <c r="G543" t="n">
-        <v>1.97561466693878</v>
+        <v>1.9756144285202</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>3.21499991416931</v>
       </c>
       <c r="G544" t="n">
-        <v>1.97561466693878</v>
+        <v>1.9756144285202</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G545" t="n">
-        <v>2.00941205024719</v>
+        <v>2.00941228866577</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G549" t="n">
-        <v>1.96332478523254</v>
+        <v>1.96332454681396</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G552" t="n">
-        <v>1.92645442485809</v>
+        <v>1.92645490169525</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G553" t="n">
-        <v>1.91723692417145</v>
+        <v>1.91723740100861</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G554" t="n">
-        <v>1.91723692417145</v>
+        <v>1.91723740100861</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G557" t="n">
-        <v>1.91416454315186</v>
+        <v>1.91416478157043</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G558" t="n">
-        <v>1.92338240146637</v>
+        <v>1.92338252067566</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G559" t="n">
-        <v>1.92338240146637</v>
+        <v>1.92338252067566</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G560" t="n">
-        <v>1.94488954544067</v>
+        <v>1.94489002227783</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G561" t="n">
-        <v>1.98175966739655</v>
+        <v>1.98175990581512</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>3.15499997138977</v>
       </c>
       <c r="G562" t="n">
-        <v>1.93874454498291</v>
+        <v>1.93874478340149</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>3.15499997138977</v>
       </c>
       <c r="G563" t="n">
-        <v>1.93874454498291</v>
+        <v>1.93874478340149</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G564" t="n">
-        <v>1.96639740467072</v>
+        <v>1.96639716625214</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G565" t="n">
-        <v>1.9725421667099</v>
+        <v>1.97254228591919</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G566" t="n">
-        <v>2.01862978935242</v>
+        <v>2.018630027771</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G567" t="n">
-        <v>2.01862978935242</v>
+        <v>2.018630027771</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G571" t="n">
-        <v>1.95717990398407</v>
+        <v>1.95717942714691</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G572" t="n">
-        <v>1.96025228500366</v>
+        <v>1.96025240421295</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G573" t="n">
-        <v>1.99404978752136</v>
+        <v>1.99404954910278</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G574" t="n">
-        <v>2.00326728820801</v>
+        <v>2.00326704978943</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G576" t="n">
-        <v>1.9725421667099</v>
+        <v>1.97254228591919</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G577" t="n">
-        <v>2.00326728820801</v>
+        <v>2.00326704978943</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G578" t="n">
-        <v>2.01862978935242</v>
+        <v>2.018630027771</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G581" t="n">
-        <v>2.00326728820801</v>
+        <v>2.00326704978943</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G582" t="n">
-        <v>2.00941205024719</v>
+        <v>2.00941228866577</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G584" t="n">
-        <v>2.0217022895813</v>
+        <v>2.02170181274414</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G585" t="n">
-        <v>2.0217022895813</v>
+        <v>2.02170181274414</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G586" t="n">
-        <v>2.0217022895813</v>
+        <v>2.02170181274414</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G587" t="n">
-        <v>2.02784729003906</v>
+        <v>2.02784705162048</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G588" t="n">
-        <v>2.02784729003906</v>
+        <v>2.02784705162048</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G589" t="n">
-        <v>2.02784729003906</v>
+        <v>2.02784705162048</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G591" t="n">
-        <v>2.02784729003906</v>
+        <v>2.02784705162048</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G593" t="n">
-        <v>2.04628205299377</v>
+        <v>2.0462818145752</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G594" t="n">
-        <v>2.08929681777954</v>
+        <v>2.08929705619812</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G595" t="n">
-        <v>2.16918182373047</v>
+        <v>2.16918206214905</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G598" t="n">
-        <v>2.17001366615295</v>
+        <v>2.17001342773438</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G602" t="n">
-        <v>2.07284879684448</v>
+        <v>2.0728485584259</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G605" t="n">
-        <v>2.02750515937805</v>
+        <v>2.02750539779663</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G606" t="n">
-        <v>2.02750515937805</v>
+        <v>2.02750539779663</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G608" t="n">
-        <v>2.01131081581116</v>
+        <v>2.01131105422974</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G609" t="n">
-        <v>2.00483345985413</v>
+        <v>2.00483369827271</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G613" t="n">
-        <v>1.94653451442719</v>
+        <v>1.94653475284576</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>2.875</v>
       </c>
       <c r="G614" t="n">
-        <v>1.86232542991638</v>
+        <v>1.86232507228851</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G615" t="n">
-        <v>1.91090703010559</v>
+        <v>1.91090726852417</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G616" t="n">
-        <v>1.94653451442719</v>
+        <v>1.94653475284576</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G620" t="n">
-        <v>1.93034040927887</v>
+        <v>1.93034064769745</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G621" t="n">
-        <v>1.94653451442719</v>
+        <v>1.94653475284576</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G622" t="n">
-        <v>1.90766870975494</v>
+        <v>1.90766859054565</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>2.97499990463257</v>
       </c>
       <c r="G627" t="n">
-        <v>1.92710137367249</v>
+        <v>1.92710161209106</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G628" t="n">
-        <v>1.93681812286377</v>
+        <v>1.93681788444519</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>2.97499990463257</v>
       </c>
       <c r="G629" t="n">
-        <v>1.92710137367249</v>
+        <v>1.92710161209106</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G631" t="n">
-        <v>1.89147460460663</v>
+        <v>1.89147436618805</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>3.06500005722046</v>
       </c>
       <c r="G632" t="n">
-        <v>1.98540031909943</v>
+        <v>1.98540055751801</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G633" t="n">
-        <v>1.91090703010559</v>
+        <v>1.91090726852417</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G634" t="n">
-        <v>1.96596765518188</v>
+        <v>1.96596741676331</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G637" t="n">
-        <v>1.93681812286377</v>
+        <v>1.93681788444519</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G638" t="n">
-        <v>1.90766870975494</v>
+        <v>1.90766859054565</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>2.97499990463257</v>
       </c>
       <c r="G641" t="n">
-        <v>1.92710137367249</v>
+        <v>1.92710161209106</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G646" t="n">
-        <v>1.87204134464264</v>
+        <v>1.87204170227051</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>2.86500000953674</v>
       </c>
       <c r="G648" t="n">
-        <v>1.8558474779129</v>
+        <v>1.85584735870361</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G650" t="n">
-        <v>1.87204134464264</v>
+        <v>1.87204170227051</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G652" t="n">
-        <v>1.87204134464264</v>
+        <v>1.87204170227051</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G653" t="n">
-        <v>1.85260844230652</v>
+        <v>1.85260856151581</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G654" t="n">
-        <v>1.84613084793091</v>
+        <v>1.84613060951233</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G657" t="n">
-        <v>2.04046058654785</v>
+        <v>2.04046082496643</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>3.35500001907349</v>
       </c>
       <c r="G661" t="n">
-        <v>2.17325234413147</v>
+        <v>2.17325258255005</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G662" t="n">
-        <v>2.17001366615295</v>
+        <v>2.17001342773438</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>3.26500010490417</v>
       </c>
       <c r="G663" t="n">
-        <v>2.1149537563324</v>
+        <v>2.11495327949524</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G664" t="n">
-        <v>2.11819219589233</v>
+        <v>2.11819243431091</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>3.25</v>
       </c>
       <c r="G665" t="n">
-        <v>2.10523700714111</v>
+        <v>2.10523676872253</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G666" t="n">
-        <v>2.06961011886597</v>
+        <v>2.06960988044739</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G667" t="n">
-        <v>2.03074383735657</v>
+        <v>2.03074431419373</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G668" t="n">
-        <v>2.00807213783264</v>
+        <v>2.00807237625122</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G669" t="n">
-        <v>2.02750515937805</v>
+        <v>2.02750539779663</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G670" t="n">
-        <v>1.95948994159698</v>
+        <v>1.95949006080627</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G672" t="n">
-        <v>1.96596765518188</v>
+        <v>1.96596741676331</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G674" t="n">
-        <v>2.02102732658386</v>
+        <v>2.02102756500244</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G675" t="n">
-        <v>1.99187803268433</v>
+        <v>1.99187815189362</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G676" t="n">
-        <v>2.00483345985413</v>
+        <v>2.00483369827271</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G677" t="n">
-        <v>1.99835574626923</v>
+        <v>1.99835586547852</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G679" t="n">
-        <v>2.01454973220825</v>
+        <v>2.01454925537109</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G680" t="n">
-        <v>2.01454973220825</v>
+        <v>2.01454925537109</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G681" t="n">
-        <v>2.01454973220825</v>
+        <v>2.01454925537109</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>3.125</v>
       </c>
       <c r="G682" t="n">
-        <v>2.02426624298096</v>
+        <v>2.02426600456238</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G683" t="n">
-        <v>2.01454973220825</v>
+        <v>2.01454925537109</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G684" t="n">
-        <v>2.01131081581116</v>
+        <v>2.01131105422974</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G687" t="n">
-        <v>2.02750515937805</v>
+        <v>2.02750539779663</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G688" t="n">
-        <v>2.02750515937805</v>
+        <v>2.02750539779663</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G689" t="n">
-        <v>2.0501766204834</v>
+        <v>2.05017709732056</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G690" t="n">
-        <v>2.04693794250488</v>
+        <v>2.04693818092346</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G693" t="n">
-        <v>2.05341601371765</v>
+        <v>2.05341577529907</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G694" t="n">
-        <v>2.05341601371765</v>
+        <v>2.05341577529907</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G695" t="n">
-        <v>2.04693794250488</v>
+        <v>2.04693818092346</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G696" t="n">
-        <v>2.05341601371765</v>
+        <v>2.05341577529907</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G697" t="n">
-        <v>2.04693794250488</v>
+        <v>2.04693818092346</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G698" t="n">
-        <v>2.04693794250488</v>
+        <v>2.04693818092346</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G699" t="n">
-        <v>2.04693794250488</v>
+        <v>2.04693818092346</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G700" t="n">
-        <v>2.01454973220825</v>
+        <v>2.01454925537109</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G702" t="n">
-        <v>1.93034040927887</v>
+        <v>1.93034064769745</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>2.97499990463257</v>
       </c>
       <c r="G703" t="n">
-        <v>1.92710137367249</v>
+        <v>1.92710161209106</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>2.97499990463257</v>
       </c>
       <c r="G704" t="n">
-        <v>1.92710137367249</v>
+        <v>1.92710161209106</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G706" t="n">
-        <v>1.90442979335785</v>
+        <v>1.90442967414856</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G707" t="n">
-        <v>1.90442979335785</v>
+        <v>1.90442967414856</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G708" t="n">
-        <v>1.90766870975494</v>
+        <v>1.90766859054565</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G710" t="n">
-        <v>1.91738498210907</v>
+        <v>1.91738522052765</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G712" t="n">
-        <v>1.90766870975494</v>
+        <v>1.90766859054565</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G714" t="n">
-        <v>1.99835574626923</v>
+        <v>1.99835586547852</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G716" t="n">
-        <v>1.93681812286377</v>
+        <v>1.93681788444519</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>2.97499990463257</v>
       </c>
       <c r="G717" t="n">
-        <v>1.92710137367249</v>
+        <v>1.92710161209106</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>2.875</v>
       </c>
       <c r="G718" t="n">
-        <v>1.86232542991638</v>
+        <v>1.86232507228851</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G720" t="n">
-        <v>1.84613084793091</v>
+        <v>1.84613060951233</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>2.90499997138977</v>
       </c>
       <c r="G722" t="n">
-        <v>1.88175821304321</v>
+        <v>1.88175797462463</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G723" t="n">
-        <v>1.87204134464264</v>
+        <v>1.87204170227051</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G725" t="n">
-        <v>1.88499689102173</v>
+        <v>1.88499677181244</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>2.97499990463257</v>
       </c>
       <c r="G726" t="n">
-        <v>1.92710137367249</v>
+        <v>1.92710161209106</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>3.04500007629395</v>
       </c>
       <c r="G728" t="n">
-        <v>1.97244489192963</v>
+        <v>1.97244513034821</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G730" t="n">
-        <v>1.99835574626923</v>
+        <v>1.99835586547852</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G733" t="n">
-        <v>1.96596765518188</v>
+        <v>1.96596741676331</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G735" t="n">
-        <v>1.93681812286377</v>
+        <v>1.93681788444519</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G736" t="n">
-        <v>1.96920621395111</v>
+        <v>1.96920597553253</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G739" t="n">
-        <v>1.94977331161499</v>
+        <v>1.94977355003357</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G746" t="n">
-        <v>2.00483345985413</v>
+        <v>2.00483369827271</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G747" t="n">
-        <v>1.99835574626923</v>
+        <v>1.99835586547852</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G749" t="n">
-        <v>2.07284879684448</v>
+        <v>2.0728485584259</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G750" t="n">
-        <v>1.99835574626923</v>
+        <v>1.99835586547852</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G751" t="n">
-        <v>1.99187803268433</v>
+        <v>1.99187815189362</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G752" t="n">
-        <v>1.99835574626923</v>
+        <v>1.99835586547852</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G754" t="n">
-        <v>2.02102732658386</v>
+        <v>2.02102756500244</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G755" t="n">
-        <v>2.01454973220825</v>
+        <v>2.01454925537109</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>3.125</v>
       </c>
       <c r="G756" t="n">
-        <v>2.02426624298096</v>
+        <v>2.02426600456238</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G758" t="n">
-        <v>1.99187803268433</v>
+        <v>1.99187815189362</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G761" t="n">
-        <v>1.99187803268433</v>
+        <v>1.99187815189362</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G763" t="n">
-        <v>2.01454973220825</v>
+        <v>2.01454925537109</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G764" t="n">
-        <v>2.00483345985413</v>
+        <v>2.00483369827271</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G765" t="n">
-        <v>2.10199809074402</v>
+        <v>2.10199785232544</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G766" t="n">
-        <v>2.12790894508362</v>
+        <v>2.1279091835022</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G768" t="n">
-        <v>2.0858039855957</v>
+        <v>2.08580422401428</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G769" t="n">
-        <v>2.06961011886597</v>
+        <v>2.06960988044739</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G770" t="n">
-        <v>2.0858039855957</v>
+        <v>2.08580422401428</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G771" t="n">
-        <v>2.06961011886597</v>
+        <v>2.06960988044739</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G774" t="n">
-        <v>2.0501766204834</v>
+        <v>2.05017709732056</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G776" t="n">
-        <v>2.06313228607178</v>
+        <v>2.06313180923462</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G777" t="n">
-        <v>2.07284879684448</v>
+        <v>2.0728485584259</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G778" t="n">
-        <v>2.06313228607178</v>
+        <v>2.06313180923462</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G782" t="n">
-        <v>2.07284879684448</v>
+        <v>2.0728485584259</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G783" t="n">
-        <v>2.07284879684448</v>
+        <v>2.0728485584259</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G785" t="n">
-        <v>2.0858039855957</v>
+        <v>2.08580422401428</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>3.25</v>
       </c>
       <c r="G788" t="n">
-        <v>2.10523700714111</v>
+        <v>2.10523676872253</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>3.25</v>
       </c>
       <c r="G791" t="n">
-        <v>2.10523700714111</v>
+        <v>2.10523676872253</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G793" t="n">
-        <v>2.11819219589233</v>
+        <v>2.11819243431091</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>3.3050000667572</v>
       </c>
       <c r="G797" t="n">
-        <v>2.14086413383484</v>
+        <v>2.14086365699768</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G798" t="n">
-        <v>2.12790894508362</v>
+        <v>2.1279091835022</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G801" t="n">
-        <v>2.18944668769836</v>
+        <v>2.18944644927979</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G806" t="n">
-        <v>2.17001366615295</v>
+        <v>2.17001342773438</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G808" t="n">
-        <v>2.18944668769836</v>
+        <v>2.18944644927979</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>3.38499999046326</v>
       </c>
       <c r="G811" t="n">
-        <v>2.19268536567688</v>
+        <v>2.1926851272583</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G813" t="n">
-        <v>2.21535730361938</v>
+        <v>2.21535682678223</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G815" t="n">
-        <v>2.21211814880371</v>
+        <v>2.21211838722229</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G816" t="n">
-        <v>2.221834897995</v>
+        <v>2.22183465957642</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G818" t="n">
-        <v>2.2088794708252</v>
+        <v>2.20887970924377</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G819" t="n">
-        <v>2.2088794708252</v>
+        <v>2.20887970924377</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G821" t="n">
-        <v>2.21211814880371</v>
+        <v>2.21211838722229</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G822" t="n">
-        <v>2.23479008674622</v>
+        <v>2.23479032516479</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G824" t="n">
-        <v>2.25422286987305</v>
+        <v>2.25422310829163</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G828" t="n">
-        <v>2.25746154785156</v>
+        <v>2.25746202468872</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G830" t="n">
-        <v>2.2995662689209</v>
+        <v>2.29956674575806</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G831" t="n">
-        <v>2.2995662689209</v>
+        <v>2.29956674575806</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>3.57500004768372</v>
       </c>
       <c r="G832" t="n">
-        <v>2.31576085090637</v>
+        <v>2.31576061248779</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G833" t="n">
-        <v>2.3125216960907</v>
+        <v>2.31252193450928</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G835" t="n">
-        <v>2.32547736167908</v>
+        <v>2.3254771232605</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G836" t="n">
-        <v>2.33843278884888</v>
+        <v>2.33843231201172</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>3.68499994277954</v>
       </c>
       <c r="G838" t="n">
-        <v>2.38701462745667</v>
+        <v>2.38701486587524</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G839" t="n">
-        <v>2.3643434047699</v>
+        <v>2.36434316635132</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>3.70499992370605</v>
       </c>
       <c r="G841" t="n">
-        <v>2.39997029304504</v>
+        <v>2.39996981620789</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G842" t="n">
-        <v>2.41292572021484</v>
+        <v>2.41292548179626</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>3.81500005722046</v>
       </c>
       <c r="G843" t="n">
-        <v>2.47122430801392</v>
+        <v>2.4712245464325</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G844" t="n">
-        <v>2.46798539161682</v>
+        <v>2.4679856300354</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>3.81500005722046</v>
       </c>
       <c r="G847" t="n">
-        <v>2.47122430801392</v>
+        <v>2.4712245464325</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G848" t="n">
-        <v>2.74367260932922</v>
+        <v>2.74367213249207</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>3.49499988555908</v>
       </c>
       <c r="G849" t="n">
-        <v>2.48423194885254</v>
+        <v>2.48423171043396</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G851" t="n">
-        <v>2.43803024291992</v>
+        <v>2.4380304813385</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>3.45499992370605</v>
       </c>
       <c r="G852" t="n">
-        <v>2.4558002948761</v>
+        <v>2.45580005645752</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G853" t="n">
-        <v>2.43092250823975</v>
+        <v>2.43092226982117</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>3.625</v>
       </c>
       <c r="G855" t="n">
-        <v>2.57663512229919</v>
+        <v>2.57663536071777</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G856" t="n">
-        <v>2.53754162788391</v>
+        <v>2.53754138946533</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G858" t="n">
-        <v>2.5233256816864</v>
+        <v>2.52332520484924</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G859" t="n">
-        <v>2.51621770858765</v>
+        <v>2.51621794700623</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G860" t="n">
-        <v>2.50910949707031</v>
+        <v>2.50910973548889</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G862" t="n">
-        <v>2.52687978744507</v>
+        <v>2.52687954902649</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G863" t="n">
-        <v>2.58018970489502</v>
+        <v>2.58018922805786</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>3.61500000953674</v>
       </c>
       <c r="G867" t="n">
-        <v>2.5695276260376</v>
+        <v>2.56952738761902</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>3.625</v>
       </c>
       <c r="G873" t="n">
-        <v>2.57663512229919</v>
+        <v>2.57663536071777</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G874" t="n">
-        <v>2.58018970489502</v>
+        <v>2.58018922805786</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G875" t="n">
-        <v>2.60506701469421</v>
+        <v>2.60506725311279</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G880" t="n">
-        <v>2.7152407169342</v>
+        <v>2.71524047851562</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G881" t="n">
-        <v>2.65126919746399</v>
+        <v>2.65126895904541</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G882" t="n">
-        <v>2.67970061302185</v>
+        <v>2.67970085144043</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G883" t="n">
-        <v>2.69391655921936</v>
+        <v>2.69391679763794</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>3.83500003814697</v>
       </c>
       <c r="G890" t="n">
-        <v>2.72590279579163</v>
+        <v>2.72590255737305</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>4.14499998092651</v>
       </c>
       <c r="G902" t="n">
-        <v>2.94624924659729</v>
+        <v>2.94624948501587</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G905" t="n">
-        <v>2.99245119094849</v>
+        <v>2.99245095252991</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>4.25</v>
       </c>
       <c r="G906" t="n">
-        <v>3.02088284492493</v>
+        <v>3.02088260650635</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>4.22499990463257</v>
       </c>
       <c r="G907" t="n">
-        <v>3.00311326980591</v>
+        <v>3.00311279296875</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G908" t="n">
-        <v>2.97112679481506</v>
+        <v>2.97112703323364</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G910" t="n">
-        <v>2.90715551376343</v>
+        <v>2.90715575218201</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>4.00500011444092</v>
       </c>
       <c r="G915" t="n">
-        <v>2.84673762321472</v>
+        <v>2.84673810005188</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G918" t="n">
-        <v>2.76499652862549</v>
+        <v>2.76499629020691</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G919" t="n">
-        <v>2.76499652862549</v>
+        <v>2.76499629020691</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>4.10500001907349</v>
       </c>
       <c r="G923" t="n">
-        <v>2.91781759262085</v>
+        <v>2.91781735420227</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G924" t="n">
-        <v>2.91426301002502</v>
+        <v>2.91426348686218</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>4.0149998664856</v>
       </c>
       <c r="G927" t="n">
-        <v>2.85384559631348</v>
+        <v>2.85384583473206</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G929" t="n">
-        <v>2.75788855552673</v>
+        <v>2.75788831710815</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G930" t="n">
-        <v>2.82896780967712</v>
+        <v>2.8289680480957</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>3.98499989509583</v>
       </c>
       <c r="G931" t="n">
-        <v>2.83252191543579</v>
+        <v>2.83252215385437</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G933" t="n">
-        <v>2.80053615570068</v>
+        <v>2.8005359172821</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>3.95499992370605</v>
       </c>
       <c r="G935" t="n">
-        <v>2.81119823455811</v>
+        <v>2.81119775772095</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G936" t="n">
-        <v>2.76499652862549</v>
+        <v>2.76499629020691</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G937" t="n">
-        <v>2.70457887649536</v>
+        <v>2.70457863807678</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G938" t="n">
-        <v>2.65126919746399</v>
+        <v>2.65126895904541</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>3.67499995231628</v>
       </c>
       <c r="G939" t="n">
-        <v>2.61217498779297</v>
+        <v>2.61217522621155</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G941" t="n">
-        <v>2.69747090339661</v>
+        <v>2.69747066497803</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>3.83500003814697</v>
       </c>
       <c r="G944" t="n">
-        <v>2.72590279579163</v>
+        <v>2.72590255737305</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G945" t="n">
-        <v>2.71879482269287</v>
+        <v>2.71879458427429</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G946" t="n">
-        <v>2.74367260932922</v>
+        <v>2.74367213249207</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G947" t="n">
-        <v>2.7223482131958</v>
+        <v>2.72234845161438</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G950" t="n">
-        <v>2.7507803440094</v>
+        <v>2.75078010559082</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G954" t="n">
-        <v>2.75788855552673</v>
+        <v>2.75788831710815</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G956" t="n">
-        <v>2.74722647666931</v>
+        <v>2.74722623825073</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G957" t="n">
-        <v>2.74367260932922</v>
+        <v>2.74367213249207</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G959" t="n">
-        <v>2.7223482131958</v>
+        <v>2.72234845161438</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G960" t="n">
-        <v>2.71879482269287</v>
+        <v>2.71879458427429</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G961" t="n">
-        <v>2.7223482131958</v>
+        <v>2.72234845161438</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>3.83500003814697</v>
       </c>
       <c r="G962" t="n">
-        <v>2.72590279579163</v>
+        <v>2.72590255737305</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G964" t="n">
-        <v>2.7152407169342</v>
+        <v>2.71524047851562</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G967" t="n">
-        <v>2.69391655921936</v>
+        <v>2.69391679763794</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G971" t="n">
-        <v>2.62994503974915</v>
+        <v>2.62994527816772</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G975" t="n">
-        <v>2.62283754348755</v>
+        <v>2.62283730506897</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G976" t="n">
-        <v>2.65126919746399</v>
+        <v>2.65126895904541</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>3.83500003814697</v>
       </c>
       <c r="G978" t="n">
-        <v>2.72590279579163</v>
+        <v>2.72590255737305</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G979" t="n">
-        <v>2.71879482269287</v>
+        <v>2.71879458427429</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G981" t="n">
-        <v>2.70457887649536</v>
+        <v>2.70457863807678</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G982" t="n">
-        <v>2.7223482131958</v>
+        <v>2.72234845161438</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G984" t="n">
-        <v>2.90715551376343</v>
+        <v>2.90715575218201</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G986" t="n">
-        <v>2.80764412879944</v>
+        <v>2.80764389038086</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>3.96499991416931</v>
       </c>
       <c r="G987" t="n">
-        <v>2.8183057308197</v>
+        <v>2.81830596923828</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G988" t="n">
-        <v>2.80053615570068</v>
+        <v>2.8005359172821</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G989" t="n">
-        <v>2.80764412879944</v>
+        <v>2.80764389038086</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G993" t="n">
-        <v>2.7223482131958</v>
+        <v>2.72234845161438</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>3.95499992370605</v>
       </c>
       <c r="G995" t="n">
-        <v>2.81119823455811</v>
+        <v>2.81119775772095</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>3.98499989509583</v>
       </c>
       <c r="G996" t="n">
-        <v>2.83252191543579</v>
+        <v>2.83252215385437</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G999" t="n">
-        <v>2.74011850357056</v>
+        <v>2.7401180267334</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1004" t="n">
-        <v>2.72945642471313</v>
+        <v>2.72945666313171</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G1008" t="n">
-        <v>2.67614722251892</v>
+        <v>2.67614698410034</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>3.81500005722046</v>
       </c>
       <c r="G1012" t="n">
-        <v>2.71168637275696</v>
+        <v>2.71168661117554</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1013" t="n">
-        <v>2.7152407169342</v>
+        <v>2.71524047851562</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1014" t="n">
-        <v>2.7223482131958</v>
+        <v>2.72234845161438</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>3.81500005722046</v>
       </c>
       <c r="G1015" t="n">
-        <v>2.71168637275696</v>
+        <v>2.71168661117554</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G1016" t="n">
-        <v>2.70457887649536</v>
+        <v>2.70457863807678</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G1017" t="n">
-        <v>2.70457887649536</v>
+        <v>2.70457863807678</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G1018" t="n">
-        <v>2.70457887649536</v>
+        <v>2.70457863807678</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G1020" t="n">
-        <v>2.70457887649536</v>
+        <v>2.70457863807678</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1022" t="n">
-        <v>2.7507803440094</v>
+        <v>2.75078010559082</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1023" t="n">
-        <v>2.74367260932922</v>
+        <v>2.74367213249207</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>3.81500005722046</v>
       </c>
       <c r="G1024" t="n">
-        <v>2.71168637275696</v>
+        <v>2.71168661117554</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1025" t="n">
-        <v>2.72945642471313</v>
+        <v>2.72945666313171</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1027" t="n">
-        <v>2.80053615570068</v>
+        <v>2.8005359172821</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>3.96499991416931</v>
       </c>
       <c r="G1030" t="n">
-        <v>2.8183057308197</v>
+        <v>2.81830596923828</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1033" t="n">
-        <v>2.80053615570068</v>
+        <v>2.8005359172821</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1037" t="n">
-        <v>3.14171862602234</v>
+        <v>3.14171814918518</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G1038" t="n">
-        <v>3.21635174751282</v>
+        <v>3.2163519859314</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G1039" t="n">
-        <v>3.15948820114136</v>
+        <v>3.15948843955994</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1040" t="n">
-        <v>3.24833750724792</v>
+        <v>3.24833798408508</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>4.49499988555908</v>
       </c>
       <c r="G1041" t="n">
-        <v>3.19502782821655</v>
+        <v>3.19502758979797</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G1043" t="n">
-        <v>3.27676963806152</v>
+        <v>3.27676939964294</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G1044" t="n">
-        <v>3.1879198551178</v>
+        <v>3.18792009353638</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>4.36499977111816</v>
       </c>
       <c r="G1045" t="n">
-        <v>3.10262441635132</v>
+        <v>3.10262417793274</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1046" t="n">
-        <v>3.07774639129639</v>
+        <v>3.07774662971497</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1047" t="n">
-        <v>3.06353044509888</v>
+        <v>3.06353068351746</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1049" t="n">
-        <v>3.14171862602234</v>
+        <v>3.14171814918518</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>4.40500020980835</v>
       </c>
       <c r="G1051" t="n">
-        <v>3.13105607032776</v>
+        <v>3.13105630874634</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G1053" t="n">
-        <v>2.98178911209106</v>
+        <v>2.98178935050964</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>4.10500001907349</v>
       </c>
       <c r="G1054" t="n">
-        <v>2.91781759262085</v>
+        <v>2.91781735420227</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1055" t="n">
-        <v>2.95691108703613</v>
+        <v>2.95691084861755</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>4.09499979019165</v>
       </c>
       <c r="G1056" t="n">
-        <v>2.91070961952209</v>
+        <v>2.91070938110352</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>4.09499979019165</v>
       </c>
       <c r="G1059" t="n">
-        <v>2.91070961952209</v>
+        <v>2.91070938110352</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>4.16499996185303</v>
       </c>
       <c r="G1060" t="n">
-        <v>2.96046543121338</v>
+        <v>2.96046495437622</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>4.125</v>
       </c>
       <c r="G1061" t="n">
-        <v>2.93203353881836</v>
+        <v>2.93203330039978</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1064" t="n">
-        <v>2.5233256816864</v>
+        <v>2.52332520484924</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1066" t="n">
-        <v>1.93336522579193</v>
+        <v>1.93336498737335</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G1067" t="n">
-        <v>2.14304995536804</v>
+        <v>2.14304971694946</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>3.125</v>
       </c>
       <c r="G1068" t="n">
-        <v>2.22123742103577</v>
+        <v>2.22123765945435</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1069" t="n">
-        <v>2.26033115386963</v>
+        <v>2.26033139228821</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G1070" t="n">
-        <v>2.27099323272705</v>
+        <v>2.27099299430847</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>3.25500011444092</v>
       </c>
       <c r="G1071" t="n">
-        <v>2.31364107131958</v>
+        <v>2.313640832901</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1074" t="n">
-        <v>2.38827466964722</v>
+        <v>2.38827443122864</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1077" t="n">
-        <v>2.26033115386963</v>
+        <v>2.26033139228821</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1078" t="n">
-        <v>2.28165507316589</v>
+        <v>2.28165483474731</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>3.36500000953674</v>
       </c>
       <c r="G1079" t="n">
-        <v>2.39182829856873</v>
+        <v>2.3918285369873</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1081" t="n">
-        <v>2.27454686164856</v>
+        <v>2.27454710006714</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1083" t="n">
-        <v>2.27454686164856</v>
+        <v>2.27454710006714</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1084" t="n">
-        <v>2.27454686164856</v>
+        <v>2.27454710006714</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G1086" t="n">
-        <v>2.27810120582581</v>
+        <v>2.27810096740723</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G1090" t="n">
-        <v>2.29231715202332</v>
+        <v>2.29231691360474</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1092" t="n">
-        <v>2.27454686164856</v>
+        <v>2.27454710006714</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1093" t="n">
-        <v>2.28876328468323</v>
+        <v>2.28876304626465</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1094" t="n">
-        <v>2.33141040802002</v>
+        <v>2.3314106464386</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1095" t="n">
-        <v>2.33141040802002</v>
+        <v>2.3314106464386</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1096" t="n">
-        <v>2.34562706947327</v>
+        <v>2.34562659263611</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>3.36500000953674</v>
       </c>
       <c r="G1098" t="n">
-        <v>2.39182829856873</v>
+        <v>2.3918285369873</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1099" t="n">
-        <v>2.36695051193237</v>
+        <v>2.36695027351379</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1101" t="n">
-        <v>2.33141040802002</v>
+        <v>2.3314106464386</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1104" t="n">
-        <v>2.34562706947327</v>
+        <v>2.34562659263611</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1105" t="n">
-        <v>2.33141040802002</v>
+        <v>2.3314106464386</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1108" t="n">
-        <v>2.34562706947327</v>
+        <v>2.34562659263611</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1109" t="n">
-        <v>2.40249037742615</v>
+        <v>2.40249061584473</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G1110" t="n">
-        <v>2.37761259078979</v>
+        <v>2.37761235237122</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1111" t="n">
-        <v>2.38116645812988</v>
+        <v>2.3811662197113</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1112" t="n">
-        <v>2.38116645812988</v>
+        <v>2.3811662197113</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G1115" t="n">
-        <v>2.64771509170532</v>
+        <v>2.64771485328674</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>3.95499992370605</v>
       </c>
       <c r="G1118" t="n">
-        <v>2.81119823455811</v>
+        <v>2.81119775772095</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1120" t="n">
-        <v>2.91426301002502</v>
+        <v>2.91426348686218</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1123" t="n">
-        <v>3.12750220298767</v>
+        <v>3.12750244140625</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>4.25500011444092</v>
       </c>
       <c r="G1125" t="n">
-        <v>3.17926239967346</v>
+        <v>3.17926263809204</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1126" t="n">
-        <v>3.01861810684204</v>
+        <v>3.01861834526062</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1127" t="n">
-        <v>2.95137166976929</v>
+        <v>2.95137190818787</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>3.81500005722046</v>
       </c>
       <c r="G1128" t="n">
-        <v>2.85050201416016</v>
+        <v>2.85050177574158</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1131" t="n">
-        <v>2.9439001083374</v>
+        <v>2.94389986991882</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>3.875</v>
       </c>
       <c r="G1132" t="n">
-        <v>2.89533281326294</v>
+        <v>2.89533305168152</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>3.875</v>
       </c>
       <c r="G1136" t="n">
-        <v>2.89533281326294</v>
+        <v>2.89533305168152</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G1144" t="n">
-        <v>2.79819917678833</v>
+        <v>2.79819941520691</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G1150" t="n">
-        <v>2.65623450279236</v>
+        <v>2.65623426437378</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1151" t="n">
-        <v>2.64502668380737</v>
+        <v>2.64502692222595</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1152" t="n">
-        <v>2.63008284568787</v>
+        <v>2.63008308410645</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1154" t="n">
-        <v>2.60019612312317</v>
+        <v>2.60019564628601</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1158" t="n">
-        <v>2.62261128425598</v>
+        <v>2.62261152267456</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1160" t="n">
-        <v>2.50306224822998</v>
+        <v>2.5030620098114</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1163" t="n">
-        <v>2.4582314491272</v>
+        <v>2.45823097229004</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G1164" t="n">
-        <v>2.47691059112549</v>
+        <v>2.47691082954407</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G1165" t="n">
-        <v>2.47691059112549</v>
+        <v>2.47691082954407</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G1166" t="n">
-        <v>2.47691059112549</v>
+        <v>2.47691082954407</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1170" t="n">
-        <v>2.62261128425598</v>
+        <v>2.62261152267456</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1171" t="n">
-        <v>2.56283688545227</v>
+        <v>2.56283664703369</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1173" t="n">
-        <v>2.59272408485413</v>
+        <v>2.59272432327271</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G1174" t="n">
-        <v>2.55162858963013</v>
+        <v>2.55162882804871</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>3.35500001907349</v>
       </c>
       <c r="G1176" t="n">
-        <v>2.50679802894592</v>
+        <v>2.5067982673645</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1177" t="n">
-        <v>2.53294968605042</v>
+        <v>2.53294944763184</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1179" t="n">
-        <v>2.52547740936279</v>
+        <v>2.52547764778137</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1181" t="n">
-        <v>2.4582314491272</v>
+        <v>2.45823097229004</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1182" t="n">
-        <v>2.450758934021</v>
+        <v>2.45075917243958</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1183" t="n">
-        <v>2.450758934021</v>
+        <v>2.45075917243958</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1184" t="n">
-        <v>2.4582314491272</v>
+        <v>2.45823097229004</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G1185" t="n">
-        <v>2.45449542999268</v>
+        <v>2.4544951915741</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G1186" t="n">
-        <v>2.49932622909546</v>
+        <v>2.49932599067688</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>3.36500000953674</v>
       </c>
       <c r="G1187" t="n">
-        <v>2.51426982879639</v>
+        <v>2.51427006721497</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G1188" t="n">
-        <v>2.49185419082642</v>
+        <v>2.491854429245</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1189" t="n">
-        <v>2.4657027721405</v>
+        <v>2.46570301055908</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1193" t="n">
-        <v>2.51800560951233</v>
+        <v>2.51800584793091</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1195" t="n">
-        <v>2.52547740936279</v>
+        <v>2.52547764778137</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>3.36500000953674</v>
       </c>
       <c r="G1196" t="n">
-        <v>2.51426982879639</v>
+        <v>2.51427006721497</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>3.5</v>
       </c>
       <c r="G1197" t="n">
-        <v>2.61513924598694</v>
+        <v>2.61513948440552</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1199" t="n">
-        <v>2.50306224822998</v>
+        <v>2.5030620098114</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1200" t="n">
-        <v>2.4582314491272</v>
+        <v>2.45823097229004</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1203" t="n">
-        <v>2.41340017318726</v>
+        <v>2.41340041160583</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G1205" t="n">
-        <v>2.38724875450134</v>
+        <v>2.38724851608276</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G1207" t="n">
-        <v>2.37977719306946</v>
+        <v>2.37977695465088</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1209" t="n">
-        <v>2.36109757423401</v>
+        <v>2.36109733581543</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1210" t="n">
-        <v>2.3835129737854</v>
+        <v>2.38351273536682</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G1213" t="n">
-        <v>2.38724875450134</v>
+        <v>2.38724851608276</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1217" t="n">
-        <v>2.35362577438354</v>
+        <v>2.35362553596497</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1218" t="n">
-        <v>2.28264331817627</v>
+        <v>2.28264307975769</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1219" t="n">
-        <v>2.28264331817627</v>
+        <v>2.28264307975769</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1223" t="n">
-        <v>2.25649189949036</v>
+        <v>2.25649166107178</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1224" t="n">
-        <v>2.27143526077271</v>
+        <v>2.27143549919128</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>3.04500007629395</v>
       </c>
       <c r="G1226" t="n">
-        <v>2.27517151832581</v>
+        <v>2.27517175674438</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1228" t="n">
-        <v>2.19671702384949</v>
+        <v>2.19671726226807</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1231" t="n">
-        <v>2.28264331817627</v>
+        <v>2.28264307975769</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G1234" t="n">
-        <v>2.24528408050537</v>
+        <v>2.24528431892395</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1237" t="n">
-        <v>2.44328737258911</v>
+        <v>2.44328761100769</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1238" t="n">
-        <v>2.4657027721405</v>
+        <v>2.46570301055908</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G1241" t="n">
-        <v>2.49932622909546</v>
+        <v>2.49932599067688</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1243" t="n">
-        <v>2.53294968605042</v>
+        <v>2.53294944763184</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1252" t="n">
-        <v>2.60019612312317</v>
+        <v>2.60019564628601</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1253" t="n">
-        <v>2.59272408485413</v>
+        <v>2.59272432327271</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1256" t="n">
-        <v>2.57778024673462</v>
+        <v>2.5777804851532</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1257" t="n">
-        <v>2.55536508560181</v>
+        <v>2.55536484718323</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1260" t="n">
-        <v>2.55536508560181</v>
+        <v>2.55536484718323</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1262" t="n">
-        <v>2.63008284568787</v>
+        <v>2.63008308410645</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G1263" t="n">
-        <v>2.65623450279236</v>
+        <v>2.65623426437378</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1265" t="n">
-        <v>2.60019612312317</v>
+        <v>2.60019564628601</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1267" t="n">
-        <v>2.7496325969696</v>
+        <v>2.74963235855103</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1269" t="n">
-        <v>2.7346887588501</v>
+        <v>2.73468852043152</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G1270" t="n">
-        <v>2.71600914001465</v>
+        <v>2.71600937843323</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G1278" t="n">
-        <v>2.79819917678833</v>
+        <v>2.79819941520691</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1279" t="n">
-        <v>2.86918115615845</v>
+        <v>2.86918163299561</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G1282" t="n">
-        <v>2.813143491745</v>
+        <v>2.81314301490784</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1285" t="n">
-        <v>2.7346887588501</v>
+        <v>2.73468852043152</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1286" t="n">
-        <v>2.69732975959778</v>
+        <v>2.6973295211792</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1287" t="n">
-        <v>2.69732975959778</v>
+        <v>2.6973295211792</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1288" t="n">
-        <v>2.68985772132874</v>
+        <v>2.68985748291016</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G1292" t="n">
-        <v>2.73842453956604</v>
+        <v>2.73842477798462</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>3.6949999332428</v>
       </c>
       <c r="G1294" t="n">
-        <v>2.76083993911743</v>
+        <v>2.76084017753601</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1295" t="n">
-        <v>2.76457595825195</v>
+        <v>2.76457619667053</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G1299" t="n">
-        <v>2.79819917678833</v>
+        <v>2.79819941520691</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G1301" t="n">
-        <v>2.80567121505737</v>
+        <v>2.80567097663879</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G1305" t="n">
-        <v>2.730952501297</v>
+        <v>2.73095273971558</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G1306" t="n">
-        <v>2.71600914001465</v>
+        <v>2.71600937843323</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G1307" t="n">
-        <v>2.71600914001465</v>
+        <v>2.71600937843323</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G1312" t="n">
-        <v>2.71600914001465</v>
+        <v>2.71600937843323</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34507,7 +34507,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G1313" t="n">
-        <v>2.68612194061279</v>
+        <v>2.68612170219421</v>
       </c>
       <c r="H1313" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G1315" t="n">
-        <v>2.72348117828369</v>
+        <v>2.72348093986511</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1316" t="n">
-        <v>2.7496325969696</v>
+        <v>2.74963235855103</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G1321" t="n">
-        <v>2.87291789054871</v>
+        <v>2.87291765213013</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G1322" t="n">
-        <v>2.88786125183105</v>
+        <v>2.88786101341248</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>3.82500004768372</v>
       </c>
       <c r="G1323" t="n">
-        <v>2.85797381401062</v>
+        <v>2.8579740524292</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1324" t="n">
-        <v>2.82435035705566</v>
+        <v>2.82435059547424</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1326" t="n">
-        <v>2.83929443359375</v>
+        <v>2.83929419517517</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G1327" t="n">
-        <v>2.813143491745</v>
+        <v>2.81314301490784</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>3.81500005722046</v>
       </c>
       <c r="G1328" t="n">
-        <v>2.85050201416016</v>
+        <v>2.85050177574158</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G1330" t="n">
-        <v>2.88786125183105</v>
+        <v>2.88786101341248</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1335" t="n">
-        <v>2.86918115615845</v>
+        <v>2.86918163299561</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>3.875</v>
       </c>
       <c r="G1340" t="n">
-        <v>2.89533281326294</v>
+        <v>2.89533305168152</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G1342" t="n">
-        <v>2.88786125183105</v>
+        <v>2.88786101341248</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>3.93499994277954</v>
       </c>
       <c r="G1344" t="n">
-        <v>2.9401638507843</v>
+        <v>2.94016408920288</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1345" t="n">
-        <v>2.89159727096558</v>
+        <v>2.891597032547</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1346" t="n">
-        <v>2.93642830848694</v>
+        <v>2.93642807006836</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35391,7 +35391,7 @@
         <v>3.97499990463257</v>
       </c>
       <c r="G1347" t="n">
-        <v>2.97005128860474</v>
+        <v>2.97005105018616</v>
       </c>
       <c r="H1347" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>3.9449999332428</v>
       </c>
       <c r="G1348" t="n">
-        <v>2.94763565063477</v>
+        <v>2.94763612747192</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1349" t="n">
-        <v>3.04850506782532</v>
+        <v>3.0485053062439</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1351" t="n">
-        <v>3.03356194496155</v>
+        <v>3.03356170654297</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1352" t="n">
-        <v>2.99620270729065</v>
+        <v>2.99620294570923</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>4.05499982833862</v>
       </c>
       <c r="G1353" t="n">
-        <v>3.02982568740845</v>
+        <v>3.02982592582703</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -71248,6 +71248,32 @@
         <v>2.70000004768372</v>
       </c>
       <c r="H2726" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2727">
+      <c r="A2727" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B2727" t="n">
+        <v>301777</v>
+      </c>
+      <c r="C2727" t="n">
+        <v>2.6949999332428</v>
+      </c>
+      <c r="D2727" t="n">
+        <v>2.64499998092651</v>
+      </c>
+      <c r="E2727" t="n">
+        <v>2.65000009536743</v>
+      </c>
+      <c r="F2727" t="n">
+        <v>2.65000009536743</v>
+      </c>
+      <c r="G2727" t="n">
+        <v>2.65000009536743</v>
+      </c>
+      <c r="H2727" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ASC.MI.xlsx
+++ b/data/ASC.MI.xlsx
@@ -447,7 +447,7 @@
         <v>2.21799993515015</v>
       </c>
       <c r="G3" t="n">
-        <v>1.21558475494385</v>
+        <v>1.21558463573456</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G5" t="n">
-        <v>1.20571970939636</v>
+        <v>1.20571982860565</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>2.17600011825562</v>
       </c>
       <c r="G6" t="n">
-        <v>1.19256663322449</v>
+        <v>1.1925665140152</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>2.16400003433228</v>
       </c>
       <c r="G7" t="n">
-        <v>1.18598973751068</v>
+        <v>1.18598997592926</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>2.21799993515015</v>
       </c>
       <c r="G8" t="n">
-        <v>1.21558475494385</v>
+        <v>1.21558463573456</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G9" t="n">
-        <v>1.21120023727417</v>
+        <v>1.21120035648346</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>2.16599988937378</v>
       </c>
       <c r="G10" t="n">
-        <v>1.1870858669281</v>
+        <v>1.18708574771881</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G12" t="n">
-        <v>1.13447260856628</v>
+        <v>1.13447248935699</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>2.07599997520447</v>
       </c>
       <c r="G13" t="n">
-        <v>1.13776111602783</v>
+        <v>1.13776099681854</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>2.16400003433228</v>
       </c>
       <c r="G16" t="n">
-        <v>1.18598973751068</v>
+        <v>1.18598997592926</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G17" t="n">
-        <v>1.19475865364075</v>
+        <v>1.19475889205933</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>2.17400002479553</v>
       </c>
       <c r="G18" t="n">
-        <v>1.19147026538849</v>
+        <v>1.19147038459778</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>2.16199994087219</v>
       </c>
       <c r="G19" t="n">
-        <v>1.18489360809326</v>
+        <v>1.18489372730255</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G20" t="n">
-        <v>1.19475865364075</v>
+        <v>1.19475889205933</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>2.21399998664856</v>
       </c>
       <c r="G22" t="n">
-        <v>1.21339249610901</v>
+        <v>1.21339237689972</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>2.21799993515015</v>
       </c>
       <c r="G23" t="n">
-        <v>1.21558475494385</v>
+        <v>1.21558463573456</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G24" t="n">
-        <v>1.21120023727417</v>
+        <v>1.21120035648346</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G25" t="n">
-        <v>1.20023918151855</v>
+        <v>1.20023930072784</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>2.16400003433228</v>
       </c>
       <c r="G26" t="n">
-        <v>1.18598973751068</v>
+        <v>1.18598997592926</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G27" t="n">
-        <v>1.14543378353119</v>
+        <v>1.1454336643219</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G28" t="n">
-        <v>1.150914311409</v>
+        <v>1.15091419219971</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>2.09800004959106</v>
       </c>
       <c r="G29" t="n">
-        <v>1.14981818199158</v>
+        <v>1.14981830120087</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>2.09400010108948</v>
       </c>
       <c r="G31" t="n">
-        <v>1.14762616157532</v>
+        <v>1.14762604236603</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>2.1340000629425</v>
       </c>
       <c r="G32" t="n">
-        <v>1.16954815387726</v>
+        <v>1.16954827308655</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G33" t="n">
-        <v>1.16735589504242</v>
+        <v>1.167356133461</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G34" t="n">
-        <v>1.16735589504242</v>
+        <v>1.167356133461</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>2.14400005340576</v>
       </c>
       <c r="G36" t="n">
-        <v>1.17502892017365</v>
+        <v>1.17502880096436</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G38" t="n">
-        <v>1.16735589504242</v>
+        <v>1.167356133461</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G39" t="n">
-        <v>1.16735589504242</v>
+        <v>1.167356133461</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>2.17400002479553</v>
       </c>
       <c r="G40" t="n">
-        <v>1.19147026538849</v>
+        <v>1.19147038459778</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G41" t="n">
-        <v>1.19475865364075</v>
+        <v>1.19475889205933</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G42" t="n">
-        <v>1.20023918151855</v>
+        <v>1.20023930072784</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>2.23600006103516</v>
       </c>
       <c r="G43" t="n">
-        <v>1.22544980049133</v>
+        <v>1.22544991970062</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G44" t="n">
-        <v>1.22216141223907</v>
+        <v>1.22216153144836</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G45" t="n">
-        <v>1.22435367107391</v>
+        <v>1.22435343265533</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G46" t="n">
-        <v>1.2177768945694</v>
+        <v>1.21777701377869</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G48" t="n">
-        <v>1.20023918151855</v>
+        <v>1.20023930072784</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G49" t="n">
-        <v>1.21120023727417</v>
+        <v>1.21120035648346</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G50" t="n">
-        <v>1.20023918151855</v>
+        <v>1.20023930072784</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>2.25399994850159</v>
       </c>
       <c r="G53" t="n">
-        <v>1.23531472682953</v>
+        <v>1.23531448841095</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>2.2960000038147</v>
       </c>
       <c r="G56" t="n">
-        <v>1.25833308696747</v>
+        <v>1.25833284854889</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>2.29200005531311</v>
       </c>
       <c r="G57" t="n">
-        <v>1.25614082813263</v>
+        <v>1.25614094734192</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>2.28800010681152</v>
       </c>
       <c r="G62" t="n">
-        <v>1.2539484500885</v>
+        <v>1.25394856929779</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>2.29200005531311</v>
       </c>
       <c r="G63" t="n">
-        <v>1.25614082813263</v>
+        <v>1.25614094734192</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>2.29399991035461</v>
       </c>
       <c r="G64" t="n">
-        <v>1.25723683834076</v>
+        <v>1.25723671913147</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G65" t="n">
-        <v>1.26052522659302</v>
+        <v>1.26052534580231</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>2.27600002288818</v>
       </c>
       <c r="G66" t="n">
-        <v>1.24737179279327</v>
+        <v>1.24737191200256</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G69" t="n">
-        <v>1.26052522659302</v>
+        <v>1.26052534580231</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>2.33400011062622</v>
       </c>
       <c r="G72" t="n">
-        <v>1.27915918827057</v>
+        <v>1.27915906906128</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>2.34800004959106</v>
       </c>
       <c r="G74" t="n">
-        <v>1.28683185577393</v>
+        <v>1.28683197498322</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>2.34800004959106</v>
       </c>
       <c r="G75" t="n">
-        <v>1.28683185577393</v>
+        <v>1.28683197498322</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>2.33400011062622</v>
       </c>
       <c r="G76" t="n">
-        <v>1.27915918827057</v>
+        <v>1.27915906906128</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>2.32599997520447</v>
       </c>
       <c r="G78" t="n">
-        <v>1.27477467060089</v>
+        <v>1.2747745513916</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>2.32800006866455</v>
       </c>
       <c r="G79" t="n">
-        <v>1.27587080001831</v>
+        <v>1.2758709192276</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>2.39199995994568</v>
       </c>
       <c r="G83" t="n">
-        <v>1.31094634532928</v>
+        <v>1.31094610691071</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>2.31599998474121</v>
       </c>
       <c r="G94" t="n">
-        <v>1.35544550418854</v>
+        <v>1.35544526576996</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G95" t="n">
-        <v>1.35193395614624</v>
+        <v>1.35193371772766</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>2.34400010108948</v>
       </c>
       <c r="G98" t="n">
-        <v>1.37183248996735</v>
+        <v>1.37183237075806</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G103" t="n">
-        <v>1.41631162166595</v>
+        <v>1.41631186008453</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>2.41599988937378</v>
       </c>
       <c r="G104" t="n">
-        <v>1.41397035121918</v>
+        <v>1.41397047042847</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>2.46399998664856</v>
       </c>
       <c r="G106" t="n">
-        <v>1.44206273555756</v>
+        <v>1.44206261634827</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>2.44199991226196</v>
       </c>
       <c r="G108" t="n">
-        <v>1.42918694019318</v>
+        <v>1.42918705940247</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G109" t="n">
-        <v>1.43972158432007</v>
+        <v>1.43972170352936</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>2.43199992179871</v>
       </c>
       <c r="G110" t="n">
-        <v>1.42333471775055</v>
+        <v>1.42333459854126</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>2.5</v>
       </c>
       <c r="G111" t="n">
-        <v>1.46313166618347</v>
+        <v>1.46313178539276</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G112" t="n">
-        <v>1.52750968933105</v>
+        <v>1.52750957012177</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>2.59200000762939</v>
       </c>
       <c r="G114" t="n">
-        <v>1.51697516441345</v>
+        <v>1.51697492599487</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>2.5</v>
       </c>
       <c r="G115" t="n">
-        <v>1.46313166618347</v>
+        <v>1.46313178539276</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>2.5</v>
       </c>
       <c r="G116" t="n">
-        <v>1.46313166618347</v>
+        <v>1.46313178539276</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G118" t="n">
-        <v>1.43386912345886</v>
+        <v>1.43386924266815</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>2.52600002288818</v>
       </c>
       <c r="G119" t="n">
-        <v>1.47834837436676</v>
+        <v>1.47834825515747</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>2.59800004959106</v>
       </c>
       <c r="G120" t="n">
-        <v>1.52048683166504</v>
+        <v>1.52048671245575</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G121" t="n">
-        <v>1.52750968933105</v>
+        <v>1.52750957012177</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G125" t="n">
-        <v>1.44557428359985</v>
+        <v>1.44557416439056</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>2.53600001335144</v>
       </c>
       <c r="G126" t="n">
-        <v>1.48420095443726</v>
+        <v>1.48420083522797</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G127" t="n">
-        <v>1.51580452919006</v>
+        <v>1.51580464839935</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G128" t="n">
-        <v>1.58018243312836</v>
+        <v>1.58018255233765</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G129" t="n">
-        <v>1.58018243312836</v>
+        <v>1.58018255233765</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>2.67799997329712</v>
       </c>
       <c r="G130" t="n">
-        <v>1.56730675697327</v>
+        <v>1.56730687618256</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>2.58800005912781</v>
       </c>
       <c r="G131" t="n">
-        <v>1.51463425159454</v>
+        <v>1.51463413238525</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>2.67600011825562</v>
       </c>
       <c r="G132" t="n">
-        <v>1.56613624095917</v>
+        <v>1.56613636016846</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>2.69400000572205</v>
       </c>
       <c r="G133" t="n">
-        <v>1.57667052745819</v>
+        <v>1.57667076587677</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.69600009918213</v>
       </c>
       <c r="G134" t="n">
-        <v>1.57784140110016</v>
+        <v>1.57784128189087</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>2.69400000572205</v>
       </c>
       <c r="G135" t="n">
-        <v>1.57667052745819</v>
+        <v>1.57667076587677</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G136" t="n">
-        <v>1.58018243312836</v>
+        <v>1.58018255233765</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G137" t="n">
-        <v>1.58018243312836</v>
+        <v>1.58018255233765</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G138" t="n">
-        <v>1.58018243312836</v>
+        <v>1.58018255233765</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G139" t="n">
-        <v>1.58018243312836</v>
+        <v>1.58018255233765</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G140" t="n">
-        <v>1.58018243312836</v>
+        <v>1.58018255233765</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G141" t="n">
-        <v>1.58018243312836</v>
+        <v>1.58018255233765</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>2.78600001335144</v>
       </c>
       <c r="G142" t="n">
-        <v>1.63051414489746</v>
+        <v>1.63051426410675</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>2.79399991035461</v>
       </c>
       <c r="G143" t="n">
-        <v>1.63519597053528</v>
+        <v>1.63519632816315</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G146" t="n">
-        <v>1.60359239578247</v>
+        <v>1.60359251499176</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G149" t="n">
-        <v>1.65041279792786</v>
+        <v>1.65041255950928</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>2.78800010681152</v>
       </c>
       <c r="G154" t="n">
-        <v>1.63168466091156</v>
+        <v>1.63168442249298</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G157" t="n">
-        <v>1.66797029972076</v>
+        <v>1.66797006130219</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>2.89599990844727</v>
       </c>
       <c r="G158" t="n">
-        <v>1.69489192962646</v>
+        <v>1.69489181041718</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>2.87599992752075</v>
       </c>
       <c r="G159" t="n">
-        <v>1.68318676948547</v>
+        <v>1.68318688869476</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>2.83800005912781</v>
       </c>
       <c r="G161" t="n">
-        <v>1.66094708442688</v>
+        <v>1.66094744205475</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G162" t="n">
-        <v>1.65041279792786</v>
+        <v>1.65041255950928</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>2.83400011062622</v>
       </c>
       <c r="G163" t="n">
-        <v>1.65860617160797</v>
+        <v>1.65860641002655</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>2.83800005912781</v>
       </c>
       <c r="G164" t="n">
-        <v>1.66094708442688</v>
+        <v>1.66094744205475</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G165" t="n">
-        <v>1.67967522144318</v>
+        <v>1.67967510223389</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G166" t="n">
-        <v>1.68552792072296</v>
+        <v>1.68552780151367</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G167" t="n">
-        <v>1.67382252216339</v>
+        <v>1.67382276058197</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G170" t="n">
-        <v>1.67382252216339</v>
+        <v>1.67382276058197</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G171" t="n">
-        <v>1.66797029972076</v>
+        <v>1.66797006130219</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G173" t="n">
-        <v>1.66797029972076</v>
+        <v>1.66797006130219</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>2.70799994468689</v>
       </c>
       <c r="G176" t="n">
-        <v>1.58486413955688</v>
+        <v>1.58486449718475</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>2.82800006866455</v>
       </c>
       <c r="G177" t="n">
-        <v>1.65509462356567</v>
+        <v>1.65509474277496</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>2.75</v>
       </c>
       <c r="G178" t="n">
-        <v>1.60944497585297</v>
+        <v>1.60944509506226</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>2.6159999370575</v>
       </c>
       <c r="G179" t="n">
-        <v>1.53102099895477</v>
+        <v>1.53102123737335</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>2.6159999370575</v>
       </c>
       <c r="G180" t="n">
-        <v>1.53102099895477</v>
+        <v>1.53102123737335</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>2.6159999370575</v>
       </c>
       <c r="G181" t="n">
-        <v>1.53102099895477</v>
+        <v>1.53102123737335</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>2.6159999370575</v>
       </c>
       <c r="G182" t="n">
-        <v>1.53102099895477</v>
+        <v>1.53102123737335</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>2.64800000190735</v>
       </c>
       <c r="G183" t="n">
-        <v>1.54974913597107</v>
+        <v>1.54974925518036</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>2.6159999370575</v>
       </c>
       <c r="G184" t="n">
-        <v>1.53102099895477</v>
+        <v>1.53102123737335</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G185" t="n">
-        <v>1.52750968933105</v>
+        <v>1.52750957012177</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>2.60400009155273</v>
       </c>
       <c r="G186" t="n">
-        <v>1.52399826049805</v>
+        <v>1.52399790287018</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>2.64599990844727</v>
       </c>
       <c r="G187" t="n">
-        <v>1.54857861995697</v>
+        <v>1.54857873916626</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>2.6159999370575</v>
       </c>
       <c r="G188" t="n">
-        <v>1.53102099895477</v>
+        <v>1.53102123737335</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>2.6159999370575</v>
       </c>
       <c r="G190" t="n">
-        <v>1.53102099895477</v>
+        <v>1.53102123737335</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>2.66599988937378</v>
       </c>
       <c r="G191" t="n">
-        <v>1.56028366088867</v>
+        <v>1.56028354167938</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>2.68400001525879</v>
       </c>
       <c r="G192" t="n">
-        <v>1.57081818580627</v>
+        <v>1.57081806659698</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G194" t="n">
-        <v>1.53921473026276</v>
+        <v>1.53921461105347</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G195" t="n">
-        <v>1.55092000961304</v>
+        <v>1.55091977119446</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>2.6159999370575</v>
       </c>
       <c r="G196" t="n">
-        <v>1.53102099895477</v>
+        <v>1.53102123737335</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>2.64599990844727</v>
       </c>
       <c r="G197" t="n">
-        <v>1.54857861995697</v>
+        <v>1.54857873916626</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>2.6159999370575</v>
       </c>
       <c r="G198" t="n">
-        <v>1.53102099895477</v>
+        <v>1.53102123737335</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>2.61800003051758</v>
       </c>
       <c r="G199" t="n">
-        <v>1.53219151496887</v>
+        <v>1.53219163417816</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>2.6159999370575</v>
       </c>
       <c r="G200" t="n">
-        <v>1.53102099895477</v>
+        <v>1.53102123737335</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>2.61800003051758</v>
       </c>
       <c r="G201" t="n">
-        <v>1.53219151496887</v>
+        <v>1.53219163417816</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>2.62199997901917</v>
       </c>
       <c r="G202" t="n">
-        <v>1.53453290462494</v>
+        <v>1.53453278541565</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>2.62599992752075</v>
       </c>
       <c r="G203" t="n">
-        <v>1.53687345981598</v>
+        <v>1.53687381744385</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>2.66199994087219</v>
       </c>
       <c r="G204" t="n">
-        <v>1.55794262886047</v>
+        <v>1.55794274806976</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>2.67400002479553</v>
       </c>
       <c r="G205" t="n">
-        <v>1.56496596336365</v>
+        <v>1.56496572494507</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G206" t="n">
-        <v>1.56847739219666</v>
+        <v>1.56847727298737</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G207" t="n">
-        <v>1.58018243312836</v>
+        <v>1.58018255233765</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>2.68799996376038</v>
       </c>
       <c r="G208" t="n">
-        <v>1.57315909862518</v>
+        <v>1.57315921783447</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>2.62599992752075</v>
       </c>
       <c r="G210" t="n">
-        <v>1.53687345981598</v>
+        <v>1.53687381744385</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>2.62800002098083</v>
       </c>
       <c r="G212" t="n">
-        <v>1.53804421424866</v>
+        <v>1.53804433345795</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G213" t="n">
-        <v>1.56262493133545</v>
+        <v>1.56262481212616</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>2.66400003433228</v>
       </c>
       <c r="G214" t="n">
-        <v>1.55911326408386</v>
+        <v>1.55911302566528</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G215" t="n">
-        <v>1.55092000961304</v>
+        <v>1.55091977119446</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>2.65199995040894</v>
       </c>
       <c r="G216" t="n">
-        <v>1.55209028720856</v>
+        <v>1.55209016799927</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>2.65199995040894</v>
       </c>
       <c r="G217" t="n">
-        <v>1.55209028720856</v>
+        <v>1.55209016799927</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G218" t="n">
-        <v>1.55092000961304</v>
+        <v>1.55091977119446</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G219" t="n">
-        <v>1.55092000961304</v>
+        <v>1.55091977119446</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G220" t="n">
-        <v>1.55092000961304</v>
+        <v>1.55091977119446</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G221" t="n">
-        <v>1.53921473026276</v>
+        <v>1.53921461105347</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>2.58200001716614</v>
       </c>
       <c r="G222" t="n">
-        <v>1.51112258434296</v>
+        <v>1.51112246513367</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G224" t="n">
-        <v>1.52750968933105</v>
+        <v>1.52750957012177</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>2.49200010299683</v>
       </c>
       <c r="G225" t="n">
-        <v>1.45844984054565</v>
+        <v>1.45844960212708</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>2.42600011825562</v>
       </c>
       <c r="G227" t="n">
-        <v>1.41982328891754</v>
+        <v>1.41982305049896</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>2.43400001525879</v>
       </c>
       <c r="G228" t="n">
-        <v>1.42450499534607</v>
+        <v>1.42450511455536</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>2.40599989891052</v>
       </c>
       <c r="G229" t="n">
-        <v>1.40811812877655</v>
+        <v>1.40811800956726</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G230" t="n">
-        <v>1.48068916797638</v>
+        <v>1.48068928718567</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>2.57800006866455</v>
       </c>
       <c r="G231" t="n">
-        <v>1.50878131389618</v>
+        <v>1.50878143310547</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G233" t="n">
-        <v>1.45727932453156</v>
+        <v>1.45727920532227</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G234" t="n">
-        <v>1.42216420173645</v>
+        <v>1.42216432094574</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>2.45799994468689</v>
       </c>
       <c r="G235" t="n">
-        <v>1.43855118751526</v>
+        <v>1.43855130672455</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G241" t="n">
-        <v>1.49239432811737</v>
+        <v>1.49239456653595</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>2.58599996566772</v>
       </c>
       <c r="G245" t="n">
-        <v>1.51346325874329</v>
+        <v>1.51346349716187</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>2.60400009155273</v>
       </c>
       <c r="G247" t="n">
-        <v>1.52399826049805</v>
+        <v>1.52399790287018</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>2.68799996376038</v>
       </c>
       <c r="G248" t="n">
-        <v>1.57315909862518</v>
+        <v>1.57315921783447</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>2.65599989891052</v>
       </c>
       <c r="G249" t="n">
-        <v>1.55443096160889</v>
+        <v>1.55443120002747</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>2.65199995040894</v>
       </c>
       <c r="G250" t="n">
-        <v>1.55209028720856</v>
+        <v>1.55209016799927</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>2.67799997329712</v>
       </c>
       <c r="G251" t="n">
-        <v>1.56730675697327</v>
+        <v>1.56730687618256</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>2.68600010871887</v>
       </c>
       <c r="G253" t="n">
-        <v>1.57198894023895</v>
+        <v>1.57198905944824</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G254" t="n">
-        <v>1.59188759326935</v>
+        <v>1.59188735485077</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>2.72399997711182</v>
       </c>
       <c r="G257" t="n">
-        <v>1.59422850608826</v>
+        <v>1.59422826766968</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G259" t="n">
-        <v>1.65041279792786</v>
+        <v>1.65041255950928</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>2.78600001335144</v>
       </c>
       <c r="G260" t="n">
-        <v>1.63051414489746</v>
+        <v>1.63051426410675</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>2.75</v>
       </c>
       <c r="G261" t="n">
-        <v>1.60944497585297</v>
+        <v>1.60944509506226</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>2.74399995803833</v>
       </c>
       <c r="G262" t="n">
-        <v>1.60593354701996</v>
+        <v>1.6059330701828</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G266" t="n">
-        <v>1.59188759326935</v>
+        <v>1.59188735485077</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>2.72399997711182</v>
       </c>
       <c r="G267" t="n">
-        <v>1.59422850608826</v>
+        <v>1.59422826766968</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G268" t="n">
-        <v>1.60359239578247</v>
+        <v>1.60359251499176</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>2.73799991607666</v>
       </c>
       <c r="G269" t="n">
-        <v>1.60242211818695</v>
+        <v>1.60242187976837</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>2.75</v>
       </c>
       <c r="G271" t="n">
-        <v>1.60944497585297</v>
+        <v>1.60944509506226</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>2.78399991989136</v>
       </c>
       <c r="G274" t="n">
-        <v>1.62934339046478</v>
+        <v>1.62934350967407</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>2.75</v>
       </c>
       <c r="G275" t="n">
-        <v>1.60944497585297</v>
+        <v>1.60944509506226</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>2.75</v>
       </c>
       <c r="G276" t="n">
-        <v>1.60944497585297</v>
+        <v>1.60944509506226</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G277" t="n">
-        <v>1.62700259685516</v>
+        <v>1.62700235843658</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>2.72399997711182</v>
       </c>
       <c r="G279" t="n">
-        <v>1.59422850608826</v>
+        <v>1.59422826766968</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>2.86400008201599</v>
       </c>
       <c r="G280" t="n">
-        <v>1.67616379261017</v>
+        <v>1.67616415023804</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G281" t="n">
-        <v>1.66797029972076</v>
+        <v>1.66797006130219</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>2.85199999809265</v>
       </c>
       <c r="G282" t="n">
-        <v>1.66914105415344</v>
+        <v>1.66914093494415</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>2.82599997520447</v>
       </c>
       <c r="G283" t="n">
-        <v>1.65392446517944</v>
+        <v>1.65392434597015</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>2.82800006866455</v>
       </c>
       <c r="G284" t="n">
-        <v>1.65509462356567</v>
+        <v>1.65509474277496</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>2.83800005912781</v>
       </c>
       <c r="G285" t="n">
-        <v>1.66094708442688</v>
+        <v>1.66094744205475</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>2.80800008773804</v>
       </c>
       <c r="G286" t="n">
-        <v>1.64338994026184</v>
+        <v>1.64338958263397</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G287" t="n">
-        <v>1.67967522144318</v>
+        <v>1.67967510223389</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G288" t="n">
-        <v>1.67382252216339</v>
+        <v>1.67382276058197</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>2.88800001144409</v>
       </c>
       <c r="G290" t="n">
-        <v>1.69020986557007</v>
+        <v>1.69020998477936</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>2.86400008201599</v>
       </c>
       <c r="G291" t="n">
-        <v>1.67616379261017</v>
+        <v>1.67616415023804</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>2.83599996566772</v>
       </c>
       <c r="G292" t="n">
-        <v>1.65977668762207</v>
+        <v>1.65977656841278</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G293" t="n">
-        <v>1.69138050079346</v>
+        <v>1.69138038158417</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G294" t="n">
-        <v>1.69138050079346</v>
+        <v>1.69138038158417</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>2.89599990844727</v>
       </c>
       <c r="G297" t="n">
-        <v>1.69489192962646</v>
+        <v>1.69489181041718</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>2.86400008201599</v>
       </c>
       <c r="G298" t="n">
-        <v>1.67616379261017</v>
+        <v>1.67616415023804</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G299" t="n">
-        <v>1.69138050079346</v>
+        <v>1.69138038158417</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G300" t="n">
-        <v>1.72649550437927</v>
+        <v>1.72649526596069</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G301" t="n">
-        <v>1.72064316272736</v>
+        <v>1.72064292430878</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G302" t="n">
-        <v>1.74405324459076</v>
+        <v>1.74405312538147</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G303" t="n">
-        <v>1.77331566810608</v>
+        <v>1.77331578731537</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>3.05599999427795</v>
       </c>
       <c r="G304" t="n">
-        <v>1.78853249549866</v>
+        <v>1.78853225708008</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>3.09599995613098</v>
       </c>
       <c r="G306" t="n">
-        <v>1.81194221973419</v>
+        <v>1.81194233894348</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G307" t="n">
-        <v>1.80843079090118</v>
+        <v>1.80843102931976</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>3.15599989891052</v>
       </c>
       <c r="G308" t="n">
-        <v>1.84705770015717</v>
+        <v>1.84705758094788</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>3.21799993515015</v>
       </c>
       <c r="G310" t="n">
-        <v>1.88334310054779</v>
+        <v>1.88334321975708</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G311" t="n">
-        <v>1.90792393684387</v>
+        <v>1.90792381763458</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>3.29200005531311</v>
       </c>
       <c r="G312" t="n">
-        <v>1.92665219306946</v>
+        <v>1.92665195465088</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>3.32200002670288</v>
       </c>
       <c r="G313" t="n">
-        <v>1.94420945644379</v>
+        <v>1.94420969486237</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G316" t="n">
-        <v>1.9547438621521</v>
+        <v>1.95474410057068</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>3.48399996757507</v>
       </c>
       <c r="G323" t="n">
-        <v>2.03902053833008</v>
+        <v>2.0390202999115</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>3.50600004196167</v>
       </c>
       <c r="G324" t="n">
-        <v>2.05189633369446</v>
+        <v>2.0518958568573</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G325" t="n">
-        <v>2.06009006500244</v>
+        <v>2.06008958816528</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>3.52600002288818</v>
       </c>
       <c r="G326" t="n">
-        <v>2.06360125541687</v>
+        <v>2.06360077857971</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>3.5</v>
       </c>
       <c r="G327" t="n">
-        <v>2.04838442802429</v>
+        <v>2.04838466644287</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G328" t="n">
-        <v>2.0717945098877</v>
+        <v>2.07179474830627</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>3.53800010681152</v>
       </c>
       <c r="G335" t="n">
-        <v>2.07062411308289</v>
+        <v>2.07062435150146</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G336" t="n">
-        <v>2.10690975189209</v>
+        <v>2.10690999031067</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>3.58599996566772</v>
       </c>
       <c r="G337" t="n">
-        <v>2.09871602058411</v>
+        <v>2.09871625900269</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>3.59200000762939</v>
       </c>
       <c r="G339" t="n">
-        <v>2.10222768783569</v>
+        <v>2.10222792625427</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>3.62199997901917</v>
       </c>
       <c r="G340" t="n">
-        <v>2.11978554725647</v>
+        <v>2.11978530883789</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>3.71199989318848</v>
       </c>
       <c r="G343" t="n">
-        <v>2.1724579334259</v>
+        <v>2.17245769500732</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>3.64599990844727</v>
       </c>
       <c r="G345" t="n">
-        <v>2.24046397209167</v>
+        <v>2.24046349525452</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>3.62599992752075</v>
       </c>
       <c r="G346" t="n">
-        <v>2.22817397117615</v>
+        <v>2.22817373275757</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>3.60599994659424</v>
       </c>
       <c r="G347" t="n">
-        <v>2.21588373184204</v>
+        <v>2.21588349342346</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>3.57800006866455</v>
       </c>
       <c r="G348" t="n">
-        <v>2.19867777824402</v>
+        <v>2.1986780166626</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>3.48600006103516</v>
       </c>
       <c r="G349" t="n">
-        <v>2.14214396476746</v>
+        <v>2.14214372634888</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>3.48200011253357</v>
       </c>
       <c r="G352" t="n">
-        <v>2.13968586921692</v>
+        <v>2.1396861076355</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G354" t="n">
-        <v>2.18761658668518</v>
+        <v>2.18761682510376</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>3.6340000629425</v>
       </c>
       <c r="G357" t="n">
-        <v>2.23308968544006</v>
+        <v>2.23308992385864</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G358" t="n">
-        <v>2.24906706809998</v>
+        <v>2.2490668296814</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>3.55599999427795</v>
       </c>
       <c r="G360" t="n">
-        <v>2.1851589679718</v>
+        <v>2.18515872955322</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>3.61400008201599</v>
       </c>
       <c r="G361" t="n">
-        <v>2.22079968452454</v>
+        <v>2.22080016136169</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G366" t="n">
-        <v>2.21219658851624</v>
+        <v>2.21219682693481</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G367" t="n">
-        <v>2.23063182830811</v>
+        <v>2.23063158988953</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G370" t="n">
-        <v>2.21219658851624</v>
+        <v>2.21219682693481</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G372" t="n">
-        <v>2.23063182830811</v>
+        <v>2.23063158988953</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>3.71799993515015</v>
       </c>
       <c r="G374" t="n">
-        <v>2.28470754623413</v>
+        <v>2.28470778465271</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>3.57399988174438</v>
       </c>
       <c r="G378" t="n">
-        <v>2.19621992111206</v>
+        <v>2.19621968269348</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G380" t="n">
-        <v>2.18147206306458</v>
+        <v>2.181471824646</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>3.48200011253357</v>
       </c>
       <c r="G383" t="n">
-        <v>2.13968586921692</v>
+        <v>2.1396861076355</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>3.48399996757507</v>
       </c>
       <c r="G387" t="n">
-        <v>2.14091491699219</v>
+        <v>2.14091467857361</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G392" t="n">
-        <v>2.14460182189941</v>
+        <v>2.14460229873657</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>3.49600005149841</v>
       </c>
       <c r="G393" t="n">
-        <v>2.14828896522522</v>
+        <v>2.14828872680664</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G402" t="n">
-        <v>2.10773205757141</v>
+        <v>2.10773229598999</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G404" t="n">
-        <v>2.12002205848694</v>
+        <v>2.12002182006836</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>3.46399998664856</v>
       </c>
       <c r="G405" t="n">
-        <v>2.12862491607666</v>
+        <v>2.12862515449524</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G406" t="n">
-        <v>2.10773205757141</v>
+        <v>2.10773229598999</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G408" t="n">
-        <v>2.18147206306458</v>
+        <v>2.181471824646</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>3.58200001716614</v>
       </c>
       <c r="G409" t="n">
-        <v>2.20113587379456</v>
+        <v>2.20113611221313</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>3.59800004959106</v>
       </c>
       <c r="G410" t="n">
-        <v>2.21096777915955</v>
+        <v>2.21096754074097</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>3.57599997520447</v>
       </c>
       <c r="G411" t="n">
-        <v>2.19744920730591</v>
+        <v>2.19744873046875</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G412" t="n">
-        <v>2.18761658668518</v>
+        <v>2.18761682510376</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>3.58200001716614</v>
       </c>
       <c r="G413" t="n">
-        <v>2.20113587379456</v>
+        <v>2.20113611221313</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>3.5460000038147</v>
       </c>
       <c r="G414" t="n">
-        <v>2.17901420593262</v>
+        <v>2.17901372909546</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>3.55599999427795</v>
       </c>
       <c r="G415" t="n">
-        <v>2.1851589679718</v>
+        <v>2.18515872955322</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G416" t="n">
-        <v>2.16303658485413</v>
+        <v>2.16303682327271</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>3.53800010681152</v>
       </c>
       <c r="G419" t="n">
-        <v>2.17409801483154</v>
+        <v>2.17409825325012</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>3.4760000705719</v>
       </c>
       <c r="G420" t="n">
-        <v>2.13599920272827</v>
+        <v>2.13599896430969</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G421" t="n">
-        <v>2.14460182189941</v>
+        <v>2.14460229873657</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G422" t="n">
-        <v>2.14460182189941</v>
+        <v>2.14460229873657</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G423" t="n">
-        <v>2.14460182189941</v>
+        <v>2.14460229873657</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G425" t="n">
-        <v>2.16303658485413</v>
+        <v>2.16303682327271</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G426" t="n">
-        <v>2.14460182189941</v>
+        <v>2.14460229873657</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>3.54399991035461</v>
       </c>
       <c r="G427" t="n">
-        <v>2.17778491973877</v>
+        <v>2.17778468132019</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G431" t="n">
-        <v>2.218341588974</v>
+        <v>2.21834206581116</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>3.61400008201599</v>
       </c>
       <c r="G432" t="n">
-        <v>2.22079968452454</v>
+        <v>2.22080016136169</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G436" t="n">
-        <v>2.218341588974</v>
+        <v>2.21834206581116</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>3.59800004959106</v>
       </c>
       <c r="G437" t="n">
-        <v>2.21096777915955</v>
+        <v>2.21096754074097</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G439" t="n">
-        <v>2.18147206306458</v>
+        <v>2.181471824646</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>3.53200006484985</v>
       </c>
       <c r="G440" t="n">
-        <v>2.1704113483429</v>
+        <v>2.17041087150574</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>3.53399991989136</v>
       </c>
       <c r="G442" t="n">
-        <v>2.17163991928101</v>
+        <v>2.17163968086243</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G446" t="n">
-        <v>2.14460182189941</v>
+        <v>2.14460229873657</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>3.51399993896484</v>
       </c>
       <c r="G447" t="n">
-        <v>2.15934991836548</v>
+        <v>2.15934944152832</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>3.50600004196167</v>
       </c>
       <c r="G448" t="n">
-        <v>2.15443420410156</v>
+        <v>2.15443396568298</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G449" t="n">
-        <v>2.16303658485413</v>
+        <v>2.16303682327271</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G451" t="n">
-        <v>2.21219658851624</v>
+        <v>2.21219682693481</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G452" t="n">
-        <v>2.23063182830811</v>
+        <v>2.23063158988953</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G454" t="n">
-        <v>2.23063182830811</v>
+        <v>2.23063158988953</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>3.61400008201599</v>
       </c>
       <c r="G455" t="n">
-        <v>2.22079968452454</v>
+        <v>2.22080016136169</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>3.57399988174438</v>
       </c>
       <c r="G456" t="n">
-        <v>2.19621992111206</v>
+        <v>2.19621968269348</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G457" t="n">
-        <v>2.16303658485413</v>
+        <v>2.16303682327271</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>3.60599994659424</v>
       </c>
       <c r="G458" t="n">
-        <v>2.21588373184204</v>
+        <v>2.21588349342346</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>3.60400009155273</v>
       </c>
       <c r="G459" t="n">
-        <v>2.21465468406677</v>
+        <v>2.21465492248535</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G463" t="n">
-        <v>2.18761658668518</v>
+        <v>2.18761682510376</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>3.60800004005432</v>
       </c>
       <c r="G464" t="n">
-        <v>2.21711301803589</v>
+        <v>2.21711277961731</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>3.56399989128113</v>
       </c>
       <c r="G465" t="n">
-        <v>2.19007468223572</v>
+        <v>2.1900749206543</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>3.57599997520447</v>
       </c>
       <c r="G466" t="n">
-        <v>2.19744920730591</v>
+        <v>2.19744873046875</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>3.60599994659424</v>
       </c>
       <c r="G470" t="n">
-        <v>2.21588373184204</v>
+        <v>2.21588349342346</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>3.81399989128113</v>
       </c>
       <c r="G474" t="n">
-        <v>2.34369969367981</v>
+        <v>2.34369945526123</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G480" t="n">
-        <v>2.24906706809998</v>
+        <v>2.2490668296814</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>3.60400009155273</v>
       </c>
       <c r="G482" t="n">
-        <v>2.21465468406677</v>
+        <v>2.21465492248535</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>3.57599997520447</v>
       </c>
       <c r="G483" t="n">
-        <v>2.19744920730591</v>
+        <v>2.19744873046875</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G485" t="n">
-        <v>2.22448706626892</v>
+        <v>2.22448682785034</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G486" t="n">
-        <v>2.24906706809998</v>
+        <v>2.2490668296814</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>3.65599989891052</v>
       </c>
       <c r="G487" t="n">
-        <v>2.24660849571228</v>
+        <v>2.24660873413086</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>3.60400009155273</v>
       </c>
       <c r="G489" t="n">
-        <v>2.21465468406677</v>
+        <v>2.21465492248535</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G490" t="n">
-        <v>2.21219658851624</v>
+        <v>2.21219682693481</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G491" t="n">
-        <v>2.24906706809998</v>
+        <v>2.2490668296814</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>3.72199988365173</v>
       </c>
       <c r="G492" t="n">
-        <v>2.28716588020325</v>
+        <v>2.28716564178467</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G494" t="n">
-        <v>2.27364683151245</v>
+        <v>2.27364730834961</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>3.67400002479553</v>
       </c>
       <c r="G495" t="n">
-        <v>2.25766944885254</v>
+        <v>2.25767016410828</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>3.65199995040894</v>
       </c>
       <c r="G496" t="n">
-        <v>2.24415063858032</v>
+        <v>2.24415111541748</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>3.68600010871887</v>
       </c>
       <c r="G497" t="n">
-        <v>2.26504373550415</v>
+        <v>2.26504349708557</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G498" t="n">
-        <v>2.24906706809998</v>
+        <v>2.2490668296814</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G499" t="n">
-        <v>2.23063182830811</v>
+        <v>2.23063158988953</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G500" t="n">
-        <v>2.19990658760071</v>
+        <v>2.19990682601929</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G503" t="n">
-        <v>2.23063182830811</v>
+        <v>2.23063158988953</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>3.62599992752075</v>
       </c>
       <c r="G504" t="n">
-        <v>2.22817397117615</v>
+        <v>2.22817373275757</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>3.58200001716614</v>
       </c>
       <c r="G505" t="n">
-        <v>2.20113587379456</v>
+        <v>2.20113611221313</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G507" t="n">
-        <v>2.22448706626892</v>
+        <v>2.22448682785034</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>3.58200001716614</v>
       </c>
       <c r="G509" t="n">
-        <v>2.20113587379456</v>
+        <v>2.20113611221313</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>3.5460000038147</v>
       </c>
       <c r="G511" t="n">
-        <v>2.17901420593262</v>
+        <v>2.17901372909546</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G519" t="n">
-        <v>2.21219658851624</v>
+        <v>2.21219682693481</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G520" t="n">
-        <v>2.24906706809998</v>
+        <v>2.2490668296814</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G521" t="n">
-        <v>2.26135659217834</v>
+        <v>2.26135683059692</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G523" t="n">
-        <v>2.25521183013916</v>
+        <v>2.25521159172058</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G528" t="n">
-        <v>2.23063182830811</v>
+        <v>2.23063158988953</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G529" t="n">
-        <v>2.22448706626892</v>
+        <v>2.22448682785034</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G530" t="n">
-        <v>2.22448706626892</v>
+        <v>2.22448682785034</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G532" t="n">
-        <v>2.20297932624817</v>
+        <v>2.20297956466675</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G533" t="n">
-        <v>2.18147206306458</v>
+        <v>2.181471824646</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G534" t="n">
-        <v>2.18147206306458</v>
+        <v>2.181471824646</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G535" t="n">
-        <v>2.12002205848694</v>
+        <v>2.12002182006836</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>3.25</v>
       </c>
       <c r="G538" t="n">
-        <v>1.99712204933167</v>
+        <v>1.99712193012238</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G539" t="n">
-        <v>1.96947002410889</v>
+        <v>1.96946954727173</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G540" t="n">
-        <v>1.93567264080048</v>
+        <v>1.93567228317261</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>3.25</v>
       </c>
       <c r="G541" t="n">
-        <v>1.99712204933167</v>
+        <v>1.99712193012238</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G542" t="n">
-        <v>1.98483216762543</v>
+        <v>1.98483180999756</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G545" t="n">
-        <v>2.00941228866577</v>
+        <v>2.00941205024719</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G546" t="n">
-        <v>1.98483216762543</v>
+        <v>1.98483180999756</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>3.25</v>
       </c>
       <c r="G547" t="n">
-        <v>1.99712204933167</v>
+        <v>1.99712193012238</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G548" t="n">
-        <v>2.01555681228638</v>
+        <v>2.01555705070496</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G552" t="n">
-        <v>1.92645490169525</v>
+        <v>1.92645466327667</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G553" t="n">
-        <v>1.91723740100861</v>
+        <v>1.91723716259003</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G554" t="n">
-        <v>1.91723740100861</v>
+        <v>1.91723716259003</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G555" t="n">
-        <v>1.88036739826202</v>
+        <v>1.88036727905273</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G556" t="n">
-        <v>1.88036739826202</v>
+        <v>1.88036727905273</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G557" t="n">
-        <v>1.91416478157043</v>
+        <v>1.91416442394257</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G558" t="n">
-        <v>1.92338252067566</v>
+        <v>1.92338240146637</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G559" t="n">
-        <v>1.92338252067566</v>
+        <v>1.92338240146637</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G560" t="n">
-        <v>1.94489002227783</v>
+        <v>1.94488978385925</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G561" t="n">
-        <v>1.98175990581512</v>
+        <v>1.98175966739655</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G564" t="n">
-        <v>1.96639716625214</v>
+        <v>1.96639692783356</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G565" t="n">
-        <v>1.97254228591919</v>
+        <v>1.9725421667099</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G566" t="n">
-        <v>2.018630027771</v>
+        <v>2.01862978935242</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G567" t="n">
-        <v>2.018630027771</v>
+        <v>2.01862978935242</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>3.25</v>
       </c>
       <c r="G569" t="n">
-        <v>1.99712204933167</v>
+        <v>1.99712193012238</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G570" t="n">
-        <v>1.96947002410889</v>
+        <v>1.96946954727173</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G571" t="n">
-        <v>1.95717942714691</v>
+        <v>1.95717966556549</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G572" t="n">
-        <v>1.96025240421295</v>
+        <v>1.96025204658508</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G573" t="n">
-        <v>1.99404954910278</v>
+        <v>1.99404978752136</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>3.25</v>
       </c>
       <c r="G575" t="n">
-        <v>1.99712204933167</v>
+        <v>1.99712193012238</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G576" t="n">
-        <v>1.97254228591919</v>
+        <v>1.9725421667099</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G578" t="n">
-        <v>2.018630027771</v>
+        <v>2.01862978935242</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G580" t="n">
-        <v>2.01555681228638</v>
+        <v>2.01555705070496</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G582" t="n">
-        <v>2.00941228866577</v>
+        <v>2.00941205024719</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G583" t="n">
-        <v>2.01248478889465</v>
+        <v>2.01248455047607</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>3.32500004768372</v>
       </c>
       <c r="G590" t="n">
-        <v>2.04320979118347</v>
+        <v>2.04320931434631</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G593" t="n">
-        <v>2.0462818145752</v>
+        <v>2.04628229141235</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G597" t="n">
-        <v>2.15381932258606</v>
+        <v>2.15381979942322</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G599" t="n">
-        <v>2.13762521743774</v>
+        <v>2.13762545585632</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G600" t="n">
-        <v>2.13762521743774</v>
+        <v>2.13762545585632</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G603" t="n">
-        <v>2.11171460151672</v>
+        <v>2.1117148399353</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G605" t="n">
-        <v>2.02750539779663</v>
+        <v>2.02750515937805</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G606" t="n">
-        <v>2.02750539779663</v>
+        <v>2.02750515937805</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G608" t="n">
-        <v>2.01131105422974</v>
+        <v>2.01131081581116</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G609" t="n">
-        <v>2.00483369827271</v>
+        <v>2.00483298301697</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G612" t="n">
-        <v>1.97892284393311</v>
+        <v>1.9789229631424</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G613" t="n">
-        <v>1.94653475284576</v>
+        <v>1.94653427600861</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>2.875</v>
       </c>
       <c r="G614" t="n">
-        <v>1.86232507228851</v>
+        <v>1.86232495307922</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G615" t="n">
-        <v>1.91090726852417</v>
+        <v>1.91090774536133</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G616" t="n">
-        <v>1.94653475284576</v>
+        <v>1.94653427600861</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G617" t="n">
-        <v>1.95301234722137</v>
+        <v>1.95301222801208</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G621" t="n">
-        <v>1.94653475284576</v>
+        <v>1.94653427600861</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G622" t="n">
-        <v>1.90766859054565</v>
+        <v>1.90766847133636</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G623" t="n">
-        <v>1.97568392753601</v>
+        <v>1.97568368911743</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G624" t="n">
-        <v>1.98216164112091</v>
+        <v>1.98216140270233</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G625" t="n">
-        <v>1.95301234722137</v>
+        <v>1.95301222801208</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G626" t="n">
-        <v>1.98216164112091</v>
+        <v>1.98216140270233</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>2.97499990463257</v>
       </c>
       <c r="G627" t="n">
-        <v>1.92710161209106</v>
+        <v>1.92710137367249</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>2.97499990463257</v>
       </c>
       <c r="G629" t="n">
-        <v>1.92710161209106</v>
+        <v>1.92710137367249</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G630" t="n">
-        <v>1.94005680084229</v>
+        <v>1.94005703926086</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G631" t="n">
-        <v>1.89147436618805</v>
+        <v>1.89147448539734</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G633" t="n">
-        <v>1.91090726852417</v>
+        <v>1.91090774536133</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G638" t="n">
-        <v>1.90766859054565</v>
+        <v>1.90766847133636</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G640" t="n">
-        <v>1.89795207977295</v>
+        <v>1.89795219898224</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>2.97499990463257</v>
       </c>
       <c r="G641" t="n">
-        <v>1.92710161209106</v>
+        <v>1.92710137367249</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G642" t="n">
-        <v>1.94005680084229</v>
+        <v>1.94005703926086</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G644" t="n">
-        <v>1.89795207977295</v>
+        <v>1.89795219898224</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>2.91499996185303</v>
       </c>
       <c r="G645" t="n">
-        <v>1.88823568820953</v>
+        <v>1.88823580741882</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>2.88499999046326</v>
       </c>
       <c r="G647" t="n">
-        <v>1.8688029050827</v>
+        <v>1.86880278587341</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>2.86500000953674</v>
       </c>
       <c r="G648" t="n">
-        <v>1.85584735870361</v>
+        <v>1.8558474779129</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G651" t="n">
-        <v>1.87851929664612</v>
+        <v>1.87851917743683</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G653" t="n">
-        <v>1.85260856151581</v>
+        <v>1.8526086807251</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G654" t="n">
-        <v>1.84613060951233</v>
+        <v>1.8461309671402</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G655" t="n">
-        <v>1.87851929664612</v>
+        <v>1.87851917743683</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G657" t="n">
-        <v>2.04046082496643</v>
+        <v>2.04046058654785</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G658" t="n">
-        <v>2.07608771324158</v>
+        <v>2.076087474823</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>3.35500001907349</v>
       </c>
       <c r="G661" t="n">
-        <v>2.17325258255005</v>
+        <v>2.17325234413147</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>3.26500010490417</v>
       </c>
       <c r="G663" t="n">
-        <v>2.11495327949524</v>
+        <v>2.11495351791382</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G664" t="n">
-        <v>2.11819243431091</v>
+        <v>2.11819219589233</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>3.25</v>
       </c>
       <c r="G665" t="n">
-        <v>2.10523676872253</v>
+        <v>2.10523700714111</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G666" t="n">
-        <v>2.06960988044739</v>
+        <v>2.06961035728455</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G667" t="n">
-        <v>2.03074431419373</v>
+        <v>2.03074383735657</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G668" t="n">
-        <v>2.00807237625122</v>
+        <v>2.00807213783264</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G669" t="n">
-        <v>2.02750539779663</v>
+        <v>2.02750515937805</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G670" t="n">
-        <v>1.95949006080627</v>
+        <v>1.95948994159698</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G671" t="n">
-        <v>1.98216164112091</v>
+        <v>1.98216140270233</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G675" t="n">
-        <v>1.99187815189362</v>
+        <v>1.99187803268433</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G676" t="n">
-        <v>2.00483369827271</v>
+        <v>2.00483298301697</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G677" t="n">
-        <v>1.99835586547852</v>
+        <v>1.99835574626923</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G678" t="n">
-        <v>1.98216164112091</v>
+        <v>1.98216140270233</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G679" t="n">
-        <v>2.01454925537109</v>
+        <v>2.01454973220825</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G680" t="n">
-        <v>2.01454925537109</v>
+        <v>2.01454973220825</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G681" t="n">
-        <v>2.01454925537109</v>
+        <v>2.01454973220825</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>3.125</v>
       </c>
       <c r="G682" t="n">
-        <v>2.02426600456238</v>
+        <v>2.02426648139954</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G683" t="n">
-        <v>2.01454925537109</v>
+        <v>2.01454973220825</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G684" t="n">
-        <v>2.01131105422974</v>
+        <v>2.01131081581116</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G687" t="n">
-        <v>2.02750539779663</v>
+        <v>2.02750515937805</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G688" t="n">
-        <v>2.02750539779663</v>
+        <v>2.02750515937805</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G689" t="n">
-        <v>2.05017709732056</v>
+        <v>2.0501766204834</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G690" t="n">
-        <v>2.04693818092346</v>
+        <v>2.04693794250488</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G695" t="n">
-        <v>2.04693818092346</v>
+        <v>2.04693794250488</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G697" t="n">
-        <v>2.04693818092346</v>
+        <v>2.04693794250488</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G698" t="n">
-        <v>2.04693818092346</v>
+        <v>2.04693794250488</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G699" t="n">
-        <v>2.04693818092346</v>
+        <v>2.04693794250488</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G700" t="n">
-        <v>2.01454925537109</v>
+        <v>2.01454973220825</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G701" t="n">
-        <v>1.96272873878479</v>
+        <v>1.96272850036621</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>2.97499990463257</v>
       </c>
       <c r="G703" t="n">
-        <v>1.92710161209106</v>
+        <v>1.92710137367249</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>2.97499990463257</v>
       </c>
       <c r="G704" t="n">
-        <v>1.92710161209106</v>
+        <v>1.92710137367249</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G705" t="n">
-        <v>1.95301234722137</v>
+        <v>1.95301222801208</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G708" t="n">
-        <v>1.90766859054565</v>
+        <v>1.90766847133636</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G709" t="n">
-        <v>1.95301234722137</v>
+        <v>1.95301222801208</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G710" t="n">
-        <v>1.91738522052765</v>
+        <v>1.91738498210907</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G712" t="n">
-        <v>1.90766859054565</v>
+        <v>1.90766847133636</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G713" t="n">
-        <v>1.96272873878479</v>
+        <v>1.96272850036621</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G714" t="n">
-        <v>1.99835586547852</v>
+        <v>1.99835574626923</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G715" t="n">
-        <v>1.98216164112091</v>
+        <v>1.98216140270233</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>2.97499990463257</v>
       </c>
       <c r="G717" t="n">
-        <v>1.92710161209106</v>
+        <v>1.92710137367249</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>2.875</v>
       </c>
       <c r="G718" t="n">
-        <v>1.86232507228851</v>
+        <v>1.86232495307922</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G720" t="n">
-        <v>1.84613060951233</v>
+        <v>1.8461309671402</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G724" t="n">
-        <v>1.87851929664612</v>
+        <v>1.87851917743683</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G725" t="n">
-        <v>1.88499677181244</v>
+        <v>1.88499665260315</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>2.97499990463257</v>
       </c>
       <c r="G726" t="n">
-        <v>1.92710161209106</v>
+        <v>1.92710137367249</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G727" t="n">
-        <v>1.97568392753601</v>
+        <v>1.97568368911743</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G730" t="n">
-        <v>1.99835586547852</v>
+        <v>1.99835574626923</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G731" t="n">
-        <v>1.97568392753601</v>
+        <v>1.97568368911743</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G732" t="n">
-        <v>1.97568392753601</v>
+        <v>1.97568368911743</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G734" t="n">
-        <v>1.96272873878479</v>
+        <v>1.96272850036621</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G736" t="n">
-        <v>1.96920597553253</v>
+        <v>1.96920621395111</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G738" t="n">
-        <v>1.97568392753601</v>
+        <v>1.97568368911743</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G739" t="n">
-        <v>1.94977355003357</v>
+        <v>1.94977331161499</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G741" t="n">
-        <v>1.97568392753601</v>
+        <v>1.97568368911743</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G743" t="n">
-        <v>1.98216164112091</v>
+        <v>1.98216140270233</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G746" t="n">
-        <v>2.00483369827271</v>
+        <v>2.00483298301697</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G747" t="n">
-        <v>1.99835586547852</v>
+        <v>1.99835574626923</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G750" t="n">
-        <v>1.99835586547852</v>
+        <v>1.99835574626923</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G751" t="n">
-        <v>1.99187815189362</v>
+        <v>1.99187803268433</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G752" t="n">
-        <v>1.99835586547852</v>
+        <v>1.99835574626923</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G755" t="n">
-        <v>2.01454925537109</v>
+        <v>2.01454973220825</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>3.125</v>
       </c>
       <c r="G756" t="n">
-        <v>2.02426600456238</v>
+        <v>2.02426648139954</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G758" t="n">
-        <v>1.99187815189362</v>
+        <v>1.99187803268433</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G761" t="n">
-        <v>1.99187815189362</v>
+        <v>1.99187803268433</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G763" t="n">
-        <v>2.01454925537109</v>
+        <v>2.01454973220825</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>3.09500002861023</v>
       </c>
       <c r="G764" t="n">
-        <v>2.00483369827271</v>
+        <v>2.00483298301697</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G766" t="n">
-        <v>2.1279091835022</v>
+        <v>2.12790894508362</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G768" t="n">
-        <v>2.08580422401428</v>
+        <v>2.0858039855957</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G769" t="n">
-        <v>2.06960988044739</v>
+        <v>2.06961035728455</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G770" t="n">
-        <v>2.08580422401428</v>
+        <v>2.0858039855957</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G771" t="n">
-        <v>2.06960988044739</v>
+        <v>2.06961035728455</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G774" t="n">
-        <v>2.05017709732056</v>
+        <v>2.0501766204834</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G776" t="n">
-        <v>2.06313180923462</v>
+        <v>2.06313228607178</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G778" t="n">
-        <v>2.06313180923462</v>
+        <v>2.06313228607178</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G779" t="n">
-        <v>2.07608771324158</v>
+        <v>2.076087474823</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G780" t="n">
-        <v>2.07932639122009</v>
+        <v>2.07932662963867</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G781" t="n">
-        <v>2.07932639122009</v>
+        <v>2.07932662963867</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>3.21499991416931</v>
       </c>
       <c r="G784" t="n">
-        <v>2.08256530761719</v>
+        <v>2.08256554603577</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G785" t="n">
-        <v>2.08580422401428</v>
+        <v>2.0858039855957</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>3.21499991416931</v>
       </c>
       <c r="G786" t="n">
-        <v>2.08256530761719</v>
+        <v>2.08256554603577</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>3.25</v>
       </c>
       <c r="G788" t="n">
-        <v>2.10523676872253</v>
+        <v>2.10523700714111</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G790" t="n">
-        <v>2.11171460151672</v>
+        <v>2.1117148399353</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>3.25</v>
       </c>
       <c r="G791" t="n">
-        <v>2.10523676872253</v>
+        <v>2.10523700714111</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G793" t="n">
-        <v>2.11819243431091</v>
+        <v>2.11819219589233</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G794" t="n">
-        <v>2.11171460151672</v>
+        <v>2.1117148399353</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G795" t="n">
-        <v>2.12466955184937</v>
+        <v>2.12466979026794</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G796" t="n">
-        <v>2.13762521743774</v>
+        <v>2.13762545585632</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>3.3050000667572</v>
       </c>
       <c r="G797" t="n">
-        <v>2.14086365699768</v>
+        <v>2.14086413383484</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G798" t="n">
-        <v>2.1279091835022</v>
+        <v>2.12790894508362</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G799" t="n">
-        <v>2.12466955184937</v>
+        <v>2.12466979026794</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G800" t="n">
-        <v>2.14410281181335</v>
+        <v>2.14410257339478</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G802" t="n">
-        <v>2.1829686164856</v>
+        <v>2.18296885490417</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G807" t="n">
-        <v>2.19916296005249</v>
+        <v>2.19916319847107</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G809" t="n">
-        <v>2.1829686164856</v>
+        <v>2.18296885490417</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>3.375</v>
       </c>
       <c r="G810" t="n">
-        <v>2.18620777130127</v>
+        <v>2.18620753288269</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G812" t="n">
-        <v>2.24126744270325</v>
+        <v>2.24126768112183</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G814" t="n">
-        <v>2.24774527549744</v>
+        <v>2.24774551391602</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G815" t="n">
-        <v>2.21211838722229</v>
+        <v>2.21211814880371</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G816" t="n">
-        <v>2.22183465957642</v>
+        <v>2.221834897995</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>3.40499997138977</v>
       </c>
       <c r="G817" t="n">
-        <v>2.2056405544281</v>
+        <v>2.20564079284668</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G818" t="n">
-        <v>2.20887970924377</v>
+        <v>2.2088794708252</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G819" t="n">
-        <v>2.20887970924377</v>
+        <v>2.2088794708252</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G821" t="n">
-        <v>2.21211838722229</v>
+        <v>2.21211814880371</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G822" t="n">
-        <v>2.23479032516479</v>
+        <v>2.23478984832764</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G823" t="n">
-        <v>2.24774527549744</v>
+        <v>2.24774551391602</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G824" t="n">
-        <v>2.25422310829163</v>
+        <v>2.25422286987305</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>3.5</v>
       </c>
       <c r="G827" t="n">
-        <v>2.26717829704285</v>
+        <v>2.26717805862427</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G828" t="n">
-        <v>2.25746202468872</v>
+        <v>2.25746178627014</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>3.5</v>
       </c>
       <c r="G829" t="n">
-        <v>2.26717829704285</v>
+        <v>2.26717805862427</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G830" t="n">
-        <v>2.29956674575806</v>
+        <v>2.29956650733948</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G831" t="n">
-        <v>2.29956674575806</v>
+        <v>2.29956650733948</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G833" t="n">
-        <v>2.31252193450928</v>
+        <v>2.3125216960907</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G836" t="n">
-        <v>2.33843231201172</v>
+        <v>2.3384325504303</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G837" t="n">
-        <v>2.37405943870544</v>
+        <v>2.37405967712402</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>3.68499994277954</v>
       </c>
       <c r="G838" t="n">
-        <v>2.38701486587524</v>
+        <v>2.38701510429382</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>3.70499992370605</v>
       </c>
       <c r="G841" t="n">
-        <v>2.39996981620789</v>
+        <v>2.39997029304504</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G842" t="n">
-        <v>2.41292548179626</v>
+        <v>2.41292524337769</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>3.81500005722046</v>
       </c>
       <c r="G843" t="n">
-        <v>2.4712245464325</v>
+        <v>2.47122430801392</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G845" t="n">
-        <v>2.49389600753784</v>
+        <v>2.49389624595642</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>3.81500005722046</v>
       </c>
       <c r="G847" t="n">
-        <v>2.4712245464325</v>
+        <v>2.47122430801392</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G848" t="n">
-        <v>2.74367213249207</v>
+        <v>2.74367237091064</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>3.49499988555908</v>
       </c>
       <c r="G849" t="n">
-        <v>2.48423171043396</v>
+        <v>2.48423194885254</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G851" t="n">
-        <v>2.4380304813385</v>
+        <v>2.43803000450134</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>3.625</v>
       </c>
       <c r="G855" t="n">
-        <v>2.57663536071777</v>
+        <v>2.57663512229919</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G857" t="n">
-        <v>2.55886554718018</v>
+        <v>2.5588653087616</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G858" t="n">
-        <v>2.52332520484924</v>
+        <v>2.52332544326782</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G859" t="n">
-        <v>2.51621794700623</v>
+        <v>2.51621770858765</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G860" t="n">
-        <v>2.50910973548889</v>
+        <v>2.50910997390747</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G861" t="n">
-        <v>2.53043341636658</v>
+        <v>2.53043365478516</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G862" t="n">
-        <v>2.52687954902649</v>
+        <v>2.52687978744507</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G863" t="n">
-        <v>2.58018922805786</v>
+        <v>2.58018946647644</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G864" t="n">
-        <v>2.55886554718018</v>
+        <v>2.5588653087616</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G866" t="n">
-        <v>2.56241941452026</v>
+        <v>2.56241965293884</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>3.61500000953674</v>
       </c>
       <c r="G867" t="n">
-        <v>2.56952738761902</v>
+        <v>2.5695276260376</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G870" t="n">
-        <v>2.55886554718018</v>
+        <v>2.5588653087616</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G871" t="n">
-        <v>2.56241941452026</v>
+        <v>2.56241965293884</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G872" t="n">
-        <v>2.59440517425537</v>
+        <v>2.59440493583679</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>3.625</v>
       </c>
       <c r="G873" t="n">
-        <v>2.57663536071777</v>
+        <v>2.57663512229919</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G874" t="n">
-        <v>2.58018922805786</v>
+        <v>2.58018946647644</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G878" t="n">
-        <v>2.59440517425537</v>
+        <v>2.59440493583679</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G882" t="n">
-        <v>2.67970085144043</v>
+        <v>2.67970061302185</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G883" t="n">
-        <v>2.69391679763794</v>
+        <v>2.69391655921936</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G884" t="n">
-        <v>2.67259287834167</v>
+        <v>2.67259311676025</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G887" t="n">
-        <v>2.67259287834167</v>
+        <v>2.67259311676025</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>4.14499998092651</v>
       </c>
       <c r="G902" t="n">
-        <v>2.94624948501587</v>
+        <v>2.94624924659729</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G903" t="n">
-        <v>2.94980359077454</v>
+        <v>2.94980335235596</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G905" t="n">
-        <v>2.99245095252991</v>
+        <v>2.99245119094849</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>4.22499990463257</v>
       </c>
       <c r="G907" t="n">
-        <v>3.00311279296875</v>
+        <v>3.00311303138733</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G908" t="n">
-        <v>2.97112703323364</v>
+        <v>2.97112679481506</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G910" t="n">
-        <v>2.90715575218201</v>
+        <v>2.90715551376343</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>4.00500011444092</v>
       </c>
       <c r="G915" t="n">
-        <v>2.84673810005188</v>
+        <v>2.84673762321472</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>3.97499990463257</v>
       </c>
       <c r="G917" t="n">
-        <v>2.82541394233704</v>
+        <v>2.82541370391846</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G924" t="n">
-        <v>2.91426348686218</v>
+        <v>2.9142632484436</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G926" t="n">
-        <v>2.86806154251099</v>
+        <v>2.86806178092957</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G929" t="n">
-        <v>2.75788831710815</v>
+        <v>2.75788855552673</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G930" t="n">
-        <v>2.8289680480957</v>
+        <v>2.82896780967712</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>3.93499994277954</v>
       </c>
       <c r="G932" t="n">
-        <v>2.79698181152344</v>
+        <v>2.79698204994202</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G933" t="n">
-        <v>2.8005359172821</v>
+        <v>2.80053615570068</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>3.95499992370605</v>
       </c>
       <c r="G935" t="n">
-        <v>2.81119775772095</v>
+        <v>2.81119799613953</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G937" t="n">
-        <v>2.70457863807678</v>
+        <v>2.7045783996582</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G940" t="n">
-        <v>2.66193079948425</v>
+        <v>2.66193056106567</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>3.79500007629395</v>
       </c>
       <c r="G941" t="n">
-        <v>2.69747066497803</v>
+        <v>2.69747090339661</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G942" t="n">
-        <v>2.70813250541687</v>
+        <v>2.70813298225403</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G946" t="n">
-        <v>2.74367213249207</v>
+        <v>2.74367237091064</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G949" t="n">
-        <v>2.77210450172424</v>
+        <v>2.77210426330566</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G951" t="n">
-        <v>2.77921223640442</v>
+        <v>2.779212474823</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>3.88499999046326</v>
       </c>
       <c r="G952" t="n">
-        <v>2.76144218444824</v>
+        <v>2.76144242286682</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G954" t="n">
-        <v>2.75788831710815</v>
+        <v>2.75788855552673</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G956" t="n">
-        <v>2.74722623825073</v>
+        <v>2.74722647666931</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G957" t="n">
-        <v>2.74367213249207</v>
+        <v>2.74367237091064</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G967" t="n">
-        <v>2.69391679763794</v>
+        <v>2.69391655921936</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G970" t="n">
-        <v>2.64060688018799</v>
+        <v>2.64060711860657</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G971" t="n">
-        <v>2.62994527816772</v>
+        <v>2.62994503974915</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>3.74499988555908</v>
       </c>
       <c r="G973" t="n">
-        <v>2.66193079948425</v>
+        <v>2.66193056106567</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G975" t="n">
-        <v>2.62283730506897</v>
+        <v>2.62283754348755</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G981" t="n">
-        <v>2.70457863807678</v>
+        <v>2.7045783996582</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G984" t="n">
-        <v>2.90715575218201</v>
+        <v>2.90715551376343</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G985" t="n">
-        <v>2.87872362136841</v>
+        <v>2.87872385978699</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G988" t="n">
-        <v>2.8005359172821</v>
+        <v>2.80053615570068</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>3.88499999046326</v>
       </c>
       <c r="G991" t="n">
-        <v>2.76144218444824</v>
+        <v>2.76144242286682</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>3.95499992370605</v>
       </c>
       <c r="G995" t="n">
-        <v>2.81119775772095</v>
+        <v>2.81119799613953</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>4.03499984741211</v>
       </c>
       <c r="G997" t="n">
-        <v>2.86806154251099</v>
+        <v>2.86806178092957</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>3.88499999046326</v>
       </c>
       <c r="G998" t="n">
-        <v>2.76144218444824</v>
+        <v>2.76144242286682</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>3.88499999046326</v>
       </c>
       <c r="G1000" t="n">
-        <v>2.76144218444824</v>
+        <v>2.76144242286682</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>3.88499999046326</v>
       </c>
       <c r="G1001" t="n">
-        <v>2.76144218444824</v>
+        <v>2.76144242286682</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1004" t="n">
-        <v>2.72945666313171</v>
+        <v>2.72945642471313</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1006" t="n">
-        <v>2.67259287834167</v>
+        <v>2.67259311676025</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G1008" t="n">
-        <v>2.67614698410034</v>
+        <v>2.67614722251892</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1010" t="n">
-        <v>2.67259287834167</v>
+        <v>2.67259311676025</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G1016" t="n">
-        <v>2.70457863807678</v>
+        <v>2.7045783996582</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G1017" t="n">
-        <v>2.70457863807678</v>
+        <v>2.7045783996582</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G1018" t="n">
-        <v>2.70457863807678</v>
+        <v>2.7045783996582</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G1020" t="n">
-        <v>2.70457863807678</v>
+        <v>2.7045783996582</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1021" t="n">
-        <v>2.70813250541687</v>
+        <v>2.70813298225403</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1023" t="n">
-        <v>2.74367213249207</v>
+        <v>2.74367237091064</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1025" t="n">
-        <v>2.72945666313171</v>
+        <v>2.72945642471313</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1027" t="n">
-        <v>2.8005359172821</v>
+        <v>2.80053615570068</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>3.99499988555908</v>
       </c>
       <c r="G1032" t="n">
-        <v>2.83962988853455</v>
+        <v>2.83962965011597</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1033" t="n">
-        <v>2.8005359172821</v>
+        <v>2.80053615570068</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1037" t="n">
-        <v>3.14171814918518</v>
+        <v>3.14171838760376</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G1038" t="n">
-        <v>3.2163519859314</v>
+        <v>3.21635174751282</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G1039" t="n">
-        <v>3.15948843955994</v>
+        <v>3.15948796272278</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G1040" t="n">
-        <v>3.24833798408508</v>
+        <v>3.24833750724792</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>4.49499988555908</v>
       </c>
       <c r="G1041" t="n">
-        <v>3.19502758979797</v>
+        <v>3.19502782821655</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>4.57499980926514</v>
       </c>
       <c r="G1042" t="n">
-        <v>3.25189137458801</v>
+        <v>3.25189161300659</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G1044" t="n">
-        <v>3.18792009353638</v>
+        <v>3.1879198551178</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>4.36499977111816</v>
       </c>
       <c r="G1045" t="n">
-        <v>3.10262417793274</v>
+        <v>3.10262441635132</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1046" t="n">
-        <v>3.07774662971497</v>
+        <v>3.07774639129639</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1047" t="n">
-        <v>3.06353068351746</v>
+        <v>3.06353044509888</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>4.38500022888184</v>
       </c>
       <c r="G1048" t="n">
-        <v>3.11684036254883</v>
+        <v>3.11684012413025</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1049" t="n">
-        <v>3.14171814918518</v>
+        <v>3.14171838760376</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1050" t="n">
-        <v>3.15593409538269</v>
+        <v>3.15593433380127</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>4.40500020980835</v>
       </c>
       <c r="G1051" t="n">
-        <v>3.13105630874634</v>
+        <v>3.13105607032776</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>4.38500022888184</v>
       </c>
       <c r="G1052" t="n">
-        <v>3.11684036254883</v>
+        <v>3.11684012413025</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1055" t="n">
-        <v>2.95691084861755</v>
+        <v>2.95691108703613</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1057" t="n">
-        <v>2.79342818260193</v>
+        <v>2.79342794418335</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>4.16499996185303</v>
       </c>
       <c r="G1060" t="n">
-        <v>2.96046495437622</v>
+        <v>2.9604651927948</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>4.125</v>
       </c>
       <c r="G1061" t="n">
-        <v>2.93203330039978</v>
+        <v>2.93203353881836</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1064" t="n">
-        <v>2.52332520484924</v>
+        <v>2.52332544326782</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G1067" t="n">
-        <v>2.14304971694946</v>
+        <v>2.14304995536804</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>3.125</v>
       </c>
       <c r="G1068" t="n">
-        <v>2.22123765945435</v>
+        <v>2.22123742103577</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1069" t="n">
-        <v>2.26033139228821</v>
+        <v>2.26033115386963</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>3.25500011444092</v>
       </c>
       <c r="G1071" t="n">
-        <v>2.313640832901</v>
+        <v>2.31364107131958</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1073" t="n">
-        <v>2.35984253883362</v>
+        <v>2.35984230041504</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1077" t="n">
-        <v>2.26033139228821</v>
+        <v>2.26033115386963</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1078" t="n">
-        <v>2.28165483474731</v>
+        <v>2.28165507316589</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>3.36500000953674</v>
       </c>
       <c r="G1079" t="n">
-        <v>2.3918285369873</v>
+        <v>2.39182829856873</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>3.20499992370605</v>
       </c>
       <c r="G1086" t="n">
-        <v>2.27810096740723</v>
+        <v>2.27810120582581</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1088" t="n">
-        <v>2.2958710193634</v>
+        <v>2.29587125778198</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G1090" t="n">
-        <v>2.29231691360474</v>
+        <v>2.29231715202332</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>3.25</v>
       </c>
       <c r="G1091" t="n">
-        <v>2.31008672714233</v>
+        <v>2.31008696556091</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1094" t="n">
-        <v>2.3314106464386</v>
+        <v>2.33141088485718</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1095" t="n">
-        <v>2.3314106464386</v>
+        <v>2.33141088485718</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1096" t="n">
-        <v>2.34562659263611</v>
+        <v>2.34562683105469</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>3.36500000953674</v>
       </c>
       <c r="G1098" t="n">
-        <v>2.3918285369873</v>
+        <v>2.39182829856873</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1099" t="n">
-        <v>2.36695027351379</v>
+        <v>2.36695051193237</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1100" t="n">
-        <v>2.35984253883362</v>
+        <v>2.35984230041504</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1101" t="n">
-        <v>2.3314106464386</v>
+        <v>2.33141088485718</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1104" t="n">
-        <v>2.34562659263611</v>
+        <v>2.34562683105469</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1105" t="n">
-        <v>2.3314106464386</v>
+        <v>2.33141088485718</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1108" t="n">
-        <v>2.34562659263611</v>
+        <v>2.34562683105469</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1109" t="n">
-        <v>2.40249061584473</v>
+        <v>2.40249037742615</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1111" t="n">
-        <v>2.3811662197113</v>
+        <v>2.38116645812988</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1112" t="n">
-        <v>2.3811662197113</v>
+        <v>2.38116645812988</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1117" t="n">
-        <v>2.70813250541687</v>
+        <v>2.70813298225403</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>3.95499992370605</v>
       </c>
       <c r="G1118" t="n">
-        <v>2.81119775772095</v>
+        <v>2.81119799613953</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1120" t="n">
-        <v>2.91426348686218</v>
+        <v>2.9142632484436</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1121" t="n">
-        <v>2.94980359077454</v>
+        <v>2.94980335235596</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1122" t="n">
-        <v>2.99955868721008</v>
+        <v>2.99955892562866</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1123" t="n">
-        <v>3.12750244140625</v>
+        <v>3.12750220298767</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>4.25500011444092</v>
       </c>
       <c r="G1125" t="n">
-        <v>3.17926263809204</v>
+        <v>3.17926239967346</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1126" t="n">
-        <v>3.01861834526062</v>
+        <v>3.01861810684204</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1127" t="n">
-        <v>2.95137190818787</v>
+        <v>2.95137166976929</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>3.81500005722046</v>
       </c>
       <c r="G1128" t="n">
-        <v>2.85050177574158</v>
+        <v>2.85050201416016</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1129" t="n">
-        <v>2.84676623344421</v>
+        <v>2.84676599502563</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1131" t="n">
-        <v>2.94389986991882</v>
+        <v>2.9439001083374</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>3.91499996185303</v>
       </c>
       <c r="G1133" t="n">
-        <v>2.92522025108337</v>
+        <v>2.92522048950195</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G1137" t="n">
-        <v>2.82061505317688</v>
+        <v>2.8206148147583</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G1138" t="n">
-        <v>2.77578377723694</v>
+        <v>2.77578353881836</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>3.77500009536743</v>
       </c>
       <c r="G1139" t="n">
-        <v>2.82061505317688</v>
+        <v>2.8206148147583</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1140" t="n">
-        <v>2.79446339607239</v>
+        <v>2.79446315765381</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>3.75</v>
       </c>
       <c r="G1141" t="n">
-        <v>2.80193519592285</v>
+        <v>2.80193543434143</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1142" t="n">
-        <v>2.79446339607239</v>
+        <v>2.79446315765381</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G1143" t="n">
-        <v>2.82808685302734</v>
+        <v>2.82808661460876</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1145" t="n">
-        <v>2.77204775810242</v>
+        <v>2.772047996521</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1146" t="n">
-        <v>2.75710415840149</v>
+        <v>2.75710439682007</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G1150" t="n">
-        <v>2.65623426437378</v>
+        <v>2.65623450279236</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1151" t="n">
-        <v>2.64502692222595</v>
+        <v>2.64502668380737</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G1164" t="n">
-        <v>2.47691082954407</v>
+        <v>2.47691059112549</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G1165" t="n">
-        <v>2.47691082954407</v>
+        <v>2.47691059112549</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G1166" t="n">
-        <v>2.47691082954407</v>
+        <v>2.47691059112549</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1171" t="n">
-        <v>2.56283664703369</v>
+        <v>2.56283688545227</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1173" t="n">
-        <v>2.59272432327271</v>
+        <v>2.59272408485413</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G1174" t="n">
-        <v>2.55162882804871</v>
+        <v>2.55162858963013</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>3.35500001907349</v>
       </c>
       <c r="G1176" t="n">
-        <v>2.5067982673645</v>
+        <v>2.50679779052734</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1177" t="n">
-        <v>2.53294944763184</v>
+        <v>2.53294968605042</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>3.375</v>
       </c>
       <c r="G1178" t="n">
-        <v>2.52174162864685</v>
+        <v>2.52174186706543</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1179" t="n">
-        <v>2.52547764778137</v>
+        <v>2.52547740936279</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G1185" t="n">
-        <v>2.4544951915741</v>
+        <v>2.45449542999268</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G1186" t="n">
-        <v>2.49932599067688</v>
+        <v>2.49932646751404</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>3.36500000953674</v>
       </c>
       <c r="G1187" t="n">
-        <v>2.51427006721497</v>
+        <v>2.51426982879639</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1189" t="n">
-        <v>2.46570301055908</v>
+        <v>2.4657027721405</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>3.3050000667572</v>
       </c>
       <c r="G1190" t="n">
-        <v>2.4694390296936</v>
+        <v>2.46943926811218</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>3.3050000667572</v>
       </c>
       <c r="G1191" t="n">
-        <v>2.4694390296936</v>
+        <v>2.46943926811218</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1195" t="n">
-        <v>2.52547764778137</v>
+        <v>2.52547740936279</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>3.36500000953674</v>
       </c>
       <c r="G1196" t="n">
-        <v>2.51427006721497</v>
+        <v>2.51426982879639</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>3.5</v>
       </c>
       <c r="G1197" t="n">
-        <v>2.61513948440552</v>
+        <v>2.61513924598694</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>3.21499991416931</v>
       </c>
       <c r="G1202" t="n">
-        <v>2.40219235420227</v>
+        <v>2.40219211578369</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1203" t="n">
-        <v>2.41340041160583</v>
+        <v>2.41340017318726</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G1204" t="n">
-        <v>2.36483335494995</v>
+        <v>2.36483359336853</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G1208" t="n">
-        <v>2.34988975524902</v>
+        <v>2.34988951683044</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1209" t="n">
-        <v>2.36109733581543</v>
+        <v>2.36109757423401</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1210" t="n">
-        <v>2.38351273536682</v>
+        <v>2.3835129737854</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1217" t="n">
-        <v>2.35362553596497</v>
+        <v>2.35362577438354</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1222" t="n">
-        <v>2.27890729904175</v>
+        <v>2.27890706062317</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1223" t="n">
-        <v>2.25649166107178</v>
+        <v>2.25649189949036</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G1225" t="n">
-        <v>2.23781228065491</v>
+        <v>2.23781204223633</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>3.04500007629395</v>
       </c>
       <c r="G1226" t="n">
-        <v>2.27517175674438</v>
+        <v>2.27517151832581</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>2.97499990463257</v>
       </c>
       <c r="G1229" t="n">
-        <v>2.2228684425354</v>
+        <v>2.22286868095398</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1230" t="n">
-        <v>2.27890729904175</v>
+        <v>2.27890706062317</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1233" t="n">
-        <v>2.21913266181946</v>
+        <v>2.21913290023804</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G1235" t="n">
-        <v>2.34988975524902</v>
+        <v>2.34988951683044</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1238" t="n">
-        <v>2.46570301055908</v>
+        <v>2.4657027721405</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G1241" t="n">
-        <v>2.49932599067688</v>
+        <v>2.49932646751404</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>3.32500004768372</v>
       </c>
       <c r="G1242" t="n">
-        <v>2.48438262939453</v>
+        <v>2.48438286781311</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1243" t="n">
-        <v>2.53294944763184</v>
+        <v>2.53294968605042</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>3.51500010490417</v>
       </c>
       <c r="G1251" t="n">
-        <v>2.62634754180908</v>
+        <v>2.6263473033905</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1253" t="n">
-        <v>2.59272432327271</v>
+        <v>2.59272408485413</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1257" t="n">
-        <v>2.55536484718323</v>
+        <v>2.55536460876465</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G1259" t="n">
-        <v>2.56657266616821</v>
+        <v>2.56657242774963</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1260" t="n">
-        <v>2.55536484718323</v>
+        <v>2.55536460876465</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>3.5550000667572</v>
       </c>
       <c r="G1263" t="n">
-        <v>2.65623426437378</v>
+        <v>2.65623450279236</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>3.51500010490417</v>
       </c>
       <c r="G1266" t="n">
-        <v>2.62634754180908</v>
+        <v>2.6263473033905</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1267" t="n">
-        <v>2.74963235855103</v>
+        <v>2.7496325969696</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1268" t="n">
-        <v>2.75710415840149</v>
+        <v>2.75710439682007</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G1270" t="n">
-        <v>2.71600937843323</v>
+        <v>2.71600914001465</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G1272" t="n">
-        <v>2.77578377723694</v>
+        <v>2.77578353881836</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1273" t="n">
-        <v>2.75710415840149</v>
+        <v>2.75710439682007</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1274" t="n">
-        <v>2.72721719741821</v>
+        <v>2.72721695899963</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1275" t="n">
-        <v>2.72721719741821</v>
+        <v>2.72721695899963</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1277" t="n">
-        <v>2.77951979637146</v>
+        <v>2.77951955795288</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1279" t="n">
-        <v>2.86918163299561</v>
+        <v>2.86918139457703</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1280" t="n">
-        <v>2.79446339607239</v>
+        <v>2.79446315765381</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1281" t="n">
-        <v>2.79446339607239</v>
+        <v>2.79446315765381</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G1282" t="n">
-        <v>2.81314301490784</v>
+        <v>2.81314325332642</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>3.75</v>
       </c>
       <c r="G1284" t="n">
-        <v>2.80193519592285</v>
+        <v>2.80193543434143</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1286" t="n">
-        <v>2.6973295211792</v>
+        <v>2.69732975959778</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1287" t="n">
-        <v>2.6973295211792</v>
+        <v>2.69732975959778</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1288" t="n">
-        <v>2.68985748291016</v>
+        <v>2.68985772132874</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1289" t="n">
-        <v>2.70480132102966</v>
+        <v>2.70480108261108</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G1290" t="n">
-        <v>2.67865014076233</v>
+        <v>2.67864990234375</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G1292" t="n">
-        <v>2.73842477798462</v>
+        <v>2.73842453956604</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>3.75</v>
       </c>
       <c r="G1296" t="n">
-        <v>2.80193519592285</v>
+        <v>2.80193543434143</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34091,7 +34091,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1297" t="n">
-        <v>2.77204775810242</v>
+        <v>2.772047996521</v>
       </c>
       <c r="H1297" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1300" t="n">
-        <v>2.80940675735474</v>
+        <v>2.80940699577332</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>3.75500011444092</v>
       </c>
       <c r="G1301" t="n">
-        <v>2.80567097663879</v>
+        <v>2.80567121505737</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>3.71499991416931</v>
       </c>
       <c r="G1302" t="n">
-        <v>2.77578377723694</v>
+        <v>2.77578353881836</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1303" t="n">
-        <v>2.75710415840149</v>
+        <v>2.75710439682007</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1304" t="n">
-        <v>2.70480132102966</v>
+        <v>2.70480108261108</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>3.65499997138977</v>
       </c>
       <c r="G1305" t="n">
-        <v>2.73095273971558</v>
+        <v>2.730952501297</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G1306" t="n">
-        <v>2.71600937843323</v>
+        <v>2.71600914001465</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G1307" t="n">
-        <v>2.71600937843323</v>
+        <v>2.71600914001465</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34377,7 +34377,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1308" t="n">
-        <v>2.70480132102966</v>
+        <v>2.70480108261108</v>
       </c>
       <c r="H1308" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G1310" t="n">
-        <v>2.67865014076233</v>
+        <v>2.67864990234375</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G1312" t="n">
-        <v>2.71600937843323</v>
+        <v>2.71600914001465</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34507,7 +34507,7 @@
         <v>3.59500002861023</v>
       </c>
       <c r="G1313" t="n">
-        <v>2.68612170219421</v>
+        <v>2.68612194061279</v>
       </c>
       <c r="H1313" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G1315" t="n">
-        <v>2.72348093986511</v>
+        <v>2.72348117828369</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1316" t="n">
-        <v>2.74963235855103</v>
+        <v>2.7496325969696</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G1317" t="n">
-        <v>2.7832555770874</v>
+        <v>2.78325533866882</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1319" t="n">
-        <v>2.8542377948761</v>
+        <v>2.85423803329468</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G1322" t="n">
-        <v>2.88786101341248</v>
+        <v>2.88786125183105</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G1325" t="n">
-        <v>2.82808685302734</v>
+        <v>2.82808661460876</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>3.76500010490417</v>
       </c>
       <c r="G1327" t="n">
-        <v>2.81314301490784</v>
+        <v>2.81314325332642</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>3.81500005722046</v>
       </c>
       <c r="G1328" t="n">
-        <v>2.85050177574158</v>
+        <v>2.85050201416016</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G1330" t="n">
-        <v>2.88786101341248</v>
+        <v>2.88786125183105</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1335" t="n">
-        <v>2.86918163299561</v>
+        <v>2.86918139457703</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G1342" t="n">
-        <v>2.88786101341248</v>
+        <v>2.88786125183105</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35391,7 +35391,7 @@
         <v>3.97499990463257</v>
       </c>
       <c r="G1347" t="n">
-        <v>2.97005105018616</v>
+        <v>2.97005128860474</v>
       </c>
       <c r="H1347" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>3.9449999332428</v>
       </c>
       <c r="G1348" t="n">
-        <v>2.94763612747192</v>
+        <v>2.94763588905334</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1351" t="n">
-        <v>3.03356170654297</v>
+        <v>3.03356194496155</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>4.05499982833862</v>
       </c>
       <c r="G1353" t="n">
-        <v>3.02982592582703</v>
+        <v>3.02982568740845</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1354" t="n">
-        <v>3.04927277565002</v>
+        <v>3.04927253723145</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1355" t="n">
-        <v>2.94814896583557</v>
+        <v>2.94814872741699</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1356" t="n">
-        <v>2.94814896583557</v>
+        <v>2.94814872741699</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1358" t="n">
-        <v>2.92481255531311</v>
+        <v>2.92481231689453</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>3.72499990463257</v>
       </c>
       <c r="G1362" t="n">
-        <v>2.89758682250977</v>
+        <v>2.89758706092834</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1367" t="n">
-        <v>2.87814021110535</v>
+        <v>2.87813997268677</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -35989,7 +35989,7 @@
         <v>3.68499994277954</v>
       </c>
       <c r="G1370" t="n">
-        <v>2.86647200584412</v>
+        <v>2.86647176742554</v>
       </c>
       <c r="H1370" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>3.68499994277954</v>
       </c>
       <c r="G1371" t="n">
-        <v>2.86647200584412</v>
+        <v>2.86647176742554</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1372" t="n">
-        <v>2.85480403900146</v>
+        <v>2.85480380058289</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1373" t="n">
-        <v>2.88591885566711</v>
+        <v>2.88591909408569</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1374" t="n">
-        <v>2.85480403900146</v>
+        <v>2.85480380058289</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1375" t="n">
-        <v>2.85480403900146</v>
+        <v>2.85480380058289</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1377" t="n">
-        <v>2.87814021110535</v>
+        <v>2.87813997268677</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1380" t="n">
-        <v>2.92481255531311</v>
+        <v>2.92481231689453</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1382" t="n">
-        <v>2.92481255531311</v>
+        <v>2.92481231689453</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G1388" t="n">
-        <v>2.83535695075989</v>
+        <v>2.83535718917847</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1390" t="n">
-        <v>2.81591010093689</v>
+        <v>2.81590986251831</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G1391" t="n">
-        <v>2.78868436813354</v>
+        <v>2.78868460655212</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>3.47499990463257</v>
       </c>
       <c r="G1402" t="n">
-        <v>2.70311808586121</v>
+        <v>2.70311832427979</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1403" t="n">
-        <v>2.72645425796509</v>
+        <v>2.72645449638367</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G1411" t="n">
-        <v>2.66422414779663</v>
+        <v>2.66422438621521</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>3.51500010490417</v>
       </c>
       <c r="G1416" t="n">
-        <v>2.73423337936401</v>
+        <v>2.73423314094543</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37237,7 +37237,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1418" t="n">
-        <v>2.73034405708313</v>
+        <v>2.73034381866455</v>
       </c>
       <c r="H1418" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>3.51500010490417</v>
       </c>
       <c r="G1420" t="n">
-        <v>2.73423337936401</v>
+        <v>2.73423314094543</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37315,7 +37315,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1421" t="n">
-        <v>2.73034405708313</v>
+        <v>2.73034381866455</v>
       </c>
       <c r="H1421" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>3.51500010490417</v>
       </c>
       <c r="G1422" t="n">
-        <v>2.73423337936401</v>
+        <v>2.73423314094543</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37393,7 +37393,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1424" t="n">
-        <v>2.87814021110535</v>
+        <v>2.87813997268677</v>
       </c>
       <c r="H1424" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1426" t="n">
-        <v>2.84702491760254</v>
+        <v>2.84702515602112</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1427" t="n">
-        <v>2.83924651145935</v>
+        <v>2.83924627304077</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37497,7 +37497,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1428" t="n">
-        <v>2.84702491760254</v>
+        <v>2.84702515602112</v>
       </c>
       <c r="H1428" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>3.64499998092651</v>
       </c>
       <c r="G1430" t="n">
-        <v>2.83535695075989</v>
+        <v>2.83535718917847</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1432" t="n">
-        <v>2.82368874549866</v>
+        <v>2.82368898391724</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37627,7 +37627,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G1433" t="n">
-        <v>2.80424189567566</v>
+        <v>2.80424165725708</v>
       </c>
       <c r="H1433" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G1434" t="n">
-        <v>2.80424189567566</v>
+        <v>2.80424165725708</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G1435" t="n">
-        <v>2.78868436813354</v>
+        <v>2.78868460655212</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1441" t="n">
-        <v>2.83924651145935</v>
+        <v>2.83924627304077</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1450" t="n">
-        <v>2.78479504585266</v>
+        <v>2.78479528427124</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38121,7 +38121,7 @@
         <v>3.52500009536743</v>
       </c>
       <c r="G1452" t="n">
-        <v>2.74201202392578</v>
+        <v>2.7420117855072</v>
       </c>
       <c r="H1452" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1453" t="n">
-        <v>2.73034405708313</v>
+        <v>2.73034381866455</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>3.52500009536743</v>
       </c>
       <c r="G1454" t="n">
-        <v>2.74201202392578</v>
+        <v>2.7420117855072</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38251,7 +38251,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1457" t="n">
-        <v>2.73034405708313</v>
+        <v>2.73034381866455</v>
       </c>
       <c r="H1457" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>3.47499990463257</v>
       </c>
       <c r="G1461" t="n">
-        <v>2.70311808586121</v>
+        <v>2.70311832427979</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38381,7 +38381,7 @@
         <v>3.47499990463257</v>
       </c>
       <c r="G1462" t="n">
-        <v>2.70311808586121</v>
+        <v>2.70311832427979</v>
       </c>
       <c r="H1462" t="s">
         <v>8</v>
@@ -38433,7 +38433,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G1464" t="n">
-        <v>2.67200303077698</v>
+        <v>2.6720027923584</v>
       </c>
       <c r="H1464" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G1466" t="n">
-        <v>2.66422414779663</v>
+        <v>2.66422438621521</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>3.47499990463257</v>
       </c>
       <c r="G1468" t="n">
-        <v>2.70311808586121</v>
+        <v>2.70311832427979</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>3.47499990463257</v>
       </c>
       <c r="G1471" t="n">
-        <v>2.70311808586121</v>
+        <v>2.70311832427979</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38641,7 +38641,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1472" t="n">
-        <v>2.71478605270386</v>
+        <v>2.71478629112244</v>
       </c>
       <c r="H1472" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>3.47499990463257</v>
       </c>
       <c r="G1473" t="n">
-        <v>2.70311808586121</v>
+        <v>2.70311832427979</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38771,7 +38771,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1477" t="n">
-        <v>2.78479504585266</v>
+        <v>2.78479528427124</v>
       </c>
       <c r="H1477" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G1480" t="n">
-        <v>2.80424189567566</v>
+        <v>2.80424165725708</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -38953,7 +38953,7 @@
         <v>3.52500009536743</v>
       </c>
       <c r="G1484" t="n">
-        <v>2.74201202392578</v>
+        <v>2.7420117855072</v>
       </c>
       <c r="H1484" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1487" t="n">
-        <v>2.73034405708313</v>
+        <v>2.73034381866455</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39083,7 +39083,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G1489" t="n">
-        <v>2.80424189567566</v>
+        <v>2.80424165725708</v>
       </c>
       <c r="H1489" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1495" t="n">
-        <v>2.73034405708313</v>
+        <v>2.73034381866455</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>3.51500010490417</v>
       </c>
       <c r="G1496" t="n">
-        <v>2.73423337936401</v>
+        <v>2.73423314094543</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>3.51500010490417</v>
       </c>
       <c r="G1497" t="n">
-        <v>2.73423337936401</v>
+        <v>2.73423314094543</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39317,7 +39317,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1498" t="n">
-        <v>2.71478605270386</v>
+        <v>2.71478629112244</v>
       </c>
       <c r="H1498" t="s">
         <v>8</v>
@@ -39395,7 +39395,7 @@
         <v>3.47499990463257</v>
       </c>
       <c r="G1501" t="n">
-        <v>2.70311808586121</v>
+        <v>2.70311832427979</v>
       </c>
       <c r="H1501" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G1505" t="n">
-        <v>2.67200303077698</v>
+        <v>2.6720027923584</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G1506" t="n">
-        <v>2.67200303077698</v>
+        <v>2.6720027923584</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G1509" t="n">
-        <v>2.66422414779663</v>
+        <v>2.66422438621521</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39655,7 +39655,7 @@
         <v>3.47499990463257</v>
       </c>
       <c r="G1511" t="n">
-        <v>2.70311808586121</v>
+        <v>2.70311832427979</v>
       </c>
       <c r="H1511" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>3.38499999046326</v>
       </c>
       <c r="G1513" t="n">
-        <v>2.63310933113098</v>
+        <v>2.6331090927124</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1515" t="n">
-        <v>2.78479504585266</v>
+        <v>2.78479528427124</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39811,7 +39811,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G1517" t="n">
-        <v>2.67200303077698</v>
+        <v>2.6720027923584</v>
       </c>
       <c r="H1517" t="s">
         <v>8</v>
@@ -39837,7 +39837,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1518" t="n">
-        <v>2.65255641937256</v>
+        <v>2.65255665779114</v>
       </c>
       <c r="H1518" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1519" t="n">
-        <v>2.65255641937256</v>
+        <v>2.65255665779114</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1522" t="n">
-        <v>2.65255641937256</v>
+        <v>2.65255665779114</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1527" t="n">
-        <v>2.72645425796509</v>
+        <v>2.72645449638367</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>3.47499990463257</v>
       </c>
       <c r="G1531" t="n">
-        <v>2.70311808586121</v>
+        <v>2.70311832427979</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40227,7 +40227,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1533" t="n">
-        <v>2.71478605270386</v>
+        <v>2.71478629112244</v>
       </c>
       <c r="H1533" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1534" t="n">
-        <v>2.73034405708313</v>
+        <v>2.73034381866455</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1536" t="n">
-        <v>2.71478605270386</v>
+        <v>2.71478629112244</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40357,7 +40357,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1538" t="n">
-        <v>2.71478605270386</v>
+        <v>2.71478629112244</v>
       </c>
       <c r="H1538" t="s">
         <v>8</v>
@@ -40383,7 +40383,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1539" t="n">
-        <v>2.73034405708313</v>
+        <v>2.73034381866455</v>
       </c>
       <c r="H1539" t="s">
         <v>8</v>
@@ -40435,7 +40435,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1541" t="n">
-        <v>2.73034405708313</v>
+        <v>2.73034381866455</v>
       </c>
       <c r="H1541" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G1542" t="n">
-        <v>2.69533944129944</v>
+        <v>2.69533920288086</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1545" t="n">
-        <v>2.71478605270386</v>
+        <v>2.71478629112244</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40617,7 +40617,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1548" t="n">
-        <v>2.78479504585266</v>
+        <v>2.78479528427124</v>
       </c>
       <c r="H1548" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1549" t="n">
-        <v>2.82368874549866</v>
+        <v>2.82368898391724</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -40669,7 +40669,7 @@
         <v>3.58500003814697</v>
       </c>
       <c r="G1550" t="n">
-        <v>2.78868436813354</v>
+        <v>2.78868460655212</v>
       </c>
       <c r="H1550" t="s">
         <v>8</v>
@@ -40721,7 +40721,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1552" t="n">
-        <v>2.73034405708313</v>
+        <v>2.73034381866455</v>
       </c>
       <c r="H1552" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1555" t="n">
-        <v>2.73034405708313</v>
+        <v>2.73034381866455</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G1559" t="n">
-        <v>2.69533944129944</v>
+        <v>2.69533920288086</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -40929,7 +40929,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G1560" t="n">
-        <v>2.66422414779663</v>
+        <v>2.66422438621521</v>
       </c>
       <c r="H1560" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>3.38499999046326</v>
       </c>
       <c r="G1564" t="n">
-        <v>2.63310933113098</v>
+        <v>2.6331090927124</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>3.52500009536743</v>
       </c>
       <c r="G1567" t="n">
-        <v>2.74201202392578</v>
+        <v>2.7420117855072</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41163,7 +41163,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G1569" t="n">
-        <v>2.64088773727417</v>
+        <v>2.64088797569275</v>
       </c>
       <c r="H1569" t="s">
         <v>8</v>
@@ -41189,7 +41189,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1570" t="n">
-        <v>2.62144112586975</v>
+        <v>2.62144088745117</v>
       </c>
       <c r="H1570" t="s">
         <v>8</v>
@@ -41241,7 +41241,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1572" t="n">
-        <v>2.51253867149353</v>
+        <v>2.51253843307495</v>
       </c>
       <c r="H1572" t="s">
         <v>8</v>
@@ -41345,7 +41345,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G1576" t="n">
-        <v>2.69533944129944</v>
+        <v>2.69533920288086</v>
       </c>
       <c r="H1576" t="s">
         <v>8</v>
@@ -41397,7 +41397,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1578" t="n">
-        <v>2.60588359832764</v>
+        <v>2.60588383674622</v>
       </c>
       <c r="H1578" t="s">
         <v>8</v>
@@ -41501,7 +41501,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G1582" t="n">
-        <v>2.64088773727417</v>
+        <v>2.64088797569275</v>
       </c>
       <c r="H1582" t="s">
         <v>8</v>
@@ -41553,7 +41553,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1584" t="n">
-        <v>2.60588359832764</v>
+        <v>2.60588383674622</v>
       </c>
       <c r="H1584" t="s">
         <v>8</v>
@@ -41605,7 +41605,7 @@
         <v>3.34500002861023</v>
       </c>
       <c r="G1586" t="n">
-        <v>2.60199403762817</v>
+        <v>2.60199427604675</v>
       </c>
       <c r="H1586" t="s">
         <v>8</v>
@@ -41631,7 +41631,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1587" t="n">
-        <v>2.65255641937256</v>
+        <v>2.65255665779114</v>
       </c>
       <c r="H1587" t="s">
         <v>8</v>
@@ -41787,7 +41787,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G1593" t="n">
-        <v>2.66422414779663</v>
+        <v>2.66422438621521</v>
       </c>
       <c r="H1593" t="s">
         <v>8</v>
@@ -41865,7 +41865,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1596" t="n">
-        <v>2.72645425796509</v>
+        <v>2.72645449638367</v>
       </c>
       <c r="H1596" t="s">
         <v>8</v>
@@ -41969,7 +41969,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1600" t="n">
-        <v>2.72645425796509</v>
+        <v>2.72645449638367</v>
       </c>
       <c r="H1600" t="s">
         <v>8</v>
@@ -42125,7 +42125,7 @@
         <v>3.51500010490417</v>
       </c>
       <c r="G1606" t="n">
-        <v>2.73423337936401</v>
+        <v>2.73423314094543</v>
       </c>
       <c r="H1606" t="s">
         <v>8</v>
@@ -42177,7 +42177,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G1608" t="n">
-        <v>2.72645425796509</v>
+        <v>2.72645449638367</v>
       </c>
       <c r="H1608" t="s">
         <v>8</v>
@@ -42203,7 +42203,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1609" t="n">
-        <v>2.73034405708313</v>
+        <v>2.73034381866455</v>
       </c>
       <c r="H1609" t="s">
         <v>8</v>
@@ -71274,6 +71274,32 @@
         <v>2.65000009536743</v>
       </c>
       <c r="H2727" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2728">
+      <c r="A2728" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B2728" t="n">
+        <v>113754</v>
+      </c>
+      <c r="C2728" t="n">
+        <v>2.67000007629395</v>
+      </c>
+      <c r="D2728" t="n">
+        <v>2.61999988555908</v>
+      </c>
+      <c r="E2728" t="n">
+        <v>2.67000007629395</v>
+      </c>
+      <c r="F2728" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="G2728" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="H2728" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ASC.MI.xlsx
+++ b/data/ASC.MI.xlsx
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>2.69000005722046</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>2.65000009536743</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>302674</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>2.73000001907349</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>2.63000011444092</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>2.63000011444092</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ASC.MI.xlsx
+++ b/data/ASC.MI.xlsx
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>2.63000011444092</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>2.73000001907349</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>184019</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>2.73000001907349</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>2.72499990463257</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ASC.MI.xlsx
+++ b/data/ASC.MI.xlsx
@@ -63316,8 +63316,31 @@
       <c r="E2737" t="n">
         <v>2.72499990463257</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>2.70499992370605</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>112144</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>2.74000000953674</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>2.66499996185303</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>2.66499996185303</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ASC.MI.xlsx
+++ b/data/ASC.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>2.66499996185303</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>2.70000004768372</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>84994</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>2.75999999046326</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>2.69000005722046</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>2.73000001907349</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ASC.MI.xlsx
+++ b/data/ASC.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>131958</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>2.78999996185303</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>2.70499992370605</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>2.74499988555908</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>2.78999996185303</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
